--- a/exports/Brewfather_Recipes_Summary.xlsx
+++ b/exports/Brewfather_Recipes_Summary.xlsx
@@ -2072,7 +2072,7 @@
         <v>5.12</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>4.3</v>
@@ -20185,10 +20185,10 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>6.3</v>
+        <v>5.2</v>
       </c>
       <c r="H77" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J77" t="n">
         <v>3.5</v>
@@ -20200,7 +20200,7 @@
         <v>30</v>
       </c>
       <c r="Q77" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>

--- a/exports/Brewfather_Recipes_Summary.xlsx
+++ b/exports/Brewfather_Recipes_Summary.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recipes'!$A$1:$P$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$94</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hops'!$A$1:$AP$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hops'!$A$1:$AP$80</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Yeast'!$A$1:$AL$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Misc'!$A$1:$AB$146</definedName>
   </definedNames>
@@ -775,7 +775,7 @@
         <v>5.12</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>22.8</v>
+        <v>21.2</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>4.2</v>
@@ -794,8 +794,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gonna leave this at d rest temp while on holiday. 
-Spund later in fermentation up to 12 psi
+          <t>Spund later in fermentation up to 12 psi
 Pitch 22 grams yeast
 No gelatine</t>
         </is>
@@ -12343,7 +12342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP81"/>
+  <dimension ref="A1:AP80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -13439,7 +13438,7 @@
         <v>30</v>
       </c>
       <c r="Q11" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -13536,7 +13535,7 @@
         <v>3.2</v>
       </c>
       <c r="H12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N12" t="b">
         <v>0</v>
@@ -13612,12 +13611,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AlNro2l8joSt8O98vSwLNZqS08yafE</t>
+          <t>DEYAnVWrgMtg87sSVkuGpS5F2eZFF4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kalahari lager</t>
+          <t>London Pub Gen 2 Amber Ale</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -13627,38 +13626,49 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>default-b73163ee</t>
+          <t>default-southerndawn</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3.2</v>
+        <v>11.7</v>
       </c>
       <c r="H13" t="n">
-        <v>20</v>
+        <v>8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5.1</v>
       </c>
       <c r="N13" t="b">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>15</v>
+      </c>
       <c r="Q13" t="n">
-        <v>1.4</v>
+        <v>18.3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Hallertauer Mittelfrueh</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr"/>
+          <t>Southern Dawn</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Resembles Southern Promise but with a different aroma profile. Has a fruity, spicy aroma and is relatively neutral when bittering.</t>
+        </is>
+      </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="n">
-        <v>80</v>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Nugget, Magnum</t>
+        </is>
       </c>
       <c r="Z13" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -13667,45 +13677,44 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Aroma</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Aroma</t>
+          <t>Boil</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 85000000, "_seconds": 1714216059}</t>
+          <t>{"_nanoseconds": 795000000, "_seconds": 1697269074}</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4uNBveCLExwfvW2GLeBzkjAPZFK1uw</t>
+          <t>6d29uGYQ3NPbK3eq6cqpiOctCm0yxG</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 227000000, "_seconds": 1789895043}</t>
+          <t>{"_nanoseconds": 911000000, "_seconds": 1721546982}</t>
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1789895043227</v>
+        <v>1721546982911</v>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>3.1.0</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="AL13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>45</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr"/>
     </row>
@@ -13734,7 +13743,7 @@
         <v>11.7</v>
       </c>
       <c r="H14" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
         <v>5.1</v>
@@ -13746,7 +13755,7 @@
         <v>15</v>
       </c>
       <c r="Q14" t="n">
-        <v>18.3</v>
+        <v>16.9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -13769,7 +13778,7 @@
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -13837,17 +13846,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>default-southerndawn</t>
+          <t>default-africanqueen</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>11.7</v>
+        <v>13</v>
       </c>
       <c r="H15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="N15" t="b">
         <v>0</v>
@@ -13856,30 +13865,26 @@
         <v>15</v>
       </c>
       <c r="Q15" t="n">
-        <v>16.9</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Southern Dawn</t>
+          <t>African Queen</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Resembles Southern Promise but with a different aroma profile. Has a fruity, spicy aroma and is relatively neutral when bittering.</t>
+          <t>A high alpha hop from South Africa with interesting bittering potential and fruity flavors. Fruity aroma includes hints of blueberry, cassis, passion fruit, citrus, stone fruit, black currant, tea, lemongrass and even chili. Can be used both for bittering and as a late addition.</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>Nugget, Magnum</t>
-        </is>
-      </c>
+          <t>South African</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
       <c r="Z15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -13900,29 +13905,29 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 795000000, "_seconds": 1697269074}</t>
+          <t>{"_nanoseconds": 311000000, "_seconds": 1699176795}</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>6d29uGYQ3NPbK3eq6cqpiOctCm0yxG</t>
+          <t>R8Z015agfqmYiPfmcje6KveBCZZtwb</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 911000000, "_seconds": 1721546982}</t>
+          <t>{"_nanoseconds": 806000000, "_seconds": 1726505806}</t>
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1721546982911</v>
+        <v>1726505806806</v>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>2.11.2</t>
         </is>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>-95</v>
       </c>
       <c r="AM15" t="inlineStr"/>
       <c r="AN15" t="inlineStr"/>
@@ -13932,12 +13937,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DEYAnVWrgMtg87sSVkuGpS5F2eZFF4</t>
+          <t>J7UYemr5KKh2Xlh4avrPvwdUZmPRfP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>London Pub Gen 2 Amber Ale</t>
+          <t>Rice beer</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -13947,45 +13952,45 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>default-africanqueen</t>
+          <t>default-J80zzFn0TQEAwwaQuzMQsRYzrIvBOC</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>13</v>
+        <v>6.3</v>
       </c>
       <c r="H16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="b">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>African Queen</t>
+          <t>Hallertau Perle</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>A high alpha hop from South Africa with interesting bittering potential and fruity flavors. Fruity aroma includes hints of blueberry, cassis, passion fruit, citrus, stone fruit, black currant, tea, lemongrass and even chili. Can be used both for bittering and as a late addition.</t>
+          <t>A dual-purpose hop that offers great bittering properties as well as a well-rounded aroma profile. Aroma: Herbal - tea, pepper, floral, citrus, earthy, woody, grassy, caramel Alpha Acid: 4.0 - 9.0% Beta Acid: 2.5 - 4.5% Total Oil: 0.5 - 1.3 ml/100g</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>South African</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -14004,31 +14009,34 @@
       </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="n">
+        <v>2024</v>
+      </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 311000000, "_seconds": 1699176795}</t>
+          <t>{"_nanoseconds": 223000000, "_seconds": 1778682625}</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>R8Z015agfqmYiPfmcje6KveBCZZtwb</t>
+          <t>RUQnJfJFRnXph5sp3FJtmw89Hv1WVi</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 806000000, "_seconds": 1726505806}</t>
+          <t>{"_nanoseconds": 223000000, "_seconds": 1778682625}</t>
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1726505806806</v>
+        <v>1778682625223</v>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2.11.2</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="AL16" t="n">
-        <v>-95</v>
+        <v>100</v>
       </c>
       <c r="AM16" t="inlineStr"/>
       <c r="AN16" t="inlineStr"/>
@@ -14053,37 +14061,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>default-J80zzFn0TQEAwwaQuzMQsRYzrIvBOC</t>
+          <t>default-b73163ee</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>6.3</v>
+        <v>3.2</v>
       </c>
       <c r="H17" t="n">
-        <v>15</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.5</v>
+        <v>30</v>
       </c>
       <c r="N17" t="b">
         <v>0</v>
       </c>
-      <c r="O17" t="n">
-        <v>30</v>
-      </c>
       <c r="Q17" t="n">
-        <v>16.7</v>
+        <v>6.1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Hallertau Perle</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>A dual-purpose hop that offers great bittering properties as well as a well-rounded aroma profile. Aroma: Herbal - tea, pepper, floral, citrus, earthy, woody, grassy, caramel Alpha Acid: 4.0 - 9.0% Beta Acid: 2.5 - 4.5% Total Oil: 0.5 - 1.3 ml/100g</t>
-        </is>
-      </c>
+          <t>Hallertauer Mittelfrueh</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Germany</t>
@@ -14091,7 +14089,7 @@
       </c>
       <c r="X17" t="inlineStr"/>
       <c r="Z17" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -14100,7 +14098,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Aroma</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -14110,34 +14108,31 @@
       </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="n">
-        <v>2024</v>
-      </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 223000000, "_seconds": 1778682625}</t>
+          <t>{"_nanoseconds": 85000000, "_seconds": 1714216059}</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>RUQnJfJFRnXph5sp3FJtmw89Hv1WVi</t>
+          <t>HFqcbMgx7i805V8lcYcrBe9YfIEduF</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 223000000, "_seconds": 1778682625}</t>
+          <t>{"_nanoseconds": 105000000, "_seconds": 1775807225}</t>
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1778682625223</v>
+        <v>1775807225105</v>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="AL17" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="AM17" t="inlineStr"/>
       <c r="AN17" t="inlineStr"/>
@@ -14147,12 +14142,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J7UYemr5KKh2Xlh4avrPvwdUZmPRfP</t>
+          <t>JosUqRpyUkkCJKNHlRWL890UWQpSUa</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rice beer</t>
+          <t>Kolserig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -14162,27 +14157,37 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>default-b73163ee</t>
+          <t>default-J80zzFn0TQEAwwaQuzMQsRYzrIvBOC</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="H18" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N18" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
         <v>30</v>
       </c>
-      <c r="N18" t="b">
-        <v>0</v>
-      </c>
       <c r="Q18" t="n">
-        <v>6.1</v>
+        <v>11.3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Hallertauer Mittelfrueh</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr"/>
+          <t>Hallertau Perle</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>A dual-purpose hop that offers great bittering properties as well as a well-rounded aroma profile. Aroma: Herbal - tea, pepper, floral, citrus, earthy, woody, grassy, caramel Alpha Acid: 4.0 - 9.0% Beta Acid: 2.5 - 4.5% Total Oil: 0.5 - 1.3 ml/100g</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr">
         <is>
           <t>Germany</t>
@@ -14190,7 +14195,7 @@
       </c>
       <c r="X18" t="inlineStr"/>
       <c r="Z18" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -14199,7 +14204,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Aroma</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -14209,32 +14214,12 @@
       </c>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 85000000, "_seconds": 1714216059}</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>HFqcbMgx7i805V8lcYcrBe9YfIEduF</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 105000000, "_seconds": 1775807225}</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1775807225105</v>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>3.0.0</t>
-        </is>
-      </c>
-      <c r="AL18" t="n">
-        <v>5</v>
-      </c>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="inlineStr"/>
       <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr"/>
@@ -14258,17 +14243,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>default-J80zzFn0TQEAwwaQuzMQsRYzrIvBOC</t>
+          <t>default-southernaroma</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="H19" t="n">
         <v>13.1</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5</v>
+        <v>5.59</v>
       </c>
       <c r="N19" t="b">
         <v>0</v>
@@ -14277,24 +14262,28 @@
         <v>30</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Hallertau Perle</t>
+          <t>Southern Aroma</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>A dual-purpose hop that offers great bittering properties as well as a well-rounded aroma profile. Aroma: Herbal - tea, pepper, floral, citrus, earthy, woody, grassy, caramel Alpha Acid: 4.0 - 9.0% Beta Acid: 2.5 - 4.5% Total Oil: 0.5 - 1.3 ml/100g</t>
+          <t>Fields of flowers, Dried Herbs, Parsley, Grain, Straw, Sunny hayfield</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr"/>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Saaz, Hallertauer Mittelfrueh</t>
+        </is>
+      </c>
       <c r="Z19" t="n">
         <v>60</v>
       </c>
@@ -14305,7 +14294,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Aroma</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -14315,12 +14304,32 @@
       </c>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 473000000, "_seconds": 1719746363}</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>natsgiFiBiltVb8LI7CaypwjHBmxN2</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 673000000, "_seconds": 1775807165}</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1775807165673</v>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>3.0.0</t>
+        </is>
+      </c>
+      <c r="AL19" t="n">
+        <v>50</v>
+      </c>
       <c r="AM19" t="inlineStr"/>
       <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="inlineStr"/>
@@ -14351,7 +14360,7 @@
         <v>5.6</v>
       </c>
       <c r="H20" t="n">
-        <v>13.1</v>
+        <v>13.3</v>
       </c>
       <c r="J20" t="n">
         <v>5.59</v>
@@ -14363,7 +14372,7 @@
         <v>30</v>
       </c>
       <c r="Q20" t="n">
-        <v>11.5</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -14386,7 +14395,7 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -14439,12 +14448,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JosUqRpyUkkCJKNHlRWL890UWQpSUa</t>
+          <t>MF5mu7sFjBzSnLUgseCxo38joSgz2l</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kolserig</t>
+          <t>London Pub Gen 1 Stout saved by Bond</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -14458,10 +14467,10 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="H21" t="n">
-        <v>13.3</v>
+        <v>35</v>
       </c>
       <c r="J21" t="n">
         <v>5.59</v>
@@ -14473,7 +14482,7 @@
         <v>30</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>28.2</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -14496,7 +14505,7 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -14522,24 +14531,24 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>natsgiFiBiltVb8LI7CaypwjHBmxN2</t>
+          <t>XCWEvYDmMFt4NFK6nyts7Bg9HJD3vR</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 673000000, "_seconds": 1775807165}</t>
+          <t>{"_nanoseconds": 473000000, "_seconds": 1719746363}</t>
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1775807165673</v>
+        <v>1719746363473</v>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="AL21" t="n">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="AM21" t="inlineStr"/>
       <c r="AN21" t="inlineStr"/>
@@ -14571,7 +14580,7 @@
         <v>4</v>
       </c>
       <c r="H22" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="J22" t="n">
         <v>5.59</v>
@@ -14583,7 +14592,7 @@
         <v>30</v>
       </c>
       <c r="Q22" t="n">
-        <v>28.2</v>
+        <v>2.7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -14606,7 +14615,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -14659,12 +14668,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MF5mu7sFjBzSnLUgseCxo38joSgz2l</t>
+          <t>MU06X8V9zEP11cbAQnGEm5fUIZajPn</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>London Pub Gen 1 Stout saved by Bond</t>
+          <t>Marigold Lager</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -14674,17 +14683,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>default-southernaroma</t>
+          <t>default-J80zzFn0TQEAwwaQuzMQsRYzrIvBOC</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="H23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J23" t="n">
-        <v>5.59</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="b">
         <v>0</v>
@@ -14693,30 +14702,26 @@
         <v>30</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.7</v>
+        <v>17.3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Southern Aroma</t>
+          <t>Hallertau Perle</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Fields of flowers, Dried Herbs, Parsley, Grain, Straw, Sunny hayfield</t>
+          <t>A dual-purpose hop that offers great bittering properties as well as a well-rounded aroma profile. Aroma: Herbal - tea, pepper, floral, citrus, earthy, woody, grassy, caramel Alpha Acid: 4.0 - 9.0% Beta Acid: 2.5 - 4.5% Total Oil: 0.5 - 1.3 ml/100g</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Saaz, Hallertauer Mittelfrueh</t>
-        </is>
-      </c>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
       <c r="Z23" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -14725,7 +14730,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Aroma</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -14735,32 +14740,12 @@
       </c>
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 473000000, "_seconds": 1719746363}</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>XCWEvYDmMFt4NFK6nyts7Bg9HJD3vR</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 473000000, "_seconds": 1719746363}</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1719746363473</v>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>2.10.6</t>
-        </is>
-      </c>
-      <c r="AL23" t="n">
-        <v>-50</v>
-      </c>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
       <c r="AM23" t="inlineStr"/>
       <c r="AN23" t="inlineStr"/>
       <c r="AO23" t="inlineStr"/>
@@ -14784,37 +14769,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>default-J80zzFn0TQEAwwaQuzMQsRYzrIvBOC</t>
+          <t>default-b73163ee</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="H24" t="n">
-        <v>15</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3.5</v>
+        <v>20</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
       </c>
-      <c r="O24" t="n">
-        <v>30</v>
-      </c>
       <c r="Q24" t="n">
-        <v>17.3</v>
+        <v>7.1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>Hallertau Perle</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>A dual-purpose hop that offers great bittering properties as well as a well-rounded aroma profile. Aroma: Herbal - tea, pepper, floral, citrus, earthy, woody, grassy, caramel Alpha Acid: 4.0 - 9.0% Beta Acid: 2.5 - 4.5% Total Oil: 0.5 - 1.3 ml/100g</t>
-        </is>
-      </c>
+          <t>Hallertauer Mittelfrueh</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
           <t>Germany</t>
@@ -14822,7 +14797,7 @@
       </c>
       <c r="X24" t="inlineStr"/>
       <c r="Z24" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -14831,7 +14806,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Aroma</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -14841,12 +14816,32 @@
       </c>
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 85000000, "_seconds": 1714216059}</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>w2Cnxu12CzkGzETWTD6jy1S8edXRv2</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 500000000, "_seconds": 1723974350}</t>
+        </is>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1723974350500</v>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
+      <c r="AL24" t="n">
+        <v>-100</v>
+      </c>
       <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="inlineStr"/>
@@ -14855,12 +14850,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MU06X8V9zEP11cbAQnGEm5fUIZajPn</t>
+          <t>NP8TWb4ne7Puem87SOkq3DrbZaJQHo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Marigold Lager</t>
+          <t>Stout</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -14870,27 +14865,37 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>default-b73163ee</t>
+          <t>default-J80zzFn0TQEAwwaQuzMQsRYzrIvBOC</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>6.3</v>
       </c>
       <c r="H25" t="n">
-        <v>20</v>
+        <v>30</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.5</v>
       </c>
       <c r="N25" t="b">
         <v>0</v>
       </c>
+      <c r="O25" t="n">
+        <v>30</v>
+      </c>
       <c r="Q25" t="n">
-        <v>7.1</v>
+        <v>30.5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>Hallertauer Mittelfrueh</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr"/>
+          <t>Hallertau Perle</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>A dual-purpose hop that offers great bittering properties as well as a well-rounded aroma profile. Aroma: Herbal - tea, pepper, floral, citrus, earthy, woody, grassy, caramel Alpha Acid: 4.0 - 9.0% Beta Acid: 2.5 - 4.5% Total Oil: 0.5 - 1.3 ml/100g</t>
+        </is>
+      </c>
       <c r="W25" t="inlineStr">
         <is>
           <t>Germany</t>
@@ -14898,7 +14903,7 @@
       </c>
       <c r="X25" t="inlineStr"/>
       <c r="Z25" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -14907,7 +14912,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Aroma</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -14917,31 +14922,34 @@
       </c>
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="n">
+        <v>2024</v>
+      </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 85000000, "_seconds": 1714216059}</t>
+          <t>{"_nanoseconds": 223000000, "_seconds": 1778682625}</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>w2Cnxu12CzkGzETWTD6jy1S8edXRv2</t>
+          <t>RUQnJfJFRnXph5sp3FJtmw89Hv1WVi</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 500000000, "_seconds": 1723974350}</t>
+          <t>{"_nanoseconds": 223000000, "_seconds": 1778682625}</t>
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1723974350500</v>
+        <v>1778682625223</v>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="AL25" t="n">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AM25" t="inlineStr"/>
       <c r="AN25" t="inlineStr"/>
@@ -14951,12 +14959,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NP8TWb4ne7Puem87SOkq3DrbZaJQHo</t>
+          <t>R2xTDLlZjcEYJ5R7Oik4G5urbLeHN6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Stout</t>
+          <t>Lager pseudo idea ii</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -14966,17 +14974,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>default-J80zzFn0TQEAwwaQuzMQsRYzrIvBOC</t>
+          <t>default-southernaroma</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="H26" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>3.5</v>
+        <v>5.59</v>
       </c>
       <c r="N26" t="b">
         <v>0</v>
@@ -14985,24 +14993,28 @@
         <v>30</v>
       </c>
       <c r="Q26" t="n">
-        <v>30.5</v>
+        <v>16.8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>Hallertau Perle</t>
+          <t>Southern Aroma</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>A dual-purpose hop that offers great bittering properties as well as a well-rounded aroma profile. Aroma: Herbal - tea, pepper, floral, citrus, earthy, woody, grassy, caramel Alpha Acid: 4.0 - 9.0% Beta Acid: 2.5 - 4.5% Total Oil: 0.5 - 1.3 ml/100g</t>
+          <t>Fields of flowers, Dried Herbs, Parsley, Grain, Straw, Sunny hayfield</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr"/>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Saaz, Hallertauer Mittelfrueh</t>
+        </is>
+      </c>
       <c r="Z26" t="n">
         <v>60</v>
       </c>
@@ -15013,7 +15025,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Aroma</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -15023,34 +15035,31 @@
       </c>
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="n">
-        <v>2024</v>
-      </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 223000000, "_seconds": 1778682625}</t>
+          <t>{"_nanoseconds": 473000000, "_seconds": 1719746363}</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>RUQnJfJFRnXph5sp3FJtmw89Hv1WVi</t>
+          <t>XCWEvYDmMFt4NFK6nyts7Bg9HJD3vR</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 223000000, "_seconds": 1778682625}</t>
+          <t>{"_nanoseconds": 473000000, "_seconds": 1719746363}</t>
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1778682625223</v>
+        <v>1719746363473</v>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="AL26" t="n">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr"/>
@@ -15082,7 +15091,7 @@
         <v>5.6</v>
       </c>
       <c r="H27" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
         <v>5.59</v>
@@ -15094,7 +15103,7 @@
         <v>30</v>
       </c>
       <c r="Q27" t="n">
-        <v>16.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -15117,7 +15126,7 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
@@ -15192,7 +15201,7 @@
         <v>5.6</v>
       </c>
       <c r="H28" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J28" t="n">
         <v>5.59</v>
@@ -15204,7 +15213,7 @@
         <v>30</v>
       </c>
       <c r="Q28" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -15227,7 +15236,7 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
@@ -15280,12 +15289,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>R2xTDLlZjcEYJ5R7Oik4G5urbLeHN6</t>
+          <t>RxtDAxv74eS2hKCxjIaWPwTWx4sYVF</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lager pseudo idea ii</t>
+          <t>First Lager v3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -15295,49 +15304,35 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>default-southernaroma</t>
+          <t>default-b73163ee</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="H29" t="n">
-        <v>30</v>
-      </c>
-      <c r="J29" t="n">
-        <v>5.59</v>
+        <v>20</v>
       </c>
       <c r="N29" t="b">
         <v>0</v>
       </c>
-      <c r="O29" t="n">
-        <v>30</v>
-      </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>Southern Aroma</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Fields of flowers, Dried Herbs, Parsley, Grain, Straw, Sunny hayfield</t>
-        </is>
-      </c>
+          <t>Hallertauer Mittelfrueh</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>Saaz, Hallertauer Mittelfrueh</t>
-        </is>
-      </c>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -15358,21 +15353,21 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 473000000, "_seconds": 1719746363}</t>
+          <t>{"_nanoseconds": 85000000, "_seconds": 1714216059}</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>XCWEvYDmMFt4NFK6nyts7Bg9HJD3vR</t>
+          <t>w2Cnxu12CzkGzETWTD6jy1S8edXRv2</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 473000000, "_seconds": 1719746363}</t>
+          <t>{"_nanoseconds": 500000000, "_seconds": 1723974350}</t>
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1719746363473</v>
+        <v>1723974350500</v>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
@@ -15380,7 +15375,7 @@
         </is>
       </c>
       <c r="AL29" t="n">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="AM29" t="inlineStr"/>
       <c r="AN29" t="inlineStr"/>
@@ -15412,13 +15407,13 @@
         <v>3.2</v>
       </c>
       <c r="H30" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N30" t="b">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>13.2</v>
+        <v>6.7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -15433,7 +15428,7 @@
       </c>
       <c r="X30" t="inlineStr"/>
       <c r="Z30" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -15486,12 +15481,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RxtDAxv74eS2hKCxjIaWPwTWx4sYVF</t>
+          <t>YOwmEZx99K2SoQK0VbXkyCchdmIrZZ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>First Lager v3</t>
+          <t>London Pub gen 2 Weskus</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -15501,33 +15496,47 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>default-b73163ee</t>
+          <t>default-southerndawn</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3.2</v>
+        <v>11.7</v>
       </c>
       <c r="H31" t="n">
-        <v>30</v>
+        <v>15</v>
+      </c>
+      <c r="J31" t="n">
+        <v>5.1</v>
       </c>
       <c r="N31" t="b">
         <v>0</v>
       </c>
+      <c r="O31" t="n">
+        <v>15</v>
+      </c>
       <c r="Q31" t="n">
-        <v>6.7</v>
+        <v>13.8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>Hallertauer Mittelfrueh</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr"/>
+          <t>Southern Dawn</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Resembles Southern Promise but with a different aroma profile. Has a fruity, spicy aroma and is relatively neutral when bittering.</t>
+        </is>
+      </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr"/>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Nugget, Magnum</t>
+        </is>
+      </c>
       <c r="Z31" t="n">
         <v>10</v>
       </c>
@@ -15538,7 +15547,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Aroma</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -15550,21 +15559,21 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 85000000, "_seconds": 1714216059}</t>
+          <t>{"_nanoseconds": 795000000, "_seconds": 1697269074}</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>w2Cnxu12CzkGzETWTD6jy1S8edXRv2</t>
+          <t>6d29uGYQ3NPbK3eq6cqpiOctCm0yxG</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 500000000, "_seconds": 1723974350}</t>
+          <t>{"_nanoseconds": 911000000, "_seconds": 1721546982}</t>
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1723974350500</v>
+        <v>1721546982911</v>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
@@ -15572,10 +15581,9 @@
         </is>
       </c>
       <c r="AL31" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="inlineStr"/>
-      <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="inlineStr"/>
     </row>
@@ -15597,17 +15605,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>default-southerndawn</t>
+          <t>default-africanqueen</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>11.7</v>
+        <v>13</v>
       </c>
       <c r="H32" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J32" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="N32" t="b">
         <v>0</v>
@@ -15616,30 +15624,26 @@
         <v>15</v>
       </c>
       <c r="Q32" t="n">
-        <v>13.8</v>
+        <v>4.9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>Southern Dawn</t>
+          <t>African Queen</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>Resembles Southern Promise but with a different aroma profile. Has a fruity, spicy aroma and is relatively neutral when bittering.</t>
+          <t>A high alpha hop from South Africa with interesting bittering potential and fruity flavors. Fruity aroma includes hints of blueberry, cassis, passion fruit, citrus, stone fruit, black currant, tea, lemongrass and even chili. Can be used both for bittering and as a late addition.</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>Nugget, Magnum</t>
-        </is>
-      </c>
+          <t>South African</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
       <c r="Z32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -15660,31 +15664,32 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 795000000, "_seconds": 1697269074}</t>
+          <t>{"_nanoseconds": 311000000, "_seconds": 1699176795}</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>6d29uGYQ3NPbK3eq6cqpiOctCm0yxG</t>
+          <t>R8Z015agfqmYiPfmcje6KveBCZZtwb</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 911000000, "_seconds": 1721546982}</t>
+          <t>{"_nanoseconds": 806000000, "_seconds": 1726505806}</t>
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1721546982911</v>
+        <v>1726505806806</v>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>2.11.2</t>
         </is>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>-95</v>
       </c>
       <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
       <c r="AO32" t="inlineStr"/>
       <c r="AP32" t="inlineStr"/>
     </row>
@@ -15706,17 +15711,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>default-africanqueen</t>
+          <t>default-southerndawn</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>13</v>
+        <v>11.7</v>
       </c>
       <c r="H33" t="n">
         <v>7</v>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="N33" t="b">
         <v>0</v>
@@ -15725,24 +15730,28 @@
         <v>15</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>African Queen</t>
+          <t>Southern Dawn</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>A high alpha hop from South Africa with interesting bittering potential and fruity flavors. Fruity aroma includes hints of blueberry, cassis, passion fruit, citrus, stone fruit, black currant, tea, lemongrass and even chili. Can be used both for bittering and as a late addition.</t>
+          <t>Resembles Southern Promise but with a different aroma profile. Has a fruity, spicy aroma and is relatively neutral when bittering.</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>South African</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr"/>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Nugget, Magnum</t>
+        </is>
+      </c>
       <c r="Z33" t="n">
         <v>5</v>
       </c>
@@ -15765,29 +15774,29 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 311000000, "_seconds": 1699176795}</t>
+          <t>{"_nanoseconds": 795000000, "_seconds": 1697269074}</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>R8Z015agfqmYiPfmcje6KveBCZZtwb</t>
+          <t>6d29uGYQ3NPbK3eq6cqpiOctCm0yxG</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 806000000, "_seconds": 1726505806}</t>
+          <t>{"_nanoseconds": 911000000, "_seconds": 1721546982}</t>
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1726505806806</v>
+        <v>1721546982911</v>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>2.11.2</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="AL33" t="n">
-        <v>-95</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="inlineStr"/>
       <c r="AN33" t="inlineStr"/>
@@ -15819,7 +15828,7 @@
         <v>11.7</v>
       </c>
       <c r="H34" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="J34" t="n">
         <v>5.1</v>
@@ -15831,7 +15840,7 @@
         <v>15</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.4</v>
+        <v>6.3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -15853,8 +15862,11 @@
           <t>Nugget, Magnum</t>
         </is>
       </c>
+      <c r="Y34" t="n">
+        <v>82</v>
+      </c>
       <c r="Z34" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
@@ -15868,7 +15880,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Boil</t>
+          <t>Aroma</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr"/>
@@ -15900,8 +15912,9 @@
         <v>0</v>
       </c>
       <c r="AM34" t="inlineStr"/>
-      <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="inlineStr"/>
+      <c r="AO34" t="n">
+        <v>4</v>
+      </c>
       <c r="AP34" t="inlineStr"/>
     </row>
     <row r="35">
@@ -15922,17 +15935,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>default-southerndawn</t>
+          <t>default-africanqueen</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>11.7</v>
+        <v>13</v>
       </c>
       <c r="H35" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J35" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="N35" t="b">
         <v>0</v>
@@ -15941,28 +15954,24 @@
         <v>15</v>
       </c>
       <c r="Q35" t="n">
-        <v>6.3</v>
+        <v>4.2</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>Southern Dawn</t>
+          <t>African Queen</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>Resembles Southern Promise but with a different aroma profile. Has a fruity, spicy aroma and is relatively neutral when bittering.</t>
+          <t>A high alpha hop from South Africa with interesting bittering potential and fruity flavors. Fruity aroma includes hints of blueberry, cassis, passion fruit, citrus, stone fruit, black currant, tea, lemongrass and even chili. Can be used both for bittering and as a late addition.</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>Nugget, Magnum</t>
-        </is>
-      </c>
+          <t>South African</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr"/>
       <c r="Y35" t="n">
         <v>82</v>
       </c>
@@ -15988,29 +15997,29 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 795000000, "_seconds": 1697269074}</t>
+          <t>{"_nanoseconds": 311000000, "_seconds": 1699176795}</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>6d29uGYQ3NPbK3eq6cqpiOctCm0yxG</t>
+          <t>R8Z015agfqmYiPfmcje6KveBCZZtwb</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 911000000, "_seconds": 1721546982}</t>
+          <t>{"_nanoseconds": 806000000, "_seconds": 1726505806}</t>
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1721546982911</v>
+        <v>1726505806806</v>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>2.11.2</t>
         </is>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>-95</v>
       </c>
       <c r="AM35" t="inlineStr"/>
       <c r="AO35" t="n">
@@ -16021,12 +16030,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>YOwmEZx99K2SoQK0VbXkyCchdmIrZZ</t>
+          <t>dsVqWqNVboCzKtRIVDlw4lsZ3qshOR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>London Pub gen 2 Weskus</t>
+          <t>Helles bock</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -16036,48 +16045,45 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>default-africanqueen</t>
+          <t>default-J80zzFn0TQEAwwaQuzMQsRYzrIvBOC</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>13</v>
+        <v>6.5</v>
       </c>
       <c r="H36" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="b">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.2</v>
+        <v>20.4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>African Queen</t>
+          <t>Hallertau Perle</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>A high alpha hop from South Africa with interesting bittering potential and fruity flavors. Fruity aroma includes hints of blueberry, cassis, passion fruit, citrus, stone fruit, black currant, tea, lemongrass and even chili. Can be used both for bittering and as a late addition.</t>
+          <t>A dual-purpose hop that offers great bittering properties as well as a well-rounded aroma profile. Aroma: Herbal - tea, pepper, floral, citrus, earthy, woody, grassy, caramel Alpha Acid: 4.0 - 9.0% Beta Acid: 2.5 - 4.5% Total Oil: 0.5 - 1.3 ml/100g</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>South African</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="n">
-        <v>82</v>
-      </c>
       <c r="Z36" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
@@ -16091,41 +16097,20 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Aroma</t>
+          <t>Boil</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="inlineStr"/>
-      <c r="AG36" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 311000000, "_seconds": 1699176795}</t>
-        </is>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>R8Z015agfqmYiPfmcje6KveBCZZtwb</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 806000000, "_seconds": 1726505806}</t>
-        </is>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1726505806806</v>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>2.11.2</t>
-        </is>
-      </c>
-      <c r="AL36" t="n">
-        <v>-95</v>
-      </c>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
       <c r="AM36" t="inlineStr"/>
-      <c r="AO36" t="n">
-        <v>4</v>
-      </c>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
       <c r="AP36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -16146,17 +16131,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>default-J80zzFn0TQEAwwaQuzMQsRYzrIvBOC</t>
+          <t>default-southernaroma</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="H37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>3.5</v>
+        <v>5.59</v>
       </c>
       <c r="N37" t="b">
         <v>0</v>
@@ -16165,26 +16150,30 @@
         <v>30</v>
       </c>
       <c r="Q37" t="n">
-        <v>20.4</v>
+        <v>6.8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>Hallertau Perle</t>
+          <t>Southern Aroma</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>A dual-purpose hop that offers great bittering properties as well as a well-rounded aroma profile. Aroma: Herbal - tea, pepper, floral, citrus, earthy, woody, grassy, caramel Alpha Acid: 4.0 - 9.0% Beta Acid: 2.5 - 4.5% Total Oil: 0.5 - 1.3 ml/100g</t>
+          <t>Fields of flowers, Dried Herbs, Parsley, Grain, Straw, Sunny hayfield</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr"/>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Saaz, Hallertauer Mittelfrueh</t>
+        </is>
+      </c>
       <c r="Z37" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
@@ -16193,7 +16182,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Aroma</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -16203,12 +16192,32 @@
       </c>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr"/>
-      <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="inlineStr"/>
-      <c r="AJ37" t="inlineStr"/>
-      <c r="AK37" t="inlineStr"/>
-      <c r="AL37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 473000000, "_seconds": 1719746363}</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>XCWEvYDmMFt4NFK6nyts7Bg9HJD3vR</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 473000000, "_seconds": 1719746363}</t>
+        </is>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1719746363473</v>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
+      <c r="AL37" t="n">
+        <v>-50</v>
+      </c>
       <c r="AM37" t="inlineStr"/>
       <c r="AN37" t="inlineStr"/>
       <c r="AO37" t="inlineStr"/>
@@ -16232,49 +16241,35 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>default-southernaroma</t>
+          <t>default-b73163ee</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="H38" t="n">
+        <v>20</v>
+      </c>
+      <c r="N38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Hallertauer Mittelfrueh</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr"/>
+      <c r="Z38" t="n">
         <v>10</v>
-      </c>
-      <c r="J38" t="n">
-        <v>5.59</v>
-      </c>
-      <c r="N38" t="b">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Southern Aroma</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Fields of flowers, Dried Herbs, Parsley, Grain, Straw, Sunny hayfield</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>Saaz, Hallertauer Mittelfrueh</t>
-        </is>
-      </c>
-      <c r="Z38" t="n">
-        <v>30</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -16295,21 +16290,21 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 473000000, "_seconds": 1719746363}</t>
+          <t>{"_nanoseconds": 85000000, "_seconds": 1714216059}</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>XCWEvYDmMFt4NFK6nyts7Bg9HJD3vR</t>
+          <t>w2Cnxu12CzkGzETWTD6jy1S8edXRv2</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 473000000, "_seconds": 1719746363}</t>
+          <t>{"_nanoseconds": 500000000, "_seconds": 1723974350}</t>
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1719746363473</v>
+        <v>1723974350500</v>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
@@ -16317,7 +16312,7 @@
         </is>
       </c>
       <c r="AL38" t="n">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="AM38" t="inlineStr"/>
       <c r="AN38" t="inlineStr"/>
@@ -16327,12 +16322,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dsVqWqNVboCzKtRIVDlw4lsZ3qshOR</t>
+          <t>hJRSice4Rnaj5KIs2qxSpXYeU2IT2b</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Helles bock</t>
+          <t>Black bit</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -16349,13 +16344,13 @@
         <v>4</v>
       </c>
       <c r="H39" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N39" t="b">
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.5</v>
+        <v>19.8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -16370,7 +16365,7 @@
       </c>
       <c r="X39" t="inlineStr"/>
       <c r="Z39" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -16438,46 +16433,68 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>default-b73163ee</t>
+          <t>default-NrD3kYzu8ONSucGjXgHxRcgSUwk2aK</t>
         </is>
       </c>
       <c r="G40" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" t="n">
+        <v>20</v>
+      </c>
+      <c r="J40" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="K40" t="n">
+        <v>11</v>
+      </c>
+      <c r="L40" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M40" t="n">
+        <v>17</v>
+      </c>
+      <c r="N40" t="b">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q40" t="n">
         <v>4</v>
       </c>
-      <c r="H40" t="n">
-        <v>25</v>
-      </c>
-      <c r="N40" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>19.8</v>
+      <c r="S40" t="n">
+        <v>33</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>Hallertauer Mittelfrueh</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr"/>
+          <t>Saaz</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Saaz is the famous aroma landrace variety originating in the Czech area of the same name. It has very mild, pleasant noble hoppy notes perfectly suited for and defines the Czech-style pilsner beers.
+Pedigree Czech landrace variety Aroma Classic noble aroma hop with long and strong tradition associated with classic pilsner beer.</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>0.7</v>
+      </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="X40" t="inlineStr"/>
       <c r="Z40" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>Pellet</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>Aroma</t>
-        </is>
-      </c>
+      <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr">
         <is>
           <t>Boil</t>
@@ -16485,32 +16502,12 @@
       </c>
       <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="inlineStr"/>
-      <c r="AG40" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 85000000, "_seconds": 1714216059}</t>
-        </is>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>w2Cnxu12CzkGzETWTD6jy1S8edXRv2</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 500000000, "_seconds": 1723974350}</t>
-        </is>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1723974350500</v>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>2.10.6</t>
-        </is>
-      </c>
-      <c r="AL40" t="n">
-        <v>-100</v>
-      </c>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
       <c r="AM40" t="inlineStr"/>
       <c r="AN40" t="inlineStr"/>
       <c r="AO40" t="inlineStr"/>
@@ -16534,56 +16531,30 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>default-NrD3kYzu8ONSucGjXgHxRcgSUwk2aK</t>
+          <t>default-b73163ee</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H41" t="n">
-        <v>20</v>
-      </c>
-      <c r="J41" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="K41" t="n">
-        <v>11</v>
-      </c>
-      <c r="L41" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="M41" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N41" t="b">
         <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>20</v>
       </c>
       <c r="Q41" t="n">
         <v>4</v>
       </c>
-      <c r="S41" t="n">
-        <v>33</v>
-      </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>Saaz</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Saaz is the famous aroma landrace variety originating in the Czech area of the same name. It has very mild, pleasant noble hoppy notes perfectly suited for and defines the Czech-style pilsner beers.
-Pedigree Czech landrace variety Aroma Classic noble aroma hop with long and strong tradition associated with classic pilsner beer.</t>
-        </is>
-      </c>
-      <c r="V41" t="n">
-        <v>0.7</v>
-      </c>
+          <t>Hallertauer Mittelfrueh</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="X41" t="inlineStr"/>
@@ -16595,7 +16566,11 @@
           <t>Pellet</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>Aroma</t>
+        </is>
+      </c>
       <c r="AC41" t="inlineStr">
         <is>
           <t>Boil</t>
@@ -16603,12 +16578,32 @@
       </c>
       <c r="AD41" t="inlineStr"/>
       <c r="AE41" t="inlineStr"/>
-      <c r="AG41" t="inlineStr"/>
-      <c r="AH41" t="inlineStr"/>
-      <c r="AI41" t="inlineStr"/>
-      <c r="AJ41" t="inlineStr"/>
-      <c r="AK41" t="inlineStr"/>
-      <c r="AL41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 85000000, "_seconds": 1714216059}</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>w2Cnxu12CzkGzETWTD6jy1S8edXRv2</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 500000000, "_seconds": 1723974350}</t>
+        </is>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1723974350500</v>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
+      <c r="AL41" t="n">
+        <v>-100</v>
+      </c>
       <c r="AM41" t="inlineStr"/>
       <c r="AN41" t="inlineStr"/>
       <c r="AO41" t="inlineStr"/>
@@ -16639,13 +16634,13 @@
         <v>4</v>
       </c>
       <c r="H42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N42" t="b">
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -16660,7 +16655,7 @@
       </c>
       <c r="X42" t="inlineStr"/>
       <c r="Z42" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -16706,19 +16701,18 @@
         <v>-100</v>
       </c>
       <c r="AM42" t="inlineStr"/>
-      <c r="AN42" t="inlineStr"/>
       <c r="AO42" t="inlineStr"/>
       <c r="AP42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>hJRSice4Rnaj5KIs2qxSpXYeU2IT2b</t>
+          <t>hV82vumYBf6BRTmLMntedEkZ1kk2pf</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Black bit</t>
+          <t>Swart bier 2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -16728,27 +16722,37 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>default-b73163ee</t>
+          <t>default-J80zzFn0TQEAwwaQuzMQsRYzrIvBOC</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>4</v>
+        <v>6.3</v>
       </c>
       <c r="H43" t="n">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="J43" t="n">
+        <v>3.5</v>
       </c>
       <c r="N43" t="b">
         <v>0</v>
       </c>
+      <c r="O43" t="n">
+        <v>30</v>
+      </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>21.9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>Hallertauer Mittelfrueh</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr"/>
+          <t>Hallertau Perle</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>A dual-purpose hop that offers great bittering properties as well as a well-rounded aroma profile. Aroma: Herbal - tea, pepper, floral, citrus, earthy, woody, grassy, caramel Alpha Acid: 4.0 - 9.0% Beta Acid: 2.5 - 4.5% Total Oil: 0.5 - 1.3 ml/100g</t>
+        </is>
+      </c>
       <c r="W43" t="inlineStr">
         <is>
           <t>Germany</t>
@@ -16756,7 +16760,7 @@
       </c>
       <c r="X43" t="inlineStr"/>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -16765,7 +16769,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Aroma</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -16775,33 +16779,37 @@
       </c>
       <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="n">
+        <v>2024</v>
+      </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 85000000, "_seconds": 1714216059}</t>
+          <t>{"_nanoseconds": 223000000, "_seconds": 1778682625}</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>w2Cnxu12CzkGzETWTD6jy1S8edXRv2</t>
+          <t>t2odApSsIG0sLTEIBBiGzwdpFCABDk</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 500000000, "_seconds": 1723974350}</t>
+          <t>{"_nanoseconds": 381000000, "_seconds": 1785061184}</t>
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1723974350500</v>
+        <v>1785061184381</v>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="AL43" t="n">
-        <v>-100</v>
+        <v>156</v>
       </c>
       <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr"/>
       <c r="AO43" t="inlineStr"/>
       <c r="AP43" t="inlineStr"/>
     </row>
@@ -16823,37 +16831,27 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>default-J80zzFn0TQEAwwaQuzMQsRYzrIvBOC</t>
+          <t>default-b73163ee</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>6.3</v>
+        <v>3.2</v>
       </c>
       <c r="H44" t="n">
-        <v>20</v>
-      </c>
-      <c r="J44" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="N44" t="b">
         <v>0</v>
       </c>
-      <c r="O44" t="n">
-        <v>30</v>
-      </c>
       <c r="Q44" t="n">
-        <v>21.9</v>
+        <v>2.5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>Hallertau Perle</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>A dual-purpose hop that offers great bittering properties as well as a well-rounded aroma profile. Aroma: Herbal - tea, pepper, floral, citrus, earthy, woody, grassy, caramel Alpha Acid: 4.0 - 9.0% Beta Acid: 2.5 - 4.5% Total Oil: 0.5 - 1.3 ml/100g</t>
-        </is>
-      </c>
+          <t>Hallertauer Mittelfrueh</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
           <t>Germany</t>
@@ -16861,7 +16859,7 @@
       </c>
       <c r="X44" t="inlineStr"/>
       <c r="Z44" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -16870,7 +16868,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Aroma</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -16880,26 +16878,23 @@
       </c>
       <c r="AD44" t="inlineStr"/>
       <c r="AE44" t="inlineStr"/>
-      <c r="AF44" t="n">
-        <v>2024</v>
-      </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 223000000, "_seconds": 1778682625}</t>
+          <t>{"_nanoseconds": 85000000, "_seconds": 1714216059}</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>t2odApSsIG0sLTEIBBiGzwdpFCABDk</t>
+          <t>NN4PCqpf5oxhJkuWbopSaKCIPRhVk7</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 381000000, "_seconds": 1785061184}</t>
+          <t>{"_nanoseconds": 749000000, "_seconds": 1781070162}</t>
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1785061184381</v>
+        <v>1781070162749</v>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
@@ -16907,10 +16902,11 @@
         </is>
       </c>
       <c r="AL44" t="n">
-        <v>156</v>
-      </c>
-      <c r="AM44" t="inlineStr"/>
-      <c r="AN44" t="inlineStr"/>
+        <v>105</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>45</v>
+      </c>
       <c r="AO44" t="inlineStr"/>
       <c r="AP44" t="inlineStr"/>
     </row>
@@ -16939,13 +16935,13 @@
         <v>3.2</v>
       </c>
       <c r="H45" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="N45" t="b">
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -16959,8 +16955,11 @@
         </is>
       </c>
       <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="n">
+        <v>80</v>
+      </c>
       <c r="Z45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -16974,7 +16973,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Boil</t>
+          <t>Aroma</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr"/>
@@ -16986,40 +16985,38 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>NN4PCqpf5oxhJkuWbopSaKCIPRhVk7</t>
+          <t>w2Cnxu12CzkGzETWTD6jy1S8edXRv2</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 749000000, "_seconds": 1781070162}</t>
+          <t>{"_nanoseconds": 500000000, "_seconds": 1723974350}</t>
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1781070162749</v>
+        <v>1723974350500</v>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="AL45" t="n">
-        <v>105</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>45</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="AM45" t="inlineStr"/>
       <c r="AO45" t="inlineStr"/>
       <c r="AP45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>hV82vumYBf6BRTmLMntedEkZ1kk2pf</t>
+          <t>jldJvRrDCbjNcw34IPbmz9kKbfWoew</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Swart bier 2026</t>
+          <t>Karoo Ale</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -17029,38 +17026,45 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>default-b73163ee</t>
+          <t>default-J80zzFn0TQEAwwaQuzMQsRYzrIvBOC</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>3.2</v>
+        <v>6.3</v>
       </c>
       <c r="H46" t="n">
+        <v>12</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N46" t="b">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
         <v>30</v>
       </c>
-      <c r="N46" t="b">
-        <v>0</v>
-      </c>
       <c r="Q46" t="n">
-        <v>2.1</v>
+        <v>12.8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>Hallertauer Mittelfrueh</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr"/>
+          <t>Hallertau Perle</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>A dual-purpose hop that offers great bittering properties as well as a well-rounded aroma profile. Aroma: Herbal - tea, pepper, floral, citrus, earthy, woody, grassy, caramel Alpha Acid: 4.0 - 9.0% Beta Acid: 2.5 - 4.5% Total Oil: 0.5 - 1.3 ml/100g</t>
+        </is>
+      </c>
       <c r="W46" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
       <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="n">
-        <v>80</v>
-      </c>
       <c r="Z46" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -17069,43 +17073,47 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Aroma</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Aroma</t>
+          <t>Boil</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="n">
+        <v>2024</v>
+      </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 85000000, "_seconds": 1714216059}</t>
+          <t>{"_nanoseconds": 223000000, "_seconds": 1778682625}</t>
         </is>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>w2Cnxu12CzkGzETWTD6jy1S8edXRv2</t>
+          <t>7XQ2gOtWELwAzHhtmwIarzOqsdzdzE</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 500000000, "_seconds": 1723974350}</t>
+          <t>{"_nanoseconds": 684000000, "_seconds": 1781339595}</t>
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1723974350500</v>
+        <v>1781339595684</v>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="AL46" t="n">
-        <v>-100</v>
+        <v>170</v>
       </c>
       <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr"/>
       <c r="AO46" t="inlineStr"/>
       <c r="AP46" t="inlineStr"/>
     </row>
@@ -17127,45 +17135,33 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>default-J80zzFn0TQEAwwaQuzMQsRYzrIvBOC</t>
+          <t>default-58d2b845</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="H47" t="n">
-        <v>12</v>
-      </c>
-      <c r="J47" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N47" t="b">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>30</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="Q47" t="n">
-        <v>12.8</v>
+        <v>3.9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>Hallertau Perle</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>A dual-purpose hop that offers great bittering properties as well as a well-rounded aroma profile. Aroma: Herbal - tea, pepper, floral, citrus, earthy, woody, grassy, caramel Alpha Acid: 4.0 - 9.0% Beta Acid: 2.5 - 4.5% Total Oil: 0.5 - 1.3 ml/100g</t>
-        </is>
-      </c>
+          <t>Cascade</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>US</t>
         </is>
       </c>
       <c r="X47" t="inlineStr"/>
       <c r="Z47" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -17184,35 +17180,12 @@
       </c>
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="inlineStr"/>
-      <c r="AF47" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AG47" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 223000000, "_seconds": 1778682625}</t>
-        </is>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>7XQ2gOtWELwAzHhtmwIarzOqsdzdzE</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 684000000, "_seconds": 1781339595}</t>
-        </is>
-      </c>
-      <c r="AJ47" t="n">
-        <v>1781339595684</v>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
-      <c r="AL47" t="n">
-        <v>170</v>
-      </c>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
       <c r="AM47" t="inlineStr"/>
       <c r="AN47" t="inlineStr"/>
       <c r="AO47" t="inlineStr"/>
@@ -17236,33 +17209,45 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>default-58d2b845</t>
+          <t>default-J80zzFn0TQEAwwaQuzMQsRYzrIvBOC</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="H48" t="n">
-        <v>15</v>
-      </c>
-      <c r="N48" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="J48" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N48" t="b">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>30</v>
+      </c>
       <c r="Q48" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>Cascade</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr"/>
+          <t>Hallertau Perle</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>A dual-purpose hop that offers great bittering properties as well as a well-rounded aroma profile. Aroma: Herbal - tea, pepper, floral, citrus, earthy, woody, grassy, caramel Alpha Acid: 4.0 - 9.0% Beta Acid: 2.5 - 4.5% Total Oil: 0.5 - 1.3 ml/100g</t>
+        </is>
+      </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="X48" t="inlineStr"/>
       <c r="Z48" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -17281,12 +17266,35 @@
       </c>
       <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="inlineStr"/>
-      <c r="AG48" t="inlineStr"/>
-      <c r="AH48" t="inlineStr"/>
-      <c r="AI48" t="inlineStr"/>
-      <c r="AJ48" t="inlineStr"/>
-      <c r="AK48" t="inlineStr"/>
-      <c r="AL48" t="inlineStr"/>
+      <c r="AF48" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 223000000, "_seconds": 1778682625}</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>7XQ2gOtWELwAzHhtmwIarzOqsdzdzE</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 684000000, "_seconds": 1781339595}</t>
+        </is>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1781339595684</v>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="AL48" t="n">
+        <v>170</v>
+      </c>
       <c r="AM48" t="inlineStr"/>
       <c r="AN48" t="inlineStr"/>
       <c r="AO48" t="inlineStr"/>
@@ -17310,40 +17318,30 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>default-J80zzFn0TQEAwwaQuzMQsRYzrIvBOC</t>
+          <t>default-bc4774ae</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>6.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>20</v>
-      </c>
-      <c r="J49" t="n">
-        <v>3.5</v>
+        <v>15</v>
       </c>
       <c r="N49" t="b">
         <v>0</v>
       </c>
-      <c r="O49" t="n">
-        <v>30</v>
-      </c>
       <c r="Q49" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>Hallertau Perle</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>A dual-purpose hop that offers great bittering properties as well as a well-rounded aroma profile. Aroma: Herbal - tea, pepper, floral, citrus, earthy, woody, grassy, caramel Alpha Acid: 4.0 - 9.0% Beta Acid: 2.5 - 4.5% Total Oil: 0.5 - 1.3 ml/100g</t>
-        </is>
-      </c>
+          <t>Centennial</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>US</t>
         </is>
       </c>
       <c r="X49" t="inlineStr"/>
@@ -17357,7 +17355,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Bittering</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -17372,21 +17370,21 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 223000000, "_seconds": 1778682625}</t>
+          <t>{"_nanoseconds": 997000000, "_seconds": 1778682602}</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>7XQ2gOtWELwAzHhtmwIarzOqsdzdzE</t>
+          <t>9bqwUroEuTMyoDsSRi5oKcTe8mF0gx</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 684000000, "_seconds": 1781339595}</t>
+          <t>{"_nanoseconds": 138000000, "_seconds": 1778997167}</t>
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1781339595684</v>
+        <v>1778997167138</v>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
@@ -17394,7 +17392,7 @@
         </is>
       </c>
       <c r="AL49" t="n">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="AM49" t="inlineStr"/>
       <c r="AN49" t="inlineStr"/>
@@ -17419,24 +17417,22 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>default-bc4774ae</t>
+          <t>default-58d2b845</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>8.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="H50" t="n">
-        <v>15</v>
-      </c>
-      <c r="N50" t="b">
-        <v>0</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="Q50" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>Centennial</t>
+          <t>Cascade</t>
         </is>
       </c>
       <c r="U50" t="inlineStr"/>
@@ -17456,7 +17452,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Bittering</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -17466,35 +17462,12 @@
       </c>
       <c r="AD50" t="inlineStr"/>
       <c r="AE50" t="inlineStr"/>
-      <c r="AF50" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AG50" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 997000000, "_seconds": 1778682602}</t>
-        </is>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>9bqwUroEuTMyoDsSRi5oKcTe8mF0gx</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 138000000, "_seconds": 1778997167}</t>
-        </is>
-      </c>
-      <c r="AJ50" t="n">
-        <v>1778997167138</v>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
-      <c r="AL50" t="n">
-        <v>65</v>
-      </c>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
       <c r="AM50" t="inlineStr"/>
       <c r="AN50" t="inlineStr"/>
       <c r="AO50" t="inlineStr"/>
@@ -17525,11 +17498,11 @@
         <v>5.5</v>
       </c>
       <c r="H51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="Q51" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -17543,8 +17516,11 @@
         </is>
       </c>
       <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="n">
+        <v>76</v>
+      </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -17558,7 +17534,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Boil</t>
+          <t>Aroma</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr"/>
@@ -17570,7 +17546,6 @@
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="inlineStr"/>
       <c r="AM51" t="inlineStr"/>
-      <c r="AN51" t="inlineStr"/>
       <c r="AO51" t="inlineStr"/>
       <c r="AP51" t="inlineStr"/>
     </row>
@@ -17592,22 +17567,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>default-58d2b845</t>
+          <t>default-bc4774ae</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="H52" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="Q52" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>Cascade</t>
+          <t>Centennial</t>
         </is>
       </c>
       <c r="U52" t="inlineStr"/>
@@ -17630,7 +17605,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Bittering</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -17653,12 +17628,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>jldJvRrDCbjNcw34IPbmz9kKbfWoew</t>
+          <t>yiPSN3Y6mmATMzlZ26e4uWlmbGRxaD</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Karoo Ale</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -17668,36 +17643,45 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>default-bc4774ae</t>
+          <t>default-J80zzFn0TQEAwwaQuzMQsRYzrIvBOC</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>10</v>
+        <v>6.3</v>
       </c>
       <c r="H53" t="n">
-        <v>15</v>
-      </c>
-      <c r="N53" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="J53" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N53" t="b">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>30</v>
+      </c>
       <c r="Q53" t="n">
-        <v>2.4</v>
+        <v>15.3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>Centennial</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr"/>
+          <t>Hallertau Perle</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>A dual-purpose hop that offers great bittering properties as well as a well-rounded aroma profile. Aroma: Herbal - tea, pepper, floral, citrus, earthy, woody, grassy, caramel Alpha Acid: 4.0 - 9.0% Beta Acid: 2.5 - 4.5% Total Oil: 0.5 - 1.3 ml/100g</t>
+        </is>
+      </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="n">
-        <v>76</v>
-      </c>
       <c r="Z53" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
@@ -17706,23 +17690,47 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Bittering</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Aroma</t>
+          <t>Boil</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr"/>
       <c r="AE53" t="inlineStr"/>
-      <c r="AG53" t="inlineStr"/>
-      <c r="AH53" t="inlineStr"/>
-      <c r="AI53" t="inlineStr"/>
-      <c r="AJ53" t="inlineStr"/>
-      <c r="AK53" t="inlineStr"/>
-      <c r="AL53" t="inlineStr"/>
+      <c r="AF53" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 223000000, "_seconds": 1778682625}</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>7XQ2gOtWELwAzHhtmwIarzOqsdzdzE</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 684000000, "_seconds": 1781339595}</t>
+        </is>
+      </c>
+      <c r="AJ53" t="n">
+        <v>1781339595684</v>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="AL53" t="n">
+        <v>170</v>
+      </c>
       <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
       <c r="AO53" t="inlineStr"/>
       <c r="AP53" t="inlineStr"/>
     </row>
@@ -17744,45 +17752,33 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>default-J80zzFn0TQEAwwaQuzMQsRYzrIvBOC</t>
+          <t>default-58d2b845</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="H54" t="n">
-        <v>14</v>
-      </c>
-      <c r="J54" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N54" t="b">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
         <v>30</v>
       </c>
+      <c r="N54" t="inlineStr"/>
       <c r="Q54" t="n">
-        <v>15.3</v>
+        <v>2.7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>Hallertau Perle</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>A dual-purpose hop that offers great bittering properties as well as a well-rounded aroma profile. Aroma: Herbal - tea, pepper, floral, citrus, earthy, woody, grassy, caramel Alpha Acid: 4.0 - 9.0% Beta Acid: 2.5 - 4.5% Total Oil: 0.5 - 1.3 ml/100g</t>
-        </is>
-      </c>
+          <t>Cascade</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>US</t>
         </is>
       </c>
       <c r="X54" t="inlineStr"/>
       <c r="Z54" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
@@ -17801,35 +17797,12 @@
       </c>
       <c r="AD54" t="inlineStr"/>
       <c r="AE54" t="inlineStr"/>
-      <c r="AF54" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AG54" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 223000000, "_seconds": 1778682625}</t>
-        </is>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>7XQ2gOtWELwAzHhtmwIarzOqsdzdzE</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 684000000, "_seconds": 1781339595}</t>
-        </is>
-      </c>
-      <c r="AJ54" t="n">
-        <v>1781339595684</v>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
-      <c r="AL54" t="n">
-        <v>170</v>
-      </c>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr"/>
+      <c r="AJ54" t="inlineStr"/>
+      <c r="AK54" t="inlineStr"/>
+      <c r="AL54" t="inlineStr"/>
       <c r="AM54" t="inlineStr"/>
       <c r="AN54" t="inlineStr"/>
       <c r="AO54" t="inlineStr"/>
@@ -17853,22 +17826,22 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>default-58d2b845</t>
+          <t>default-bc4774ae</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="H55" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="Q55" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>Cascade</t>
+          <t>Centennial</t>
         </is>
       </c>
       <c r="U55" t="inlineStr"/>
@@ -17888,7 +17861,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Bittering</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -17934,11 +17907,11 @@
         <v>10</v>
       </c>
       <c r="H56" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="Q56" t="n">
-        <v>3.2</v>
+        <v>7.3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -17952,8 +17925,11 @@
         </is>
       </c>
       <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="n">
+        <v>76</v>
+      </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -17967,7 +17943,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Boil</t>
+          <t>Aroma</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr"/>
@@ -17979,7 +17955,6 @@
       <c r="AK56" t="inlineStr"/>
       <c r="AL56" t="inlineStr"/>
       <c r="AM56" t="inlineStr"/>
-      <c r="AN56" t="inlineStr"/>
       <c r="AO56" t="inlineStr"/>
       <c r="AP56" t="inlineStr"/>
     </row>
@@ -18001,22 +17976,22 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>default-bc4774ae</t>
+          <t>default-58d2b845</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="H57" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="Q57" t="n">
-        <v>7.3</v>
+        <v>1.8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>Centennial</t>
+          <t>Cascade</t>
         </is>
       </c>
       <c r="U57" t="inlineStr"/>
@@ -18039,7 +18014,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Bittering</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -18062,12 +18037,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>yiPSN3Y6mmATMzlZ26e4uWlmbGRxaD</t>
+          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>First lager</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -18077,36 +18052,33 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>default-58d2b845</t>
+          <t>default-b73163ee</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="H58" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="Q58" t="n">
-        <v>1.8</v>
+        <v>19.2</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>Cascade</t>
+          <t>Hallertauer Mittelfrueh</t>
         </is>
       </c>
       <c r="U58" t="inlineStr"/>
       <c r="W58" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="n">
-        <v>76</v>
-      </c>
       <c r="Z58" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -18115,12 +18087,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Aroma</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Aroma</t>
+          <t>Boil</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr"/>
@@ -18132,6 +18104,7 @@
       <c r="AK58" t="inlineStr"/>
       <c r="AL58" t="inlineStr"/>
       <c r="AM58" t="inlineStr"/>
+      <c r="AN58" t="inlineStr"/>
       <c r="AO58" t="inlineStr"/>
       <c r="AP58" t="inlineStr"/>
     </row>
@@ -18160,11 +18133,11 @@
         <v>4</v>
       </c>
       <c r="H59" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="Q59" t="n">
-        <v>19.2</v>
+        <v>2.3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -18179,7 +18152,7 @@
       </c>
       <c r="X59" t="inlineStr"/>
       <c r="Z59" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
@@ -18212,12 +18185,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>First lager</t>
+          <t>Smash - Citra</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -18227,44 +18200,51 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>default-b73163ee</t>
+          <t>new-51wCf6O7CNR123kNt0aqW8Oah49aNp</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H60" t="n">
-        <v>10</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="n">
-        <v>2.3</v>
-      </c>
+        <v>14.7</v>
+      </c>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr">
         <is>
-          <t>Hallertauer Mittelfrueh</t>
+          <t>Citra</t>
         </is>
       </c>
       <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>U.S.</t>
         </is>
       </c>
       <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>Pellet</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>Aroma</t>
-        </is>
-      </c>
+      <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr">
         <is>
           <t>Boil</t>
@@ -18272,6 +18252,7 @@
       </c>
       <c r="AD60" t="inlineStr"/>
       <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr"/>
       <c r="AI60" t="inlineStr"/>
@@ -18281,7 +18262,9 @@
       <c r="AM60" t="inlineStr"/>
       <c r="AN60" t="inlineStr"/>
       <c r="AO60" t="inlineStr"/>
-      <c r="AP60" t="inlineStr"/>
+      <c r="AP60" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -18308,7 +18291,7 @@
         <v>12</v>
       </c>
       <c r="H61" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
@@ -18319,7 +18302,7 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="n">
-        <v>14.7</v>
+        <v>15.3</v>
       </c>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
@@ -18338,7 +18321,7 @@
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
@@ -18363,9 +18346,7 @@
       <c r="AM61" t="inlineStr"/>
       <c r="AN61" t="inlineStr"/>
       <c r="AO61" t="inlineStr"/>
-      <c r="AP61" t="b">
-        <v>1</v>
-      </c>
+      <c r="AP61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -18392,7 +18373,7 @@
         <v>12</v>
       </c>
       <c r="H62" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
@@ -18403,7 +18384,7 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
@@ -18422,7 +18403,7 @@
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
@@ -18474,7 +18455,7 @@
         <v>12</v>
       </c>
       <c r="H63" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
@@ -18485,7 +18466,7 @@
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="n">
-        <v>14.6</v>
+        <v>5.6</v>
       </c>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
@@ -18504,7 +18485,7 @@
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
@@ -18514,7 +18495,7 @@
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Boil</t>
+          <t>Aroma</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr"/>
@@ -18552,6 +18533,9 @@
           <t>new-51wCf6O7CNR123kNt0aqW8Oah49aNp</t>
         </is>
       </c>
+      <c r="F64" t="n">
+        <v>1764889200000</v>
+      </c>
       <c r="G64" t="n">
         <v>12</v>
       </c>
@@ -18567,7 +18551,7 @@
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
@@ -18586,7 +18570,7 @@
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
@@ -18596,7 +18580,7 @@
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Aroma</t>
+          <t>Dry Hop</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr"/>
@@ -18610,18 +18594,22 @@
       <c r="AL64" t="inlineStr"/>
       <c r="AM64" t="inlineStr"/>
       <c r="AN64" t="inlineStr"/>
-      <c r="AO64" t="inlineStr"/>
-      <c r="AP64" t="inlineStr"/>
+      <c r="AO64" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP64" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Smash - Citra</t>
+          <t>Saison</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -18631,76 +18619,96 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>new-51wCf6O7CNR123kNt0aqW8Oah49aNp</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>1764889200000</v>
+          <t>default-J80zzFn0TQEAwwaQuzMQsRYzrIvBOC</t>
+        </is>
       </c>
       <c r="G65" t="n">
-        <v>12</v>
+        <v>6.3</v>
       </c>
       <c r="H65" t="n">
+        <v>15</v>
+      </c>
+      <c r="J65" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N65" t="b">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Hallertau Perle</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>A dual-purpose hop that offers great bittering properties as well as a well-rounded aroma profile. Aroma: Herbal - tea, pepper, floral, citrus, earthy, woody, grassy, caramel Alpha Acid: 4.0 - 9.0% Beta Acid: 2.5 - 4.5% Total Oil: 0.5 - 1.3 ml/100g</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr"/>
+      <c r="Z65" t="n">
         <v>60</v>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Citra</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>U.S.</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr"/>
-      <c r="Y65" t="inlineStr"/>
-      <c r="Z65" t="n">
-        <v>2</v>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>Pellet</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Dry Hop</t>
+          <t>Boil</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr"/>
       <c r="AE65" t="inlineStr"/>
-      <c r="AF65" t="inlineStr"/>
-      <c r="AG65" t="inlineStr"/>
-      <c r="AH65" t="inlineStr"/>
-      <c r="AI65" t="inlineStr"/>
-      <c r="AJ65" t="inlineStr"/>
-      <c r="AK65" t="inlineStr"/>
-      <c r="AL65" t="inlineStr"/>
+      <c r="AF65" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 223000000, "_seconds": 1778682625}</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>7XQ2gOtWELwAzHhtmwIarzOqsdzdzE</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 684000000, "_seconds": 1781339595}</t>
+        </is>
+      </c>
+      <c r="AJ65" t="n">
+        <v>1781339595684</v>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="AL65" t="n">
+        <v>170</v>
+      </c>
       <c r="AM65" t="inlineStr"/>
       <c r="AN65" t="inlineStr"/>
-      <c r="AO65" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP65" t="b">
-        <v>1</v>
-      </c>
+      <c r="AO65" t="inlineStr"/>
+      <c r="AP65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -18720,45 +18728,49 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>default-J80zzFn0TQEAwwaQuzMQsRYzrIvBOC</t>
+          <t>default-kazbek</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="H66" t="n">
+        <v>20</v>
+      </c>
+      <c r="J66" t="n">
+        <v>5</v>
+      </c>
+      <c r="N66" t="b">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
         <v>15</v>
       </c>
-      <c r="J66" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N66" t="b">
-        <v>0</v>
-      </c>
-      <c r="O66" t="n">
-        <v>30</v>
-      </c>
       <c r="Q66" t="n">
-        <v>17.1</v>
+        <v>8.5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>Hallertau Perle</t>
+          <t>Kazbek</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>A dual-purpose hop that offers great bittering properties as well as a well-rounded aroma profile. Aroma: Herbal - tea, pepper, floral, citrus, earthy, woody, grassy, caramel Alpha Acid: 4.0 - 9.0% Beta Acid: 2.5 - 4.5% Total Oil: 0.5 - 1.3 ml/100g</t>
+          <t>The classic noble spice of saaz, but with a earthy lemon peel tone. Primarily an aroma hop for whirlpool or dry hopping. Noble hop character but high oil content. Similar to a very strong Saaz with notes of citrus and grapefruit.</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="X66" t="inlineStr"/>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Saaz</t>
+        </is>
+      </c>
       <c r="Z66" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
@@ -18767,7 +18779,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Aroma</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -18775,28 +18787,29 @@
           <t>Boil</t>
         </is>
       </c>
-      <c r="AD66" t="inlineStr"/>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>Pilsner, IPA, Modern Lager, Saison</t>
+        </is>
+      </c>
       <c r="AE66" t="inlineStr"/>
-      <c r="AF66" t="n">
-        <v>2024</v>
-      </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 223000000, "_seconds": 1778682625}</t>
+          <t>{"_nanoseconds": 295000000, "_seconds": 1781069919}</t>
         </is>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>7XQ2gOtWELwAzHhtmwIarzOqsdzdzE</t>
+          <t>jum9pfmvmCJNF6xINUHu7wVYN7BFCG</t>
         </is>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 684000000, "_seconds": 1781339595}</t>
+          <t>{"_nanoseconds": 295000000, "_seconds": 1781069919}</t>
         </is>
       </c>
       <c r="AJ66" t="n">
-        <v>1781339595684</v>
+        <v>1781069919295</v>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
@@ -18804,7 +18817,7 @@
         </is>
       </c>
       <c r="AL66" t="n">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="AM66" t="inlineStr"/>
       <c r="AN66" t="inlineStr"/>
@@ -18848,7 +18861,7 @@
         <v>15</v>
       </c>
       <c r="Q67" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -18871,7 +18884,7 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
@@ -18928,12 +18941,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Saison</t>
+          <t>Smash Mosaic</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -18943,49 +18956,57 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>default-kazbek</t>
+          <t>default-0c4aeb7c</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>5</v>
+        <v>11.1</v>
       </c>
       <c r="H68" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J68" t="n">
-        <v>5</v>
+        <v>5.6</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.1</v>
       </c>
       <c r="N68" t="b">
         <v>0</v>
       </c>
-      <c r="O68" t="n">
-        <v>15</v>
+      <c r="P68" t="n">
+        <v>0.1</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>15.9</v>
+      </c>
+      <c r="S68" t="n">
+        <v>40.6</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>Kazbek</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>The classic noble spice of saaz, but with a earthy lemon peel tone. Primarily an aroma hop for whirlpool or dry hopping. Noble hop character but high oil content. Similar to a very strong Saaz with notes of citrus and grapefruit.</t>
-        </is>
+          <t>Mosaic</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="n">
+        <v>1.7</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>US</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Saaz</t>
+          <t>Citra®</t>
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
@@ -18994,7 +19015,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>Aroma</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -19004,27 +19025,27 @@
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>Pilsner, IPA, Modern Lager, Saison</t>
+          <t>India Pale Ale, Pale Ale</t>
         </is>
       </c>
       <c r="AE68" t="inlineStr"/>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 295000000, "_seconds": 1781069919}</t>
+          <t>{"_nanoseconds": 406000000, "_seconds": 1785754354}</t>
         </is>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>jum9pfmvmCJNF6xINUHu7wVYN7BFCG</t>
+          <t>LISH4vcmJYasu0xkwyZMJ3hK9ZNvds</t>
         </is>
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 295000000, "_seconds": 1781069919}</t>
+          <t>{"_nanoseconds": 406000000, "_seconds": 1785754354}</t>
         </is>
       </c>
       <c r="AJ68" t="n">
-        <v>1781069919295</v>
+        <v>1785754354406</v>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
@@ -19032,9 +19053,11 @@
         </is>
       </c>
       <c r="AL68" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM68" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>15</v>
+      </c>
       <c r="AN68" t="inlineStr"/>
       <c r="AO68" t="inlineStr"/>
       <c r="AP68" t="inlineStr"/>
@@ -19064,7 +19087,7 @@
         <v>11.1</v>
       </c>
       <c r="H69" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J69" t="n">
         <v>5.6</v>
@@ -19082,7 +19105,7 @@
         <v>0.1</v>
       </c>
       <c r="Q69" t="n">
-        <v>15.9</v>
+        <v>7.9</v>
       </c>
       <c r="S69" t="n">
         <v>40.6</v>
@@ -19107,7 +19130,7 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
@@ -19188,7 +19211,7 @@
         <v>11.1</v>
       </c>
       <c r="H70" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="J70" t="n">
         <v>5.6</v>
@@ -19206,7 +19229,7 @@
         <v>0.1</v>
       </c>
       <c r="Q70" t="n">
-        <v>7.9</v>
+        <v>5.5</v>
       </c>
       <c r="S70" t="n">
         <v>40.6</v>
@@ -19231,7 +19254,7 @@
         </is>
       </c>
       <c r="Z70" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
@@ -19312,7 +19335,7 @@
         <v>11.1</v>
       </c>
       <c r="H71" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="J71" t="n">
         <v>5.6</v>
@@ -19330,7 +19353,7 @@
         <v>0.1</v>
       </c>
       <c r="Q71" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="S71" t="n">
         <v>40.6</v>
@@ -19354,8 +19377,11 @@
           <t>Citra®</t>
         </is>
       </c>
+      <c r="Y71" t="n">
+        <v>75</v>
+      </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
@@ -19369,7 +19395,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Boil</t>
+          <t>Aroma</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr">
@@ -19407,19 +19433,18 @@
       <c r="AM71" t="n">
         <v>15</v>
       </c>
-      <c r="AN71" t="inlineStr"/>
       <c r="AO71" t="inlineStr"/>
       <c r="AP71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
+          <t>dXad4F2tnZ5bYPr0H7o1LxG5LkDq1C</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Smash Mosaic</t>
+          <t>Smash shoddy</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -19436,7 +19461,7 @@
         <v>11.1</v>
       </c>
       <c r="H72" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="J72" t="n">
         <v>5.6</v>
@@ -19454,7 +19479,7 @@
         <v>0.1</v>
       </c>
       <c r="Q72" t="n">
-        <v>8.5</v>
+        <v>16.7</v>
       </c>
       <c r="S72" t="n">
         <v>40.6</v>
@@ -19478,11 +19503,8 @@
           <t>Citra®</t>
         </is>
       </c>
-      <c r="Y72" t="n">
-        <v>75</v>
-      </c>
       <c r="Z72" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
@@ -19496,7 +19518,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Aroma</t>
+          <t>Boil</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr">
@@ -19534,6 +19556,7 @@
       <c r="AM72" t="n">
         <v>15</v>
       </c>
+      <c r="AN72" t="inlineStr"/>
       <c r="AO72" t="inlineStr"/>
       <c r="AP72" t="inlineStr"/>
     </row>
@@ -19562,7 +19585,7 @@
         <v>11.1</v>
       </c>
       <c r="H73" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J73" t="n">
         <v>5.6</v>
@@ -19580,7 +19603,7 @@
         <v>0.1</v>
       </c>
       <c r="Q73" t="n">
-        <v>16.7</v>
+        <v>7.9</v>
       </c>
       <c r="S73" t="n">
         <v>40.6</v>
@@ -19605,7 +19628,7 @@
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
@@ -19686,7 +19709,7 @@
         <v>11.1</v>
       </c>
       <c r="H74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="J74" t="n">
         <v>5.6</v>
@@ -19704,7 +19727,7 @@
         <v>0.1</v>
       </c>
       <c r="Q74" t="n">
-        <v>7.9</v>
+        <v>4.3</v>
       </c>
       <c r="S74" t="n">
         <v>40.6</v>
@@ -19729,7 +19752,7 @@
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
@@ -19810,7 +19833,7 @@
         <v>11.1</v>
       </c>
       <c r="H75" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="J75" t="n">
         <v>5.6</v>
@@ -19828,7 +19851,7 @@
         <v>0.1</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="S75" t="n">
         <v>40.6</v>
@@ -19852,8 +19875,11 @@
           <t>Citra®</t>
         </is>
       </c>
+      <c r="Y75" t="n">
+        <v>75</v>
+      </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
@@ -19867,7 +19893,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Boil</t>
+          <t>Aroma</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr">
@@ -19905,19 +19931,18 @@
       <c r="AM75" t="n">
         <v>15</v>
       </c>
-      <c r="AN75" t="inlineStr"/>
       <c r="AO75" t="inlineStr"/>
       <c r="AP75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>dXad4F2tnZ5bYPr0H7o1LxG5LkDq1C</t>
+          <t>TtkyFZuS1krih6K7d2BW7nY3qFmYPZ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Smash shoddy</t>
+          <t>Kalahari blond</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -19927,60 +19952,45 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>default-0c4aeb7c</t>
+          <t>default-J80zzFn0TQEAwwaQuzMQsRYzrIvBOC</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>11.1</v>
+        <v>5.2</v>
       </c>
       <c r="H76" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
       <c r="N76" t="b">
         <v>0</v>
       </c>
-      <c r="P76" t="n">
-        <v>0.1</v>
+      <c r="O76" t="n">
+        <v>30</v>
       </c>
       <c r="Q76" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="S76" t="n">
-        <v>40.6</v>
+        <v>16.6</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>Mosaic</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr"/>
-      <c r="V76" t="n">
-        <v>1.7</v>
+          <t>Hallertau Perle</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>A dual-purpose hop that offers great bittering properties as well as a well-rounded aroma profile. Aroma: Herbal - tea, pepper, floral, citrus, earthy, woody, grassy, caramel Alpha Acid: 4.0 - 9.0% Beta Acid: 2.5 - 4.5% Total Oil: 0.5 - 1.3 ml/100g</t>
+        </is>
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>Citra®</t>
-        </is>
-      </c>
-      <c r="Y76" t="n">
-        <v>75</v>
-      </c>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr"/>
       <c r="Z76" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
@@ -19994,32 +20004,31 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Aroma</t>
-        </is>
-      </c>
-      <c r="AD76" t="inlineStr">
-        <is>
-          <t>India Pale Ale, Pale Ale</t>
-        </is>
-      </c>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr"/>
       <c r="AE76" t="inlineStr"/>
+      <c r="AF76" t="n">
+        <v>2024</v>
+      </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 406000000, "_seconds": 1785754354}</t>
+          <t>{"_nanoseconds": 223000000, "_seconds": 1778682625}</t>
         </is>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>LISH4vcmJYasu0xkwyZMJ3hK9ZNvds</t>
+          <t>t2odApSsIG0sLTEIBBiGzwdpFCABDk</t>
         </is>
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 406000000, "_seconds": 1785754354}</t>
+          <t>{"_nanoseconds": 381000000, "_seconds": 1785061184}</t>
         </is>
       </c>
       <c r="AJ76" t="n">
-        <v>1785754354406</v>
+        <v>1785061184381</v>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
@@ -20027,11 +20036,10 @@
         </is>
       </c>
       <c r="AL76" t="n">
-        <v>200</v>
-      </c>
-      <c r="AM76" t="n">
-        <v>15</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="AM76" t="inlineStr"/>
+      <c r="AN76" t="inlineStr"/>
       <c r="AO76" t="inlineStr"/>
       <c r="AP76" t="inlineStr"/>
     </row>
@@ -20053,37 +20061,27 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>default-J80zzFn0TQEAwwaQuzMQsRYzrIvBOC</t>
+          <t>default-b73163ee</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="H77" t="n">
-        <v>18</v>
-      </c>
-      <c r="J77" t="n">
-        <v>3.5</v>
+        <v>20</v>
       </c>
       <c r="N77" t="b">
         <v>0</v>
       </c>
-      <c r="O77" t="n">
-        <v>30</v>
-      </c>
       <c r="Q77" t="n">
-        <v>16.6</v>
+        <v>4.8</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>Hallertau Perle</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>A dual-purpose hop that offers great bittering properties as well as a well-rounded aroma profile. Aroma: Herbal - tea, pepper, floral, citrus, earthy, woody, grassy, caramel Alpha Acid: 4.0 - 9.0% Beta Acid: 2.5 - 4.5% Total Oil: 0.5 - 1.3 ml/100g</t>
-        </is>
-      </c>
+          <t>Hallertauer Mittelfrueh</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr"/>
       <c r="W77" t="inlineStr">
         <is>
           <t>Germany</t>
@@ -20091,7 +20089,7 @@
       </c>
       <c r="X77" t="inlineStr"/>
       <c r="Z77" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
@@ -20100,7 +20098,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Aroma</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
@@ -20110,26 +20108,23 @@
       </c>
       <c r="AD77" t="inlineStr"/>
       <c r="AE77" t="inlineStr"/>
-      <c r="AF77" t="n">
-        <v>2024</v>
-      </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 223000000, "_seconds": 1778682625}</t>
+          <t>{"_nanoseconds": 85000000, "_seconds": 1714216059}</t>
         </is>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>t2odApSsIG0sLTEIBBiGzwdpFCABDk</t>
+          <t>NN4PCqpf5oxhJkuWbopSaKCIPRhVk7</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 381000000, "_seconds": 1785061184}</t>
+          <t>{"_nanoseconds": 749000000, "_seconds": 1781070162}</t>
         </is>
       </c>
       <c r="AJ77" t="n">
-        <v>1785061184381</v>
+        <v>1781070162749</v>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
@@ -20137,9 +20132,11 @@
         </is>
       </c>
       <c r="AL77" t="n">
-        <v>156</v>
-      </c>
-      <c r="AM77" t="inlineStr"/>
+        <v>105</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>45</v>
+      </c>
       <c r="AN77" t="inlineStr"/>
       <c r="AO77" t="inlineStr"/>
       <c r="AP77" t="inlineStr"/>
@@ -20175,7 +20172,7 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -20189,8 +20186,11 @@
         </is>
       </c>
       <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="n">
+        <v>80</v>
+      </c>
       <c r="Z78" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Boil</t>
+          <t>Aroma</t>
         </is>
       </c>
       <c r="AD78" t="inlineStr"/>
@@ -20238,19 +20238,18 @@
       <c r="AM78" t="n">
         <v>45</v>
       </c>
-      <c r="AN78" t="inlineStr"/>
       <c r="AO78" t="inlineStr"/>
       <c r="AP78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TtkyFZuS1krih6K7d2BW7nY3qFmYPZ</t>
+          <t>3IHDxeB1SX3QaLERATIxYhFsnmvLZZ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Kalahari blond</t>
+          <t>Old English Summer Stout</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -20260,38 +20259,49 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>default-b73163ee</t>
+          <t>default-southernaroma</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="H79" t="n">
-        <v>20</v>
+        <v>30</v>
+      </c>
+      <c r="J79" t="n">
+        <v>5.59</v>
       </c>
       <c r="N79" t="b">
         <v>0</v>
       </c>
+      <c r="O79" t="n">
+        <v>30</v>
+      </c>
       <c r="Q79" t="n">
-        <v>1.4</v>
+        <v>21.1</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>Hallertauer Mittelfrueh</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr"/>
+          <t>Southern Aroma</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Fields of flowers, Dried Herbs, Parsley, Grain, Straw, Sunny hayfield</t>
+        </is>
+      </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="X79" t="inlineStr"/>
-      <c r="Y79" t="n">
-        <v>80</v>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Saaz, Hallertauer Mittelfrueh</t>
+        </is>
       </c>
       <c r="Z79" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
@@ -20305,40 +20315,39 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Aroma</t>
+          <t>Boil</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr"/>
       <c r="AE79" t="inlineStr"/>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 85000000, "_seconds": 1714216059}</t>
+          <t>{"_nanoseconds": 473000000, "_seconds": 1719746363}</t>
         </is>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>NN4PCqpf5oxhJkuWbopSaKCIPRhVk7</t>
+          <t>XCWEvYDmMFt4NFK6nyts7Bg9HJD3vR</t>
         </is>
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 749000000, "_seconds": 1781070162}</t>
+          <t>{"_nanoseconds": 473000000, "_seconds": 1719746363}</t>
         </is>
       </c>
       <c r="AJ79" t="n">
-        <v>1781070162749</v>
+        <v>1719746363473</v>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="AL79" t="n">
-        <v>105</v>
-      </c>
-      <c r="AM79" t="n">
-        <v>45</v>
-      </c>
+        <v>-50</v>
+      </c>
+      <c r="AM79" t="inlineStr"/>
+      <c r="AN79" t="inlineStr"/>
       <c r="AO79" t="inlineStr"/>
       <c r="AP79" t="inlineStr"/>
     </row>
@@ -20367,7 +20376,7 @@
         <v>4</v>
       </c>
       <c r="H80" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J80" t="n">
         <v>5.59</v>
@@ -20379,7 +20388,7 @@
         <v>30</v>
       </c>
       <c r="Q80" t="n">
-        <v>21.1</v>
+        <v>1.8</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -20401,8 +20410,11 @@
           <t>Saaz, Hallertauer Mittelfrueh</t>
         </is>
       </c>
+      <c r="Y80" t="n">
+        <v>80</v>
+      </c>
       <c r="Z80" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
@@ -20416,7 +20428,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Boil</t>
+          <t>Aroma</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr"/>
@@ -20448,124 +20460,11 @@
         <v>-50</v>
       </c>
       <c r="AM80" t="inlineStr"/>
-      <c r="AN80" t="inlineStr"/>
       <c r="AO80" t="inlineStr"/>
       <c r="AP80" t="inlineStr"/>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>3IHDxeB1SX3QaLERATIxYhFsnmvLZZ</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Old English Summer Stout</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Hop</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>default-southernaroma</t>
-        </is>
-      </c>
-      <c r="G81" t="n">
-        <v>4</v>
-      </c>
-      <c r="H81" t="n">
-        <v>20</v>
-      </c>
-      <c r="J81" t="n">
-        <v>5.59</v>
-      </c>
-      <c r="N81" t="b">
-        <v>0</v>
-      </c>
-      <c r="O81" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Southern Aroma</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Fields of flowers, Dried Herbs, Parsley, Grain, Straw, Sunny hayfield</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>Saaz, Hallertauer Mittelfrueh</t>
-        </is>
-      </c>
-      <c r="Y81" t="n">
-        <v>80</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>Pellet</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>Aroma</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Aroma</t>
-        </is>
-      </c>
-      <c r="AD81" t="inlineStr"/>
-      <c r="AE81" t="inlineStr"/>
-      <c r="AG81" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 473000000, "_seconds": 1719746363}</t>
-        </is>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>XCWEvYDmMFt4NFK6nyts7Bg9HJD3vR</t>
-        </is>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 473000000, "_seconds": 1719746363}</t>
-        </is>
-      </c>
-      <c r="AJ81" t="n">
-        <v>1719746363473</v>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>2.10.6</t>
-        </is>
-      </c>
-      <c r="AL81" t="n">
-        <v>-50</v>
-      </c>
-      <c r="AM81" t="inlineStr"/>
-      <c r="AO81" t="inlineStr"/>
-      <c r="AP81" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AP81"/>
+  <autoFilter ref="A1:AP80"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20608,15 +20507,15 @@
     <col width="10" customWidth="1" min="27" max="27"/>
     <col width="20" customWidth="1" min="28" max="28"/>
     <col width="13" customWidth="1" min="29" max="29"/>
-    <col width="10" customWidth="1" min="30" max="30"/>
-    <col width="55" customWidth="1" min="31" max="31"/>
-    <col width="13" customWidth="1" min="32" max="32"/>
-    <col width="53" customWidth="1" min="33" max="33"/>
-    <col width="32" customWidth="1" min="34" max="34"/>
-    <col width="53" customWidth="1" min="35" max="35"/>
-    <col width="15" customWidth="1" min="36" max="36"/>
-    <col width="10" customWidth="1" min="37" max="37"/>
-    <col width="11" customWidth="1" min="38" max="38"/>
+    <col width="53" customWidth="1" min="30" max="30"/>
+    <col width="32" customWidth="1" min="31" max="31"/>
+    <col width="53" customWidth="1" min="32" max="32"/>
+    <col width="15" customWidth="1" min="33" max="33"/>
+    <col width="10" customWidth="1" min="34" max="34"/>
+    <col width="11" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="55" customWidth="1" min="37" max="37"/>
+    <col width="13" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20767,47 +20666,47 @@
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
+          <t>_created</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>_rev</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>_timestamp</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>_timestamp_ms</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>_version</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
           <t>ageRate</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>bestFor</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>cellsPerPkg</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>_created</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>_rev</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>_timestamp</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>_timestamp_ms</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>_version</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>inventory</t>
         </is>
       </c>
     </row>
@@ -21141,19 +21040,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>default-exgZZZ2LIu3saBJpvYyCkGXMi18wxD</t>
+          <t>default-CXQrkdu4oQc6aNLKctrnvpf05s3aKZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>80</v>
       </c>
+      <c r="I5" t="n">
+        <v>1835301600000</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>pres Ski is prized for its ability to produce exceptionally clean and refreshing lagers. Your beers will exhibit a delightful and subtle interplay of floral and fruity notes, imparting a unique character that’s bound to captivate palates. With low ester production and crispness at higher fermentation temps it represents an ideal house lager strain option, ensuring consistent and predictable results with each batch.</t>
+          <t>A German Lager yeast that has it characterized by a clean profile, low ester formation during
+fermentation and medium sulphur production. A good bottom fermenting yeast strain for cold
+fermentation A great choice for all lager styles.</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -21161,12 +21065,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Medium-Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Slurry</t>
+          <t>Dry</t>
         </is>
       </c>
       <c r="N5" t="b">
@@ -21187,21 +21091,17 @@
         <v>16</v>
       </c>
       <c r="T5" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="U5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Crispy lager</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Apres Ski</t>
-        </is>
-      </c>
+          <t>Einstein</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
           <t>Lager</t>
@@ -21209,23 +21109,39 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>First repitch</t>
-        </is>
-      </c>
+          <t>pkg</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 640000000, "_seconds": 1775809389}</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>sygWkeOaDxyFuhHuYUsFOB95taxbvR</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 640000000, "_seconds": 1775809389}</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1775809389640</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>3.0.0</t>
+        </is>
+      </c>
+      <c r="AI5" t="n">
+        <v>2</v>
+      </c>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
@@ -21327,23 +21243,23 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>Stout, IPA, Pale Ale, Brown Ale, Red Ale, Imperial Stout</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>250</v>
-      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
+      <c r="AJ6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Stout, IPA, Pale Ale, Brown Ale, Red Ale, Imperial Stout</t>
+        </is>
+      </c>
+      <c r="AL6" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21439,35 +21355,35 @@
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>{"_nanoseconds": 640000000, "_seconds": 1775809389}</t>
         </is>
       </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>sygWkeOaDxyFuhHuYUsFOB95taxbvR</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 640000000, "_seconds": 1775809389}</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1775809389640</v>
+      </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>sygWkeOaDxyFuhHuYUsFOB95taxbvR</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 640000000, "_seconds": 1775809389}</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1775809389640</v>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
           <t>3.0.0</t>
         </is>
       </c>
-      <c r="AL7" t="n">
+      <c r="AI7" t="n">
         <v>2</v>
       </c>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21651,23 +21567,23 @@
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>Stout, IPA, Pale Ale, Brown Ale, Red Ale, Imperial Stout</t>
-        </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>250</v>
-      </c>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
+      <c r="AJ9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Stout, IPA, Pale Ale, Brown Ale, Red Ale, Imperial Stout</t>
+        </is>
+      </c>
+      <c r="AL9" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21748,35 +21664,35 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>{"_nanoseconds": 592000000, "_seconds": 1714216069}</t>
         </is>
       </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>EQoOb275xeGHoJJIjjGsUWYLSjWwRD</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 986000000, "_seconds": 1723974355}</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1723974355986</v>
+      </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>EQoOb275xeGHoJJIjjGsUWYLSjWwRD</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 986000000, "_seconds": 1723974355}</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1723974355986</v>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
           <t>2.10.6</t>
         </is>
       </c>
-      <c r="AL10" t="n">
+      <c r="AI10" t="n">
         <v>-6</v>
       </c>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -21871,23 +21787,23 @@
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>Stout, IPA, Pale Ale, Brown Ale, Red Ale, Imperial Stout</t>
-        </is>
-      </c>
-      <c r="AF11" t="n">
-        <v>250</v>
-      </c>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
+      <c r="AJ11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Stout, IPA, Pale Ale, Brown Ale, Red Ale, Imperial Stout</t>
+        </is>
+      </c>
+      <c r="AL11" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -22198,23 +22114,23 @@
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>Stout, IPA, Pale Ale, Brown Ale, Red Ale, Imperial Stout</t>
-        </is>
-      </c>
-      <c r="AF14" t="n">
-        <v>250</v>
-      </c>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
+      <c r="AJ14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Stout, IPA, Pale Ale, Brown Ale, Red Ale, Imperial Stout</t>
+        </is>
+      </c>
+      <c r="AL14" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -22299,35 +22215,35 @@
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>{"_nanoseconds": 592000000, "_seconds": 1714216069}</t>
         </is>
       </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>EQoOb275xeGHoJJIjjGsUWYLSjWwRD</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 986000000, "_seconds": 1723974355}</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1723974355986</v>
+      </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>EQoOb275xeGHoJJIjjGsUWYLSjWwRD</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 986000000, "_seconds": 1723974355}</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1723974355986</v>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
           <t>2.10.6</t>
         </is>
       </c>
-      <c r="AL15" t="n">
+      <c r="AI15" t="n">
         <v>-6</v>
       </c>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -22412,35 +22328,35 @@
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>{"_nanoseconds": 592000000, "_seconds": 1714216069}</t>
         </is>
       </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>EQoOb275xeGHoJJIjjGsUWYLSjWwRD</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 986000000, "_seconds": 1723974355}</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1723974355986</v>
+      </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>EQoOb275xeGHoJJIjjGsUWYLSjWwRD</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 986000000, "_seconds": 1723974355}</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1723974355986</v>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
           <t>2.10.6</t>
         </is>
       </c>
-      <c r="AL16" t="n">
+      <c r="AI16" t="n">
         <v>-6</v>
       </c>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -22460,22 +22376,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>default-exgZZZ2LIu3saBJpvYyCkGXMi18wxD</t>
+          <t>default-CXQrkdu4oQc6aNLKctrnvpf05s3aKZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
         <v>80</v>
       </c>
       <c r="I17" t="n">
-        <v>1827525600000</v>
+        <v>1835301600000</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>pres Ski is prized for its ability to produce exceptionally clean and refreshing lagers. Your beers will exhibit a delightful and subtle interplay of floral and fruity notes, imparting a unique character that’s bound to captivate palates. With low ester production and crispness at higher fermentation temps it represents an ideal house lager strain option, ensuring consistent and predictable results with each batch.</t>
+          <t>A German Lager yeast that has it characterized by a clean profile, low ester formation during
+fermentation and medium sulphur production. A good bottom fermenting yeast strain for cold
+fermentation A great choice for all lager styles.</t>
         </is>
       </c>
       <c r="K17" t="b">
@@ -22483,7 +22401,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Medium-Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -22509,21 +22427,17 @@
         <v>16</v>
       </c>
       <c r="T17" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="U17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Crispy lager</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Apres Ski</t>
-        </is>
-      </c>
+          <t>Einstein</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
           <t>Lager</t>
@@ -22531,42 +22445,42 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>pkg</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 925000000, "_seconds": 1775809360}</t>
-        </is>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 640000000, "_seconds": 1775809389}</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>sygWkeOaDxyFuhHuYUsFOB95taxbvR</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 640000000, "_seconds": 1775809389}</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1775809389640</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>B0SCb2UaZONU861NICuknzc19bWGGa</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 572000000, "_seconds": 1788087138}</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1788087138572</v>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
+          <t>3.0.0</t>
+        </is>
+      </c>
+      <c r="AI17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -23040,42 +22954,42 @@
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="n">
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 856000000, "_seconds": 1784057989}</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>ExrXBelZBDAWJ8Bul57dLy2OgQdtkF</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 856000000, "_seconds": 1784057989}</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1784057989856</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="AI22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>1.66</v>
       </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AK22" t="inlineStr">
         <is>
           <t>kölsch-style, neutral ales</t>
         </is>
       </c>
-      <c r="AF22" t="n">
+      <c r="AL22" t="n">
         <v>60</v>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 856000000, "_seconds": 1784057989}</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>ExrXBelZBDAWJ8Bul57dLy2OgQdtkF</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 856000000, "_seconds": 1784057989}</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1784057989856</v>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
-      <c r="AL22" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -23171,35 +23085,35 @@
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>{"_nanoseconds": 443000000, "_seconds": 1784057955}</t>
         </is>
       </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>7L5ixnuXBXaqmTBXyQnlfKg5wkjOhb</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 72000000, "_seconds": 1785061190}</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1785061190072</v>
+      </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>7L5ixnuXBXaqmTBXyQnlfKg5wkjOhb</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 72000000, "_seconds": 1785061190}</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1785061190072</v>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
           <t>3.0.1</t>
         </is>
       </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -23294,35 +23208,35 @@
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>{"_nanoseconds": 443000000, "_seconds": 1784057955}</t>
         </is>
       </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>7L5ixnuXBXaqmTBXyQnlfKg5wkjOhb</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 72000000, "_seconds": 1785061190}</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1785061190072</v>
+      </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>7L5ixnuXBXaqmTBXyQnlfKg5wkjOhb</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 72000000, "_seconds": 1785061190}</t>
-        </is>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1785061190072</v>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
           <t>3.0.1</t>
         </is>
       </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -25619,7 +25533,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="b">

--- a/exports/Brewfather_Recipes_Summary.xlsx
+++ b/exports/Brewfather_Recipes_Summary.xlsx
@@ -2089,7 +2089,8 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>7-8 grams of the yeast.</t>
+          <t>7-8 grams of the yeast. 
+Not more than 2% wheat. 6 was too high.</t>
         </is>
       </c>
     </row>

--- a/exports/Brewfather_Recipes_Summary.xlsx
+++ b/exports/Brewfather_Recipes_Summary.xlsx
@@ -1085,10 +1085,10 @@
         <v>1.047547709</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1.009</v>
+        <v>1.006</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>5.12</v>
+        <v>5.51</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>24.4</v>
@@ -21604,7 +21604,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>default-51d6d6</t>
+          <t>default-CXQrkdu4oQc6aNLKctrnvpf05s3aKZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -21614,13 +21614,22 @@
       <c r="H10" t="n">
         <v>80</v>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>1835301600000</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>A German Lager yeast that has it characterized by a clean profile, low ester formation during
+fermentation and medium sulphur production. A good bottom fermenting yeast strain for cold
+fermentation A great choice for all lager styles.</t>
+        </is>
+      </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -21633,21 +21642,27 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Lallemand (LalBrew)</t>
+          <t>WHC Lab</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="R10" t="n">
+        <v>80</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="T10" t="n">
+        <v>76</v>
       </c>
       <c r="U10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Diamond Lager</t>
+          <t>Einstein</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
@@ -21667,29 +21682,29 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 592000000, "_seconds": 1714216069}</t>
+          <t>{"_nanoseconds": 640000000, "_seconds": 1775809389}</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>EQoOb275xeGHoJJIjjGsUWYLSjWwRD</t>
+          <t>sygWkeOaDxyFuhHuYUsFOB95taxbvR</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 986000000, "_seconds": 1723974355}</t>
+          <t>{"_nanoseconds": 640000000, "_seconds": 1775809389}</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1723974355986</v>
+        <v>1775809389640</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="AI10" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
@@ -27638,30 +27653,30 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 538000000, "_seconds": 1697269076}</t>
+          <t>{"_nanoseconds": 320000000, "_seconds": 1787845020}</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>default-90c63c</t>
+          <t>FxymQbqWfYaVaT8ypqgApwGcTjOAXm</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>UuCzoDs2igKSNb78ZPk2m6iGVQT4Eo</t>
+          <t>8ohTm584SLfO1z9IbILXf1d0nQqtl4</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 76000000, "_seconds": 1723974355}</t>
+          <t>{"_nanoseconds": 14000000, "_seconds": 1788116824}</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1723974355076</v>
+        <v>1788116824014</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -27672,29 +27687,30 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>-15</v>
+        <v>47.4</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Gelatin</t>
-        </is>
-      </c>
-      <c r="Q49" t="b">
-        <v>1</v>
-      </c>
+          <t>ISY Enhabce</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Fining</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Boil</t>
         </is>
       </c>
       <c r="U49" t="inlineStr"/>

--- a/exports/Brewfather_Recipes_Summary.xlsx
+++ b/exports/Brewfather_Recipes_Summary.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recipes'!$A$1:$P$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$95</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hops'!$A$1:$AP$80</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Yeast'!$A$1:$AL$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Misc'!$A$1:$AB$146</definedName>
@@ -1082,19 +1082,19 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1.047547709</v>
+        <v>1.047349593</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1.006</v>
+        <v>1.007</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>5.51</v>
+        <v>5.25</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>24.4</v>
+        <v>24.6</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>12</v>
@@ -2170,7 +2170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT94"/>
+  <dimension ref="A1:AT95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5587,7 +5587,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="L32" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="Q32" t="n">
         <v>1.9</v>
@@ -5613,7 +5613,7 @@
         </is>
       </c>
       <c r="AH32" t="n">
-        <v>100</v>
+        <v>83.33</v>
       </c>
       <c r="AI32" t="n">
         <v>1.0368</v>
@@ -5642,12 +5642,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NP8TWb4ne7Puem87SOkq3DrbZaJQHo</t>
+          <t>MU06X8V9zEP11cbAQnGEm5fUIZajPn</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Stout</t>
+          <t>Marigold Lager</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5657,26 +5657,26 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>PsuWsusDk4opmOZifXKLwShlKVhI2n</t>
+          <t>eZokmPT0UrEuu6NhJHvYoDqPZ4hJao</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 61000000, "_seconds": 1778997165}</t>
+          <t>{"_nanoseconds": 944000000, "_seconds": 1788086445}</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1778997165061</v>
+        <v>1788086445944</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -5684,25 +5684,25 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.9</v>
+        <v>5.1</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X33" t="b">
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>7.7</v>
+        <v>2.15</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE33" t="b">
@@ -5715,13 +5715,13 @@
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>26.25</v>
+        <v>16.67</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.0368</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ33" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AL33" t="inlineStr"/>
       <c r="AM33" t="inlineStr">
@@ -5759,69 +5759,52 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Jr8QUoFHfyKXPhn1IjtiaA3GZwRjfZ</t>
+          <t>PsuWsusDk4opmOZifXKLwShlKVhI2n</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 385000000, "_seconds": 1777108191}</t>
+          <t>{"_nanoseconds": 61000000, "_seconds": 1778997165}</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1777108191385</v>
+        <v>1778997165061</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="P34" t="n">
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S34" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U34" t="n">
-        <v>80</v>
-      </c>
-      <c r="V34" t="n">
-        <v>80</v>
+        <v>1.9</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X34" t="b">
         <v>0</v>
       </c>
-      <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>4.6</v>
+        <v>7.7</v>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE34" t="b">
@@ -5834,16 +5817,13 @@
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>15.75</v>
+        <v>26.25</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.035</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ34" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>11.7</v>
+        <v>80</v>
       </c>
       <c r="AL34" t="inlineStr"/>
       <c r="AM34" t="inlineStr">
@@ -5881,26 +5861,26 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>9h9WIJ7SDEmO08EFQoac9tOfhGvSmw</t>
+          <t>Jr8QUoFHfyKXPhn1IjtiaA3GZwRjfZ</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 984000000, "_seconds": 1776345923}</t>
+          <t>{"_nanoseconds": 385000000, "_seconds": 1777108191}</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1776345923984</v>
+        <v>1777108191385</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -5910,23 +5890,40 @@
       <c r="L35" t="n">
         <v>0.6</v>
       </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
       <c r="Q35" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
+      </c>
+      <c r="S35" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>80</v>
+      </c>
+      <c r="V35" t="n">
+        <v>80</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X35" t="b">
         <v>0</v>
       </c>
+      <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="n">
-        <v>3.45</v>
+        <v>3.14</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>4.6</v>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE35" t="b">
@@ -5942,10 +5939,13 @@
         <v>15.75</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.03588</v>
+        <v>1.035</v>
       </c>
       <c r="AJ35" t="n">
-        <v>78</v>
+        <v>75.37</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>11.7</v>
       </c>
       <c r="AL35" t="inlineStr"/>
       <c r="AM35" t="inlineStr">
@@ -5981,83 +5981,78 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>default-96t8Xs5OLBpW9y5feB0tUbwyNtbfO4</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="n">
-        <v>0</v>
+          <t>default-d9e04639a2c</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>9h9WIJ7SDEmO08EFQoac9tOfhGvSmw</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 984000000, "_seconds": 1776345923}</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>1776345923984</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>3.0.0</t>
+        </is>
       </c>
       <c r="L36" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="P36" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.5380711</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X36" t="b">
         <v>0</v>
       </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>11</v>
+      <c r="Z36" t="n">
+        <v>3.45</v>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>Flaked Torrefied Oats</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>Pre-cooked, non-malted cereals provide the brewer with the opportunity for product differentiation. Flaked products can be added directly to the mash without the need for milling.</t>
-        </is>
-      </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH36" t="n">
-        <v>12.6</v>
+        <v>15.75</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.032</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ36" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="AL36" t="inlineStr"/>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
@@ -6088,52 +6083,31 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 207000000, "_seconds": 1776345941}</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>default-0aa30343c0c</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>JLLnm9cGPVv3337nwYsF4XU4bmE8yr</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 206000000, "_seconds": 1776345941}</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>1776345941206</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>3.0.0</t>
-        </is>
+          <t>default-96t8Xs5OLBpW9y5feB0tUbwyNtbfO4</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="n">
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="M37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.6</v>
+        <v>2.5380711</v>
       </c>
       <c r="S37" t="n">
-        <v>76</v>
-      </c>
-      <c r="U37" t="n">
-        <v>81</v>
-      </c>
-      <c r="V37" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -6143,19 +6117,18 @@
       <c r="X37" t="b">
         <v>0</v>
       </c>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="n">
-        <v>4</v>
+      <c r="Y37" t="n">
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="AC37" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>Swaen Ale</t>
+          <t>Flaked Torrefied Oats</t>
         </is>
       </c>
       <c r="AE37" t="b">
@@ -6163,30 +6136,30 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>Swaen Ale is used to correct over-pale malts, to produce "golden" beer and to improve palate fullness.</t>
+          <t>Pre-cooked, non-malted cereals provide the brewer with the opportunity for product differentiation. Flaked products can be added directly to the mash without the need for milling.</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH37" t="n">
-        <v>10.5</v>
+        <v>12.6</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.037</v>
+        <v>1.032</v>
       </c>
       <c r="AJ37" t="n">
-        <v>80.13</v>
+        <v>70</v>
       </c>
       <c r="AK37" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AL37" t="inlineStr"/>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Crisp</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
@@ -6219,26 +6192,26 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 593000000, "_seconds": 1776345977}</t>
+          <t>{"_nanoseconds": 207000000, "_seconds": 1776345941}</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>default-29dda1b5335</t>
+          <t>default-0aa30343c0c</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>bvta1UbScHCOHOL3y0bkomTlBk4ToI</t>
+          <t>JLLnm9cGPVv3337nwYsF4XU4bmE8yr</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 566000000, "_seconds": 1776346236}</t>
+          <t>{"_nanoseconds": 206000000, "_seconds": 1776345941}</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1776346236566</v>
+        <v>1776345941206</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -6246,44 +6219,71 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>329.949239</v>
+        <v>3.6</v>
+      </c>
+      <c r="S38" t="n">
+        <v>76</v>
+      </c>
+      <c r="U38" t="n">
+        <v>81</v>
+      </c>
+      <c r="V38" t="n">
+        <v>80</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Roasted</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X38" t="b">
         <v>0</v>
       </c>
+      <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>4.5</v>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>BlackSwaen Coffee</t>
+          <t>Swaen Ale</t>
         </is>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>Swaen Ale is used to correct over-pale malts, to produce "golden" beer and to improve palate fullness.</t>
+        </is>
+      </c>
       <c r="AG38" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH38" t="n">
-        <v>9.19</v>
+        <v>10.5</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.028</v>
+        <v>1.037</v>
       </c>
       <c r="AJ38" t="n">
-        <v>60.8695652</v>
+        <v>80.13</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>11.5</v>
       </c>
       <c r="AL38" t="inlineStr"/>
       <c r="AM38" t="inlineStr">
@@ -6298,9 +6298,7 @@
       </c>
       <c r="AO38" t="inlineStr"/>
       <c r="AP38" t="inlineStr"/>
-      <c r="AQ38" t="n">
-        <v>244.1</v>
-      </c>
+      <c r="AQ38" t="inlineStr"/>
       <c r="AR38" t="inlineStr"/>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr"/>
@@ -6323,26 +6321,26 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 593000000, "_seconds": 1776345977}</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>default-25ba5c7007d</t>
+          <t>default-29dda1b5335</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>rvKpzQzk7zcFyo8SUDwJClJQhEMsUP</t>
+          <t>bvta1UbScHCOHOL3y0bkomTlBk4ToI</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 305000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 566000000, "_seconds": 1776346236}</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1776345994305</v>
+        <v>1776346236566</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -6350,48 +6348,44 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0.28</v>
+        <v>0.35</v>
       </c>
       <c r="Q39" t="n">
-        <v>61</v>
+        <v>329.949239</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Roasted</t>
         </is>
       </c>
       <c r="X39" t="b">
         <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>GoldSwaen Classic</t>
+          <t>BlackSwaen Coffee</t>
         </is>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
-        </is>
-      </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH39" t="n">
-        <v>7.35</v>
+        <v>9.19</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.034</v>
+        <v>1.028</v>
       </c>
       <c r="AJ39" t="n">
-        <v>73.9130435</v>
+        <v>60.8695652</v>
       </c>
       <c r="AL39" t="inlineStr"/>
       <c r="AM39" t="inlineStr">
@@ -6406,7 +6400,9 @@
       </c>
       <c r="AO39" t="inlineStr"/>
       <c r="AP39" t="inlineStr"/>
-      <c r="AQ39" t="inlineStr"/>
+      <c r="AQ39" t="n">
+        <v>244.1</v>
+      </c>
       <c r="AR39" t="inlineStr"/>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr"/>
@@ -6429,71 +6425,52 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 545000000, "_seconds": 1775499034}</t>
+          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>default-b5ffdd1</t>
+          <t>default-25ba5c7007d</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>jWuqIkMLK24jzylCQapUkVKL5iFO6T</t>
+          <t>rvKpzQzk7zcFyo8SUDwJClJQhEMsUP</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 551000000, "_seconds": 1777108193}</t>
+          <t>{"_nanoseconds": 305000000, "_seconds": 1776345994}</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1777108193551</v>
+        <v>1776345994305</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>3.0.0</t>
         </is>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
       <c r="L40" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="P40" t="n">
-        <v>1.5</v>
+        <v>0.28</v>
       </c>
       <c r="Q40" t="n">
-        <v>558.375635</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Roasted</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X40" t="b">
         <v>0</v>
       </c>
-      <c r="Y40" t="n">
-        <v>0</v>
-      </c>
       <c r="Z40" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>Carafa Special II</t>
+          <t>GoldSwaen Classic</t>
         </is>
       </c>
       <c r="AE40" t="b">
@@ -6501,30 +6478,27 @@
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
+          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH40" t="n">
-        <v>2.62</v>
+        <v>7.35</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.036</v>
+        <v>1.034</v>
       </c>
       <c r="AJ40" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>10</v>
+        <v>73.9130435</v>
       </c>
       <c r="AL40" t="inlineStr"/>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
@@ -6534,9 +6508,7 @@
       </c>
       <c r="AO40" t="inlineStr"/>
       <c r="AP40" t="inlineStr"/>
-      <c r="AQ40" t="n">
-        <v>412.8</v>
-      </c>
+      <c r="AQ40" t="inlineStr"/>
       <c r="AR40" t="inlineStr"/>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr"/>
@@ -6559,30 +6531,30 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 546000000, "_seconds": 1712314605}</t>
+          <t>{"_nanoseconds": 545000000, "_seconds": 1775499034}</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>default-Q0GFlvnA7LLqVkkfYBAXCniMcRZwnf</t>
+          <t>default-b5ffdd1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>7aV7RCW73FffCIp6YwXe3Ui8TTLeJE</t>
+          <t>jWuqIkMLK24jzylCQapUkVKL5iFO6T</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 122000000, "_seconds": 1778682369}</t>
+          <t>{"_nanoseconds": 551000000, "_seconds": 1777108193}</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1778682369122</v>
+        <v>1777108193551</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -6593,17 +6565,17 @@
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.8</v>
+        <v>558.375635</v>
       </c>
       <c r="S41" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Roasted</t>
         </is>
       </c>
       <c r="X41" t="b">
@@ -6613,17 +6585,17 @@
         <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AB41" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="AC41" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>Malteurop Pilsen</t>
+          <t>Carafa Special II</t>
         </is>
       </c>
       <c r="AE41" t="b">
@@ -6631,30 +6603,30 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>The lightest of our two-row base malts, Malteurop Pilsen malt imparts a sweet and subtle malt flavor and a straw yellow to light golden color. It can be used up to 100% in all beer styles and provides a perfect canvas for other specialty malts.</t>
+          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.038</v>
+        <v>1.036</v>
       </c>
       <c r="AJ41" t="n">
-        <v>81.7</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AK41" t="n">
-        <v>11.3</v>
+        <v>10</v>
       </c>
       <c r="AL41" t="inlineStr"/>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Malteurop Malting Co.</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
@@ -6664,22 +6636,22 @@
       </c>
       <c r="AO41" t="inlineStr"/>
       <c r="AP41" t="inlineStr"/>
-      <c r="AQ41" t="inlineStr"/>
-      <c r="AR41" t="b">
-        <v>1</v>
-      </c>
+      <c r="AQ41" t="n">
+        <v>412.8</v>
+      </c>
+      <c r="AR41" t="inlineStr"/>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>R2xTDLlZjcEYJ5R7Oik4G5urbLeHN6</t>
+          <t>NP8TWb4ne7Puem87SOkq3DrbZaJQHo</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lager pseudo idea ii</t>
+          <t>Stout</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6689,79 +6661,102 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
+          <t>{"_nanoseconds": 546000000, "_seconds": 1712314605}</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>default-sabmjufsad</t>
+          <t>default-Q0GFlvnA7LLqVkkfYBAXCniMcRZwnf</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ezv51k90QM8inkGAdcPNryYgCE8eAF</t>
+          <t>7aV7RCW73FffCIp6YwXe3Ui8TTLeJE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 716000000, "_seconds": 1721546982}</t>
+          <t>{"_nanoseconds": 122000000, "_seconds": 1778682369}</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1721546982716</v>
+        <v>1778682369122</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2.10.6</t>
-        </is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>3</v>
-      </c>
-      <c r="M42" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="P42" t="n">
         <v>0.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>1.8</v>
+      </c>
+      <c r="S42" t="n">
+        <v>146</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X42" t="b">
         <v>0</v>
       </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
       <c r="Z42" t="n">
-        <v>-2.59</v>
+        <v>1</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>4.4</v>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>Pale Malt 2-Row</t>
+          <t>Malteurop Pilsen</t>
         </is>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>The lightest of our two-row base malts, Malteurop Pilsen malt imparts a sweet and subtle malt flavor and a straw yellow to light golden color. It can be used up to 100% in all beer styles and provides a perfect canvas for other specialty malts.</t>
+        </is>
+      </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>US</t>
         </is>
       </c>
       <c r="AH42" t="n">
-        <v>92.59</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.035</v>
+        <v>1.038</v>
       </c>
       <c r="AJ42" t="n">
-        <v>76</v>
+        <v>81.7</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>11.3</v>
       </c>
       <c r="AL42" t="inlineStr"/>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>Malteurop Malting Co.</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
@@ -6772,7 +6767,9 @@
       <c r="AO42" t="inlineStr"/>
       <c r="AP42" t="inlineStr"/>
       <c r="AQ42" t="inlineStr"/>
-      <c r="AR42" t="inlineStr"/>
+      <c r="AR42" t="b">
+        <v>1</v>
+      </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr"/>
     </row>
@@ -6792,89 +6789,81 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>default-cdbfbd6</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="n">
-        <v>0</v>
+          <t>default-sabmjufsad</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ezv51k90QM8inkGAdcPNryYgCE8eAF</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 716000000, "_seconds": 1721546982}</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>1721546982716</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
       </c>
       <c r="L43" t="n">
-        <v>0.14</v>
+        <v>3</v>
       </c>
       <c r="M43" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="P43" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>30</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X43" t="b">
         <v>0</v>
       </c>
-      <c r="Y43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>3.8</v>
+      <c r="Z43" t="n">
+        <v>-2.59</v>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>Melanoidin</t>
+          <t>Pale Malt 2-Row</t>
         </is>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>Red colored malt that improved head retention and stability. Used in red lagers, ales, dark beers. Intense red colour and malty aroma.</t>
-        </is>
-      </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="AH43" t="n">
-        <v>4.32</v>
+        <v>92.59</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.037</v>
+        <v>1.035</v>
       </c>
       <c r="AJ43" t="n">
-        <v>80.06999999999999</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>Carared</t>
-        </is>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="AL43" t="inlineStr"/>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
@@ -6908,50 +6897,88 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>default-08f456e</t>
+          <t>default-cdbfbd6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
       <c r="L44" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr"/>
+          <t>Crystal/Caramel</t>
+        </is>
+      </c>
+      <c r="X44" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>3.8</v>
+      </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>Oats, Flaked</t>
+          <t>Melanoidin</t>
         </is>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>Red colored malt that improved head retention and stability. Used in red lagers, ales, dark beers. Intense red colour and malty aroma.</t>
+        </is>
+      </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH44" t="n">
-        <v>3.09</v>
+        <v>4.32</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.0368</v>
+        <v>1.037</v>
       </c>
       <c r="AJ44" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL44" t="inlineStr"/>
-      <c r="AM44" t="inlineStr"/>
+        <v>80.06999999999999</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>Carared</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Weyermann</t>
+        </is>
+      </c>
       <c r="AN44" t="inlineStr">
         <is>
           <t>Grain</t>
@@ -6967,12 +6994,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RxtDAxv74eS2hKCxjIaWPwTWx4sYVF</t>
+          <t>R2xTDLlZjcEYJ5R7Oik4G5urbLeHN6</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>First Lager v3</t>
+          <t>Lager pseudo idea ii</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6983,7 +7010,7 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>default-kTJTLZIhyeFDXlOIOLxrPWfGnU8z4A</t>
+          <t>default-08f456e</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -6991,45 +7018,120 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="L45" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>Oats, Flaked</t>
+        </is>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AH45" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>1.0368</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="inlineStr"/>
+      <c r="AQ45" t="inlineStr"/>
+      <c r="AR45" t="inlineStr"/>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>RxtDAxv74eS2hKCxjIaWPwTWx4sYVF</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>First Lager v3</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>default-kTJTLZIhyeFDXlOIOLxrPWfGnU8z4A</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="L46" t="n">
         <v>2</v>
       </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="P45" t="n">
+      <c r="M46" t="inlineStr"/>
+      <c r="P46" t="n">
         <v>1</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="Q46" t="n">
         <v>1.9</v>
       </c>
-      <c r="U45" t="n">
+      <c r="U46" t="n">
         <v>80</v>
       </c>
-      <c r="V45" t="n">
+      <c r="V46" t="n">
         <v>82</v>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>Base (Pilsner)</t>
         </is>
       </c>
-      <c r="X45" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="inlineStr"/>
-      <c r="AB45" t="n">
+      <c r="X46" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="AB46" t="n">
         <v>100</v>
       </c>
-      <c r="AC45" t="n">
+      <c r="AC46" t="n">
         <v>5</v>
       </c>
-      <c r="AD45" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>Bohemian Pilsner</t>
         </is>
       </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="inlineStr">
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr">
         <is>
           <t>Made from the finest Bohemian malting quality barley (Barley varieties Bojos and Malz), this Pilsner malt is characterized by the typical sententious core notes of the original barley varieties.
 Sensory: nutty malt aroma, malty-sweet
@@ -7038,160 +7140,47 @@
 Product Sheet: https://www.weyermann.de/wp-content/uploads/2021/02/Weyermann_Bohemian_Pilsner_Malt_Specification.pdf</t>
         </is>
       </c>
-      <c r="AG45" t="inlineStr">
+      <c r="AG46" t="inlineStr">
         <is>
           <t>Bohemia</t>
         </is>
       </c>
-      <c r="AH45" t="n">
+      <c r="AH46" t="n">
         <v>71.94</v>
       </c>
-      <c r="AI45" t="n">
+      <c r="AI46" t="n">
         <v>1.035</v>
       </c>
-      <c r="AJ45" t="n">
+      <c r="AJ46" t="n">
         <v>75.05</v>
       </c>
-      <c r="AK45" t="n">
+      <c r="AK46" t="n">
         <v>10.75</v>
       </c>
-      <c r="AL45" t="inlineStr">
+      <c r="AL46" t="inlineStr">
         <is>
           <t>Weyermann Floor-Malted Bohemian Pilsner Malt</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
+      <c r="AM46" t="inlineStr">
         <is>
           <t>Weyermann</t>
         </is>
       </c>
-      <c r="AN45" t="inlineStr">
+      <c r="AN46" t="inlineStr">
         <is>
           <t>Grain</t>
         </is>
       </c>
-      <c r="AO45" t="inlineStr">
+      <c r="AO46" t="inlineStr">
         <is>
           <t>pilsners</t>
         </is>
       </c>
-      <c r="AP45" t="inlineStr"/>
-      <c r="AQ45" t="n">
+      <c r="AP46" t="inlineStr"/>
+      <c r="AQ46" t="n">
         <v>1.95</v>
       </c>
-      <c r="AR45" t="inlineStr"/>
-      <c r="AS45" t="inlineStr"/>
-      <c r="AT45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>RxtDAxv74eS2hKCxjIaWPwTWx4sYVF</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>First Lager v3</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Fermentable</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>default-4d8b7c4</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>3</v>
-      </c>
-      <c r="S46" t="n">
-        <v>50</v>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Base (Vienna)</t>
-        </is>
-      </c>
-      <c r="X46" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>Vienna Malt</t>
-        </is>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>Vienna base malt - used in many continental beer styles. Full bodied, golden color.</t>
-        </is>
-      </c>
-      <c r="AG46" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="AH46" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>1.038</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>82.23</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>Pale Liquid Extract</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Weyermann</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>Grain</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr"/>
-      <c r="AP46" t="inlineStr"/>
-      <c r="AQ46" t="inlineStr"/>
       <c r="AR46" t="inlineStr"/>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr"/>
@@ -7215,7 +7204,7 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>default-1482365</t>
+          <t>default-4d8b7c4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -7226,23 +7215,23 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0.28</v>
+        <v>0.5</v>
       </c>
       <c r="M47" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="P47" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X47" t="b">
@@ -7252,14 +7241,14 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="AC47" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>Carapils/Carafoam</t>
+          <t>Vienna Malt</t>
         </is>
       </c>
       <c r="AE47" t="b">
@@ -7267,7 +7256,7 @@
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>Carafoam (also called Carapils) adds body and head retention without substantially altering flavor. Up to 10% for light beers, 40% for mashed beers</t>
+          <t>Vienna base malt - used in many continental beer styles. Full bodied, golden color.</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
@@ -7276,18 +7265,22 @@
         </is>
       </c>
       <c r="AH47" t="n">
-        <v>10.07</v>
+        <v>17.99</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.037</v>
+        <v>1.038</v>
       </c>
       <c r="AJ47" t="n">
-        <v>80.06999999999999</v>
+        <v>82.23</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL47" t="inlineStr"/>
+        <v>10.9</v>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>Pale Liquid Extract</t>
+        </is>
+      </c>
       <c r="AM47" t="inlineStr">
         <is>
           <t>Weyermann</t>
@@ -7308,12 +7301,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>YOwmEZx99K2SoQK0VbXkyCchdmIrZZ</t>
+          <t>RxtDAxv74eS2hKCxjIaWPwTWx4sYVF</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>London Pub gen 2 Weskus</t>
+          <t>First Lager v3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7321,78 +7314,85 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>default-sabmjufsad</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>ezv51k90QM8inkGAdcPNryYgCE8eAF</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 716000000, "_seconds": 1721546982}</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>1721546982716</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2.10.6</t>
-        </is>
+          <t>default-1482365</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="n">
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>2.6</v>
+        <v>0.28</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q48" t="n">
         <v>2</v>
       </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X48" t="b">
         <v>0</v>
       </c>
-      <c r="Z48" t="n">
-        <v>-2.59</v>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>4.9</v>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>Pale Malt 2-Row</t>
+          <t>Carapils/Carafoam</t>
         </is>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>Carafoam (also called Carapils) adds body and head retention without substantially altering flavor. Up to 10% for light beers, 40% for mashed beers</t>
+        </is>
+      </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH48" t="n">
-        <v>79.27</v>
+        <v>10.07</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.035</v>
+        <v>1.037</v>
       </c>
       <c r="AJ48" t="n">
-        <v>76</v>
+        <v>80.06999999999999</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>0</v>
       </c>
       <c r="AL48" t="inlineStr"/>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
@@ -7425,102 +7425,76 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 248000000, "_seconds": 1714216056}</t>
+          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>default-x1sQkldAFEgNTfYCHtBq70SjihT1F8</t>
+          <t>default-sabmjufsad</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>CPkrJFvR0z03f2qIouoRdQwhmALFMG</t>
+          <t>ezv51k90QM8inkGAdcPNryYgCE8eAF</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 27000000, "_seconds": 1723974350}</t>
+          <t>{"_nanoseconds": 716000000, "_seconds": 1721546982}</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1723974350027</v>
+        <v>1721546982716</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>2.10.6</t>
         </is>
       </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
       <c r="L49" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="P49" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.9593909</v>
-      </c>
-      <c r="S49" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X49" t="b">
         <v>0</v>
       </c>
-      <c r="Y49" t="n">
-        <v>0</v>
-      </c>
       <c r="Z49" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>4.5</v>
+        <v>-2.59</v>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>Vienna Malt</t>
+          <t>Pale Malt 2-Row</t>
         </is>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>Vienna malt is produced on a conventional kiln and provides a light golden hue</t>
-        </is>
-      </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="AH49" t="n">
-        <v>15.24</v>
+        <v>79.27</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.037</v>
+        <v>1.035</v>
       </c>
       <c r="AJ49" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>9.6</v>
+        <v>76</v>
       </c>
       <c r="AL49" t="inlineStr"/>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
@@ -7551,37 +7525,53 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 248000000, "_seconds": 1714216056}</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>default-cdbfbd6</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>default-x1sQkldAFEgNTfYCHtBq70SjihT1F8</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>CPkrJFvR0z03f2qIouoRdQwhmALFMG</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 27000000, "_seconds": 1723974350}</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>1723974350027</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0.73</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="P50" t="n">
         <v>1.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>30</v>
+        <v>3.9593909</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X50" t="b">
@@ -7590,15 +7580,18 @@
       <c r="Y50" t="n">
         <v>0</v>
       </c>
+      <c r="Z50" t="n">
+        <v>-3</v>
+      </c>
       <c r="AB50" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>Melanoidin</t>
+          <t>Vienna Malt</t>
         </is>
       </c>
       <c r="AE50" t="b">
@@ -7606,34 +7599,30 @@
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>Red colored malt that improved head retention and stability. Used in red lagers, ales, dark beers. Intense red colour and malty aroma.</t>
+          <t>Vienna malt is produced on a conventional kiln and provides a light golden hue</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH50" t="n">
-        <v>3.96</v>
+        <v>15.24</v>
       </c>
       <c r="AI50" t="n">
         <v>1.037</v>
       </c>
       <c r="AJ50" t="n">
-        <v>80.06999999999999</v>
+        <v>80</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL50" t="inlineStr">
-        <is>
-          <t>Carared</t>
-        </is>
-      </c>
+        <v>9.6</v>
+      </c>
+      <c r="AL50" t="inlineStr"/>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>Crisp</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
@@ -7667,7 +7656,7 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>default-aaaccad</t>
+          <t>default-cdbfbd6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -7678,14 +7667,16 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M51" t="inlineStr"/>
+        <v>0.13</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.73</v>
+      </c>
       <c r="P51" t="n">
         <v>1.5</v>
       </c>
       <c r="Q51" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -7702,14 +7693,14 @@
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AC51" t="n">
-        <v>6.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>Carahell</t>
+          <t>Melanoidin</t>
         </is>
       </c>
       <c r="AE51" t="b">
@@ -7717,7 +7708,7 @@
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>Light colored caramel malt. Adds body, color and aroma. Use up to 30% in low alcohol beers</t>
+          <t>Red colored malt that improved head retention and stability. Used in red lagers, ales, dark beers. Intense red colour and malty aroma.</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">
@@ -7726,18 +7717,22 @@
         </is>
       </c>
       <c r="AH51" t="n">
-        <v>1.52</v>
+        <v>3.96</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.035</v>
+        <v>1.037</v>
       </c>
       <c r="AJ51" t="n">
-        <v>75.73999999999999</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="AK51" t="n">
         <v>0</v>
       </c>
-      <c r="AL51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>Carared</t>
+        </is>
+      </c>
       <c r="AM51" t="inlineStr">
         <is>
           <t>Weyermann</t>
@@ -7758,12 +7753,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>dsVqWqNVboCzKtRIVDlw4lsZ3qshOR</t>
+          <t>YOwmEZx99K2SoQK0VbXkyCchdmIrZZ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Helles bock</t>
+          <t>London Pub gen 2 Weskus</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7774,52 +7769,80 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-aaaccad</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
       <c r="L52" t="n">
-        <v>2.9</v>
+        <v>0.05</v>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.9</v>
+        <v>13</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr"/>
+          <t>Crystal/Caramel</t>
+        </is>
+      </c>
+      <c r="X52" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>6.7</v>
+      </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Carahell</t>
         </is>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>Light colored caramel malt. Adds body, color and aroma. Use up to 30% in low alcohol beers</t>
+        </is>
+      </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH52" t="n">
-        <v>70.73</v>
+        <v>1.52</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.0368</v>
+        <v>1.035</v>
       </c>
       <c r="AJ52" t="n">
-        <v>80</v>
+        <v>75.73999999999999</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>0</v>
       </c>
       <c r="AL52" t="inlineStr"/>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
@@ -7853,7 +7876,7 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -7861,20 +7884,20 @@
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="L53" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X53" t="inlineStr"/>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE53" t="b">
@@ -7887,13 +7910,13 @@
         </is>
       </c>
       <c r="AH53" t="n">
-        <v>19.51</v>
+        <v>70.73</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ53" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL53" t="inlineStr"/>
       <c r="AM53" t="inlineStr">
@@ -7932,7 +7955,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -7940,39 +7963,20 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="L54" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="P54" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q54" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S54" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U54" t="n">
-        <v>80</v>
-      </c>
-      <c r="V54" t="n">
-        <v>80</v>
+        <v>5.1</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
-        </is>
-      </c>
-      <c r="X54" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="inlineStr"/>
-      <c r="AC54" t="n">
-        <v>4.6</v>
-      </c>
+          <t>Base (Vienna)</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE54" t="b">
@@ -7985,16 +7989,13 @@
         </is>
       </c>
       <c r="AH54" t="n">
-        <v>8.539999999999999</v>
+        <v>19.51</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.035</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ54" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>11.7</v>
+        <v>78</v>
       </c>
       <c r="AL54" t="inlineStr"/>
       <c r="AM54" t="inlineStr">
@@ -8030,77 +8031,72 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>default-25ba5c7007d</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>lBdAIVmlcp7FjYPSV55HleXloB6alW</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 491000000, "_seconds": 1781339589}</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>1781339589491</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
+          <t>default-c454dca637a</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="L55" t="n">
-        <v>0.05</v>
+        <v>0.35</v>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="P55" t="n">
+        <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>61</v>
+        <v>6.6</v>
+      </c>
+      <c r="S55" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>80</v>
+      </c>
+      <c r="V55" t="n">
+        <v>80</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X55" t="b">
         <v>0</v>
       </c>
-      <c r="Z55" t="n">
-        <v>1.36</v>
+      <c r="Y55" t="inlineStr"/>
+      <c r="AC55" t="n">
+        <v>4.6</v>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>GoldSwaen Classic</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
-        </is>
-      </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH55" t="n">
-        <v>1.22</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="AI55" t="n">
-        <v>1.034</v>
+        <v>1.035</v>
       </c>
       <c r="AJ55" t="n">
-        <v>73.9130435</v>
+        <v>75.37</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>11.7</v>
       </c>
       <c r="AL55" t="inlineStr"/>
       <c r="AM55" t="inlineStr">
@@ -8123,12 +8119,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>hJRSice4Rnaj5KIs2qxSpXYeU2IT2b</t>
+          <t>dsVqWqNVboCzKtRIVDlw4lsZ3qshOR</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Black bit</t>
+          <t>Helles bock</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8138,90 +8134,80 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 863000000, "_seconds": 1716635703}</t>
+          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>default-nym-3n456</t>
+          <t>default-25ba5c7007d</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>08DPhtHHs3tnJkiCc2upQ6GHIshNL8</t>
+          <t>lBdAIVmlcp7FjYPSV55HleXloB6alW</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 782000000, "_seconds": 1721546982}</t>
+          <t>{"_nanoseconds": 491000000, "_seconds": 1781339589}</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1721546982782</v>
+        <v>1781339589491</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2.10.6</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M56" t="inlineStr"/>
+        <v>0.05</v>
+      </c>
       <c r="Q56" t="n">
-        <v>1.77665</v>
-      </c>
-      <c r="U56" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="V56" t="n">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X56" t="b">
         <v>0</v>
       </c>
-      <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>5</v>
+        <v>1.36</v>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>Barke Pilsner</t>
+          <t>GoldSwaen Classic</t>
         </is>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
+        </is>
+      </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH56" t="n">
-        <v>45.16</v>
+        <v>1.22</v>
       </c>
       <c r="AI56" t="n">
-        <v>1.035</v>
+        <v>1.034</v>
       </c>
       <c r="AJ56" t="n">
-        <v>76.48</v>
+        <v>73.9130435</v>
       </c>
       <c r="AL56" t="inlineStr"/>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
@@ -8252,47 +8238,68 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 863000000, "_seconds": 1716635703}</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>default-xEmREaAKEqiWVqh8d63GKWePssUELH</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>default-nym-3n456</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>08DPhtHHs3tnJkiCc2upQ6GHIshNL8</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 782000000, "_seconds": 1721546982}</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>1721546982782</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="M57" t="inlineStr"/>
       <c r="Q57" t="n">
-        <v>3.807107</v>
+        <v>1.77665</v>
       </c>
       <c r="U57" t="n">
-        <v>79</v>
+        <v>80.5</v>
       </c>
       <c r="V57" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X57" t="b">
         <v>0</v>
       </c>
       <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="n">
+        <v>0</v>
+      </c>
       <c r="AB57" t="n">
         <v>100</v>
       </c>
       <c r="AC57" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>Barke Vienna Malt</t>
+          <t>Barke Pilsner</t>
         </is>
       </c>
       <c r="AE57" t="b">
@@ -8305,16 +8312,13 @@
         </is>
       </c>
       <c r="AH57" t="n">
-        <v>32.26</v>
+        <v>45.16</v>
       </c>
       <c r="AI57" t="n">
-        <v>1.034</v>
+        <v>1.035</v>
       </c>
       <c r="AJ57" t="n">
-        <v>74.66</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>10.5</v>
+        <v>76.48</v>
       </c>
       <c r="AL57" t="inlineStr"/>
       <c r="AM57" t="inlineStr">
@@ -8329,13 +8333,9 @@
       </c>
       <c r="AO57" t="inlineStr"/>
       <c r="AP57" t="inlineStr"/>
-      <c r="AQ57" t="n">
-        <v>3.4</v>
-      </c>
+      <c r="AQ57" t="inlineStr"/>
       <c r="AR57" t="inlineStr"/>
-      <c r="AS57" t="b">
-        <v>0</v>
-      </c>
+      <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr"/>
     </row>
     <row r="58">
@@ -8357,75 +8357,66 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>default-b5ffdd1</t>
+          <t>default-xEmREaAKEqiWVqh8d63GKWePssUELH</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
       <c r="L58" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="M58" t="inlineStr"/>
-      <c r="P58" t="n">
-        <v>1.5</v>
-      </c>
       <c r="Q58" t="n">
-        <v>558.375635</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
+        <v>3.807107</v>
+      </c>
+      <c r="U58" t="n">
+        <v>79</v>
+      </c>
+      <c r="V58" t="n">
+        <v>80</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>Roasted</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X58" t="b">
         <v>0</v>
       </c>
-      <c r="Y58" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y58" t="inlineStr"/>
       <c r="AB58" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="AC58" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>Carafa Special II</t>
+          <t>Barke Vienna Malt</t>
         </is>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
-        </is>
-      </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
       <c r="AH58" t="n">
-        <v>8.06</v>
+        <v>32.26</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.036</v>
+        <v>1.034</v>
       </c>
       <c r="AJ58" t="n">
-        <v>77.90000000000001</v>
+        <v>74.66</v>
       </c>
       <c r="AK58" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AL58" t="inlineStr"/>
       <c r="AM58" t="inlineStr">
@@ -8441,10 +8432,12 @@
       <c r="AO58" t="inlineStr"/>
       <c r="AP58" t="inlineStr"/>
       <c r="AQ58" t="n">
-        <v>412.8</v>
+        <v>3.4</v>
       </c>
       <c r="AR58" t="inlineStr"/>
-      <c r="AS58" t="inlineStr"/>
+      <c r="AS58" t="b">
+        <v>0</v>
+      </c>
       <c r="AT58" t="inlineStr"/>
     </row>
     <row r="59">
@@ -8466,7 +8459,7 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>default-1482365</t>
+          <t>default-b5ffdd1</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -8479,14 +8472,12 @@
       <c r="L59" t="n">
         <v>0.25</v>
       </c>
-      <c r="M59" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="P59" t="n">
         <v>1.5</v>
       </c>
       <c r="Q59" t="n">
-        <v>2</v>
+        <v>558.375635</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -8503,14 +8494,14 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AC59" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>Carapils/Carafoam</t>
+          <t>Carafa Special II</t>
         </is>
       </c>
       <c r="AE59" t="b">
@@ -8518,7 +8509,7 @@
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>Carafoam (also called Carapils) adds body and head retention without substantially altering flavor. Up to 10% for light beers, 40% for mashed beers</t>
+          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
         </is>
       </c>
       <c r="AG59" t="inlineStr">
@@ -8530,13 +8521,13 @@
         <v>8.06</v>
       </c>
       <c r="AI59" t="n">
-        <v>1.037</v>
+        <v>1.036</v>
       </c>
       <c r="AJ59" t="n">
-        <v>80.06999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AK59" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL59" t="inlineStr"/>
       <c r="AM59" t="inlineStr">
@@ -8551,7 +8542,9 @@
       </c>
       <c r="AO59" t="inlineStr"/>
       <c r="AP59" t="inlineStr"/>
-      <c r="AQ59" t="inlineStr"/>
+      <c r="AQ59" t="n">
+        <v>412.8</v>
+      </c>
       <c r="AR59" t="inlineStr"/>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr"/>
@@ -8575,29 +8568,34 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>default-60a8af8</t>
+          <t>default-1482365</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
       <c r="L60" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M60" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P60" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q60" t="n">
-        <v>7.614213</v>
+        <v>2</v>
       </c>
       <c r="S60" t="n">
-        <v>50</v>
-      </c>
-      <c r="U60" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
+          <t>Roasted</t>
         </is>
       </c>
       <c r="X60" t="b">
@@ -8607,14 +8605,14 @@
         <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AC60" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>Munich I</t>
+          <t>Carapils/Carafoam</t>
         </is>
       </c>
       <c r="AE60" t="b">
@@ -8622,7 +8620,7 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>Light Munich malt. May be used as a base for many German beer styles. Fest beers, bocks, ales. Enhances malty flavour and aroma</t>
+          <t>Carafoam (also called Carapils) adds body and head retention without substantially altering flavor. Up to 10% for light beers, 40% for mashed beers</t>
         </is>
       </c>
       <c r="AG60" t="inlineStr">
@@ -8631,22 +8629,18 @@
         </is>
       </c>
       <c r="AH60" t="n">
-        <v>6.45</v>
+        <v>8.06</v>
       </c>
       <c r="AI60" t="n">
-        <v>1.038</v>
+        <v>1.037</v>
       </c>
       <c r="AJ60" t="n">
-        <v>82.3</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="AK60" t="n">
-        <v>11</v>
-      </c>
-      <c r="AL60" t="inlineStr">
-        <is>
-          <t>Amber Liquid Extract</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AL60" t="inlineStr"/>
       <c r="AM60" t="inlineStr">
         <is>
           <t>Weyermann</t>
@@ -8659,9 +8653,7 @@
       </c>
       <c r="AO60" t="inlineStr"/>
       <c r="AP60" t="inlineStr"/>
-      <c r="AQ60" t="n">
-        <v>6.2</v>
-      </c>
+      <c r="AQ60" t="inlineStr"/>
       <c r="AR60" t="inlineStr"/>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr"/>
@@ -8669,12 +8661,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>hV82vumYBf6BRTmLMntedEkZ1kk2pf</t>
+          <t>hJRSice4Rnaj5KIs2qxSpXYeU2IT2b</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Swart bier 2026</t>
+          <t>Black bit</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8685,7 +8677,7 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-60a8af8</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -8693,44 +8685,73 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="L61" t="n">
-        <v>2</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="Q61" t="n">
-        <v>1.9</v>
+        <v>7.614213</v>
+      </c>
+      <c r="S61" t="n">
+        <v>50</v>
+      </c>
+      <c r="U61" t="n">
+        <v>78</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr"/>
+          <t>Base (Munich)</t>
+        </is>
+      </c>
+      <c r="X61" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>4.5</v>
+      </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Munich I</t>
         </is>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>Light Munich malt. May be used as a base for many German beer styles. Fest beers, bocks, ales. Enhances malty flavour and aroma</t>
+        </is>
+      </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH61" t="n">
-        <v>62.5</v>
+        <v>6.45</v>
       </c>
       <c r="AI61" t="n">
-        <v>1.0368</v>
+        <v>1.038</v>
       </c>
       <c r="AJ61" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL61" t="inlineStr"/>
+        <v>82.3</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>11</v>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>Amber Liquid Extract</t>
+        </is>
+      </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
@@ -8740,7 +8761,9 @@
       </c>
       <c r="AO61" t="inlineStr"/>
       <c r="AP61" t="inlineStr"/>
-      <c r="AQ61" t="inlineStr"/>
+      <c r="AQ61" t="n">
+        <v>6.2</v>
+      </c>
       <c r="AR61" t="inlineStr"/>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr"/>
@@ -8764,7 +8787,7 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -8772,39 +8795,20 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="L62" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="P62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q62" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S62" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U62" t="n">
-        <v>80</v>
-      </c>
-      <c r="V62" t="n">
-        <v>80</v>
+        <v>1.9</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
-        </is>
-      </c>
-      <c r="X62" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y62" t="inlineStr"/>
-      <c r="AC62" t="n">
-        <v>4.6</v>
-      </c>
+          <t>Base (Pilsner)</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE62" t="b">
@@ -8817,16 +8821,13 @@
         </is>
       </c>
       <c r="AH62" t="n">
-        <v>18.75</v>
+        <v>62.5</v>
       </c>
       <c r="AI62" t="n">
-        <v>1.035</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ62" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK62" t="n">
-        <v>11.7</v>
+        <v>80</v>
       </c>
       <c r="AL62" t="inlineStr"/>
       <c r="AM62" t="inlineStr">
@@ -8865,7 +8866,7 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -8873,20 +8874,39 @@
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="L63" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="P63" t="n">
+        <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
+      </c>
+      <c r="S63" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>80</v>
+      </c>
+      <c r="V63" t="n">
+        <v>80</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr"/>
+          <t>Base (Munich)</t>
+        </is>
+      </c>
+      <c r="X63" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="AC63" t="n">
+        <v>4.6</v>
+      </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE63" t="b">
@@ -8899,13 +8919,16 @@
         </is>
       </c>
       <c r="AH63" t="n">
-        <v>9.369999999999999</v>
+        <v>18.75</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.03588</v>
+        <v>1.035</v>
       </c>
       <c r="AJ63" t="n">
-        <v>78</v>
+        <v>75.37</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>11.7</v>
       </c>
       <c r="AL63" t="inlineStr"/>
       <c r="AM63" t="inlineStr">
@@ -8944,80 +8967,52 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>default-b5ffdd1</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
       <c r="L64" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M64" t="inlineStr"/>
-      <c r="P64" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="Q64" t="n">
-        <v>558.375635</v>
-      </c>
-      <c r="S64" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Roasted</t>
-        </is>
-      </c>
-      <c r="X64" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>3</v>
-      </c>
+          <t>Base (Vienna)</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr"/>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>Carafa Special II</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr">
-        <is>
-          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
-        </is>
-      </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH64" t="n">
-        <v>6.25</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="AI64" t="n">
-        <v>1.036</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ64" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="AK64" t="n">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="AL64" t="inlineStr"/>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
@@ -9027,9 +9022,7 @@
       </c>
       <c r="AO64" t="inlineStr"/>
       <c r="AP64" t="inlineStr"/>
-      <c r="AQ64" t="n">
-        <v>412.8</v>
-      </c>
+      <c r="AQ64" t="inlineStr"/>
       <c r="AR64" t="inlineStr"/>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr"/>
@@ -9050,54 +9043,52 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>default-25ba5c7007d</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>1J9fe3tUex3oOKOPk0F51aZTCC6NvP</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1785061179}</t>
-        </is>
-      </c>
-      <c r="I65" t="n">
-        <v>1785061179983</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
+          <t>default-b5ffdd1</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="n">
+        <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="P65" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q65" t="n">
-        <v>61</v>
+        <v>558.375635</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Roasted</t>
         </is>
       </c>
       <c r="X65" t="b">
         <v>0</v>
       </c>
-      <c r="Z65" t="n">
-        <v>1.31</v>
+      <c r="Y65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>3</v>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>GoldSwaen Classic</t>
+          <t>Carafa Special II</t>
         </is>
       </c>
       <c r="AE65" t="b">
@@ -9105,27 +9096,30 @@
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
+          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
         </is>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH65" t="n">
-        <v>3.13</v>
+        <v>6.25</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.034</v>
+        <v>1.036</v>
       </c>
       <c r="AJ65" t="n">
-        <v>73.9130435</v>
+        <v>77.90000000000001</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>10</v>
       </c>
       <c r="AL65" t="inlineStr"/>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
@@ -9135,7 +9129,9 @@
       </c>
       <c r="AO65" t="inlineStr"/>
       <c r="AP65" t="inlineStr"/>
-      <c r="AQ65" t="inlineStr"/>
+      <c r="AQ65" t="n">
+        <v>412.8</v>
+      </c>
       <c r="AR65" t="inlineStr"/>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr"/>
@@ -9143,12 +9139,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>jldJvRrDCbjNcw34IPbmz9kKbfWoew</t>
+          <t>hV82vumYBf6BRTmLMntedEkZ1kk2pf</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Karoo Ale</t>
+          <t>Swart bier 2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9158,71 +9154,75 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-25ba5c7007d</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>dVHriCxcQvFiRnK1pq8TNs8Aop6maI</t>
+          <t>1J9fe3tUex3oOKOPk0F51aZTCC6NvP</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 684000000, "_seconds": 1777108192}</t>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1785061179}</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1777108192684</v>
+        <v>1785061179983</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.9</v>
+        <v>61</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X66" t="b">
         <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>7.8</v>
+        <v>1.31</v>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>GoldSwaen Classic</t>
         </is>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
+        </is>
+      </c>
       <c r="AG66" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH66" t="n">
-        <v>73.95999999999999</v>
+        <v>3.13</v>
       </c>
       <c r="AI66" t="n">
-        <v>1.0368</v>
+        <v>1.034</v>
       </c>
       <c r="AJ66" t="n">
-        <v>80</v>
+        <v>73.9130435</v>
       </c>
       <c r="AL66" t="inlineStr"/>
       <c r="AM66" t="inlineStr">
@@ -9238,9 +9238,7 @@
       <c r="AO66" t="inlineStr"/>
       <c r="AP66" t="inlineStr"/>
       <c r="AQ66" t="inlineStr"/>
-      <c r="AR66" t="b">
-        <v>0</v>
-      </c>
+      <c r="AR66" t="inlineStr"/>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr"/>
     </row>
@@ -9262,52 +9260,52 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
+          <t>dVHriCxcQvFiRnK1pq8TNs8Aop6maI</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 684000000, "_seconds": 1777108192}</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1781339591852</v>
+        <v>1777108192684</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q67" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X67" t="b">
         <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.85</v>
+        <v>7.8</v>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE67" t="b">
@@ -9320,13 +9318,13 @@
         </is>
       </c>
       <c r="AH67" t="n">
-        <v>14.79</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="AI67" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ67" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL67" t="inlineStr"/>
       <c r="AM67" t="inlineStr">
@@ -9342,7 +9340,9 @@
       <c r="AO67" t="inlineStr"/>
       <c r="AP67" t="inlineStr"/>
       <c r="AQ67" t="inlineStr"/>
-      <c r="AR67" t="inlineStr"/>
+      <c r="AR67" t="b">
+        <v>0</v>
+      </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr"/>
     </row>
@@ -9364,26 +9364,26 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>wqxhntH7cVkHGBGQHdmwHvGQQ8QOhy</t>
+          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 50000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1781339591050</v>
+        <v>1781339591852</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -9391,42 +9391,25 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="P68" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q68" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S68" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U68" t="n">
-        <v>80</v>
-      </c>
-      <c r="V68" t="n">
-        <v>80</v>
+        <v>5.1</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X68" t="b">
         <v>0</v>
       </c>
-      <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>4.6</v>
+        <v>2.85</v>
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE68" t="b">
@@ -9439,16 +9422,13 @@
         </is>
       </c>
       <c r="AH68" t="n">
-        <v>8.880000000000001</v>
+        <v>14.79</v>
       </c>
       <c r="AI68" t="n">
-        <v>1.035</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ68" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK68" t="n">
-        <v>11.7</v>
+        <v>78</v>
       </c>
       <c r="AL68" t="inlineStr"/>
       <c r="AM68" t="inlineStr">
@@ -9486,75 +9466,91 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>default-25ba5c7007d</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>rvKpzQzk7zcFyo8SUDwJClJQhEMsUP</t>
+          <t>wqxhntH7cVkHGBGQHdmwHvGQQ8QOhy</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 305000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 50000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1776345994305</v>
+        <v>1781339591050</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0.08</v>
+        <v>0.3</v>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="P69" t="n">
+        <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>61</v>
+        <v>6.6</v>
+      </c>
+      <c r="S69" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>80</v>
+      </c>
+      <c r="V69" t="n">
+        <v>80</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X69" t="b">
         <v>0</v>
       </c>
+      <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="n">
-        <v>2</v>
+        <v>2.54</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>4.6</v>
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>GoldSwaen Classic</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr">
-        <is>
-          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
-        </is>
-      </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH69" t="n">
-        <v>2.37</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AI69" t="n">
-        <v>1.034</v>
+        <v>1.035</v>
       </c>
       <c r="AJ69" t="n">
-        <v>73.9130435</v>
+        <v>75.37</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>11.7</v>
       </c>
       <c r="AL69" t="inlineStr"/>
       <c r="AM69" t="inlineStr">
@@ -9577,12 +9573,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>yiPSN3Y6mmATMzlZ26e4uWlmbGRxaD</t>
+          <t>jldJvRrDCbjNcw34IPbmz9kKbfWoew</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>Karoo Ale</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9592,71 +9588,75 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-25ba5c7007d</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>tqtVycoLMiKmJMplyu7GCIAsAeeETL</t>
+          <t>rvKpzQzk7zcFyo8SUDwJClJQhEMsUP</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 476000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 305000000, "_seconds": 1776345994}</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1781339591476</v>
+        <v>1776345994305</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.3</v>
+        <v>0.08</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.9</v>
+        <v>61</v>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X70" t="b">
         <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>6.7</v>
+        <v>2</v>
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>GoldSwaen Classic</t>
         </is>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
+        </is>
+      </c>
       <c r="AG70" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH70" t="n">
-        <v>73.02</v>
+        <v>2.37</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.0368</v>
+        <v>1.034</v>
       </c>
       <c r="AJ70" t="n">
-        <v>80</v>
+        <v>73.9130435</v>
       </c>
       <c r="AL70" t="inlineStr"/>
       <c r="AM70" t="inlineStr">
@@ -9694,26 +9694,26 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
+          <t>tqtVycoLMiKmJMplyu7GCIAsAeeETL</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 476000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1781339591852</v>
+        <v>1781339591476</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -9721,25 +9721,25 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q71" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X71" t="b">
         <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>2.85</v>
+        <v>6.7</v>
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE71" t="b">
@@ -9752,13 +9752,13 @@
         </is>
       </c>
       <c r="AH71" t="n">
-        <v>14.29</v>
+        <v>73.02</v>
       </c>
       <c r="AI71" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ71" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL71" t="inlineStr"/>
       <c r="AM71" t="inlineStr">
@@ -9796,26 +9796,26 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>wqxhntH7cVkHGBGQHdmwHvGQQ8QOhy</t>
+          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 50000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1781339591050</v>
+        <v>1781339591852</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -9823,42 +9823,25 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="M72" t="inlineStr"/>
-      <c r="P72" t="n">
-        <v>1</v>
+        <v>0.45</v>
       </c>
       <c r="Q72" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S72" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U72" t="n">
-        <v>80</v>
-      </c>
-      <c r="V72" t="n">
-        <v>80</v>
+        <v>5.1</v>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X72" t="b">
         <v>0</v>
       </c>
-      <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AC72" t="n">
-        <v>4.6</v>
+        <v>2.85</v>
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE72" t="b">
@@ -9871,16 +9854,13 @@
         </is>
       </c>
       <c r="AH72" t="n">
-        <v>11.11</v>
+        <v>14.29</v>
       </c>
       <c r="AI72" t="n">
-        <v>1.035</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ72" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK72" t="n">
-        <v>11.7</v>
+        <v>78</v>
       </c>
       <c r="AL72" t="inlineStr"/>
       <c r="AM72" t="inlineStr">
@@ -9918,26 +9898,26 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>default-25ba5c7007d</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>lBdAIVmlcp7FjYPSV55HleXloB6alW</t>
+          <t>wqxhntH7cVkHGBGQHdmwHvGQQ8QOhy</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 491000000, "_seconds": 1781339589}</t>
+          <t>{"_nanoseconds": 50000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1781339589491</v>
+        <v>1781339591050</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -9945,48 +9925,64 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0.05</v>
+        <v>0.35</v>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="P73" t="n">
+        <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>61</v>
+        <v>6.6</v>
+      </c>
+      <c r="S73" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>80</v>
+      </c>
+      <c r="V73" t="n">
+        <v>80</v>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X73" t="b">
         <v>0</v>
       </c>
+      <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="n">
-        <v>1.36</v>
+        <v>2.54</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>4.6</v>
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>GoldSwaen Classic</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr">
-        <is>
-          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
-        </is>
-      </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH73" t="n">
-        <v>1.59</v>
+        <v>11.11</v>
       </c>
       <c r="AI73" t="n">
-        <v>1.034</v>
+        <v>1.035</v>
       </c>
       <c r="AJ73" t="n">
-        <v>73.9130435</v>
+        <v>75.37</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>11.7</v>
       </c>
       <c r="AL73" t="inlineStr"/>
       <c r="AM73" t="inlineStr">
@@ -10009,12 +10005,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
+          <t>yiPSN3Y6mmATMzlZ26e4uWlmbGRxaD</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>First lager</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10022,52 +10018,54 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>default-HM41QfsZjsnkL2GS5s3sTYkVX5OKSM</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="n">
-        <v>0</v>
+          <t>default-25ba5c7007d</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>lBdAIVmlcp7FjYPSV55HleXloB6alW</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 491000000, "_seconds": 1781339589}</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>1781339589491</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
       </c>
       <c r="L74" t="n">
-        <v>3</v>
-      </c>
-      <c r="M74" t="inlineStr"/>
-      <c r="P74" t="n">
-        <v>1.5</v>
+        <v>0.05</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.8527919</v>
-      </c>
-      <c r="S74" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X74" t="b">
         <v>0</v>
       </c>
-      <c r="Y74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB74" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC74" t="n">
-        <v>4.5</v>
+      <c r="Z74" t="n">
+        <v>1.36</v>
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>Clear Choice Malt ® Extra Pale</t>
+          <t>GoldSwaen Classic</t>
         </is>
       </c>
       <c r="AE74" t="b">
@@ -10075,30 +10073,27 @@
       </c>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>Clear Choice Malt ® does not contain polyphenols thus reducing the risk of haze formation, increasing shelf life and reducing cold conditioning costs</t>
+          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
         </is>
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH74" t="n">
-        <v>68.18000000000001</v>
+        <v>1.59</v>
       </c>
       <c r="AI74" t="n">
-        <v>1.038</v>
+        <v>1.034</v>
       </c>
       <c r="AJ74" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="AK74" t="n">
-        <v>10.1</v>
+        <v>73.9130435</v>
       </c>
       <c r="AL74" t="inlineStr"/>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
@@ -10132,7 +10127,7 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>default-x1sQkldAFEgNTfYCHtBq70SjihT1F8</t>
+          <t>default-HM41QfsZjsnkL2GS5s3sTYkVX5OKSM</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -10143,21 +10138,21 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M75" t="inlineStr"/>
       <c r="P75" t="n">
         <v>1.5</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.9593909</v>
+        <v>1.8527919</v>
       </c>
       <c r="S75" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X75" t="b">
@@ -10174,7 +10169,7 @@
       </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>Vienna Malt</t>
+          <t>Clear Choice Malt ® Extra Pale</t>
         </is>
       </c>
       <c r="AE75" t="b">
@@ -10182,7 +10177,7 @@
       </c>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>Vienna malt is produced on a conventional kiln and provides a light golden hue</t>
+          <t>Clear Choice Malt ® does not contain polyphenols thus reducing the risk of haze formation, increasing shelf life and reducing cold conditioning costs</t>
         </is>
       </c>
       <c r="AG75" t="inlineStr">
@@ -10191,16 +10186,16 @@
         </is>
       </c>
       <c r="AH75" t="n">
-        <v>22.73</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="AI75" t="n">
-        <v>1.037</v>
+        <v>1.038</v>
       </c>
       <c r="AJ75" t="n">
-        <v>80</v>
+        <v>81.5</v>
       </c>
       <c r="AK75" t="n">
-        <v>9.6</v>
+        <v>10.1</v>
       </c>
       <c r="AL75" t="inlineStr"/>
       <c r="AM75" t="inlineStr">
@@ -10236,75 +10231,83 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>default-sabmjufsad</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>TbX832JbWp5BHVi5ATe4AaXk3nMfr9</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
-        </is>
-      </c>
-      <c r="I76" t="n">
-        <v>1706434202728</v>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>2.10.5</t>
-        </is>
+          <t>default-x1sQkldAFEgNTfYCHtBq70SjihT1F8</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="n">
+        <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0.3</v>
+        <v>1</v>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="P76" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q76" t="n">
-        <v>2</v>
+        <v>3.9593909</v>
+      </c>
+      <c r="S76" t="n">
+        <v>50</v>
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base (Vienna)</t>
         </is>
       </c>
       <c r="X76" t="b">
         <v>0</v>
       </c>
-      <c r="Z76" t="n">
-        <v>-2.29</v>
+      <c r="Y76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>4.5</v>
       </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>Pale Malt 2-Row</t>
+          <t>Vienna Malt</t>
         </is>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>Vienna malt is produced on a conventional kiln and provides a light golden hue</t>
+        </is>
+      </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH76" t="n">
-        <v>6.82</v>
+        <v>22.73</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.036</v>
+        <v>1.037</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>9.6</v>
       </c>
       <c r="AL76" t="inlineStr"/>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>Crisp</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
@@ -10315,9 +10318,7 @@
       <c r="AO76" t="inlineStr"/>
       <c r="AP76" t="inlineStr"/>
       <c r="AQ76" t="inlineStr"/>
-      <c r="AR76" t="b">
-        <v>0</v>
-      </c>
+      <c r="AR76" t="inlineStr"/>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr"/>
     </row>
@@ -10339,108 +10340,73 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 526000000, "_seconds": 1706434203}</t>
+          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>default-4c1345c</t>
+          <t>default-sabmjufsad</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>KAv9WQAuhq3uEgowTzBf8YrHtXE4LO</t>
+          <t>TbX832JbWp5BHVi5ATe4AaXk3nMfr9</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 140000000, "_seconds": 1712314604}</t>
+          <t>{"_nanoseconds": 728000000, "_seconds": 1706434202}</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1712314604140</v>
+        <v>1706434202728</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2.10.6</t>
-        </is>
-      </c>
-      <c r="K77" t="n">
+          <t>2.10.5</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q77" t="n">
         <v>2</v>
       </c>
-      <c r="L77" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="P77" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S77" t="n">
-        <v>0</v>
-      </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>Acidulated</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="X77" t="b">
         <v>0</v>
       </c>
-      <c r="Y77" t="n">
-        <v>0</v>
-      </c>
       <c r="Z77" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="AB77" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC77" t="n">
-        <v>4</v>
+        <v>-2.29</v>
       </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>Acidulated</t>
+          <t>Pale Malt 2-Row</t>
         </is>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr">
-        <is>
-          <t>Used in Germany to lower PH levels without resorting to chemicals. Lowers mash pH levels, lightens color, improves flavor stability.</t>
-        </is>
-      </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="AH77" t="n">
-        <v>2.27</v>
+        <v>6.82</v>
       </c>
       <c r="AI77" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AJ77" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="AK77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL77" t="inlineStr">
-        <is>
-          <t>Pale Liquid Extract</t>
-        </is>
-      </c>
+        <v>1.036</v>
+      </c>
+      <c r="AL77" t="inlineStr"/>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
@@ -10451,19 +10417,21 @@
       <c r="AO77" t="inlineStr"/>
       <c r="AP77" t="inlineStr"/>
       <c r="AQ77" t="inlineStr"/>
-      <c r="AR77" t="inlineStr"/>
+      <c r="AR77" t="b">
+        <v>0</v>
+      </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
+          <t>zLftyphr8T4DoHNZs92dj1mO4gPXZq</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Smash - Citra</t>
+          <t>First lager</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10471,69 +10439,110 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 526000000, "_seconds": 1706434203}</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>new-eNDTHs2wb879roS3Dq1orvcb3ATgbD</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+          <t>default-4c1345c</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>KAv9WQAuhq3uEgowTzBf8YrHtXE4LO</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 140000000, "_seconds": 1712314604}</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>1712314604140</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>2</v>
+      </c>
       <c r="L78" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="P78" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q78" t="n">
-        <v>3</v>
-      </c>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>Base (Maris Otter)</t>
-        </is>
-      </c>
-      <c r="X78" t="inlineStr"/>
-      <c r="Y78" t="inlineStr"/>
-      <c r="Z78" t="inlineStr"/>
-      <c r="AA78" t="inlineStr"/>
-      <c r="AB78" t="inlineStr"/>
-      <c r="AC78" t="inlineStr"/>
+          <t>Acidulated</t>
+        </is>
+      </c>
+      <c r="X78" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>4</v>
+      </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>Pale Malt, Maris Otter</t>
-        </is>
-      </c>
-      <c r="AE78" t="inlineStr"/>
-      <c r="AF78" t="inlineStr"/>
+          <t>Acidulated</t>
+        </is>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>Used in Germany to lower PH levels without resorting to chemicals. Lowers mash pH levels, lightens color, improves flavor stability.</t>
+        </is>
+      </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH78" t="n">
-        <v>100</v>
+        <v>2.27</v>
       </c>
       <c r="AI78" t="n">
-        <v>1.03795</v>
+        <v>1.03</v>
       </c>
       <c r="AJ78" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="AK78" t="inlineStr"/>
-      <c r="AL78" t="inlineStr"/>
+        <v>65.2</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL78" t="inlineStr">
+        <is>
+          <t>Pale Liquid Extract</t>
+        </is>
+      </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>Maris Otter</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
@@ -10546,21 +10555,17 @@
       <c r="AQ78" t="inlineStr"/>
       <c r="AR78" t="inlineStr"/>
       <c r="AS78" t="inlineStr"/>
-      <c r="AT78" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
+      <c r="AT78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
+          <t>ldKgMhTaCxdOMCepRg4HaR2lskjbXE</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Saison</t>
+          <t>Smash - Citra</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10568,78 +10573,69 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>tqtVycoLMiKmJMplyu7GCIAsAeeETL</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 476000000, "_seconds": 1781339591}</t>
-        </is>
-      </c>
-      <c r="I79" t="n">
-        <v>1781339591476</v>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
+          <t>new-eNDTHs2wb879roS3Dq1orvcb3ATgbD</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="n">
-        <v>2.4</v>
-      </c>
+        <v>13.18</v>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
       <c r="Q79" t="n">
-        <v>1.9</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
       <c r="W79" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
-        </is>
-      </c>
-      <c r="X79" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>6.7</v>
-      </c>
+          <t>Base (Maris Otter)</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="inlineStr"/>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
-        </is>
-      </c>
-      <c r="AE79" t="b">
-        <v>0</v>
-      </c>
+          <t>Pale Malt, Maris Otter</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH79" t="n">
-        <v>78.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="AI79" t="n">
-        <v>1.0368</v>
+        <v>1.03795</v>
       </c>
       <c r="AJ79" t="n">
-        <v>80</v>
-      </c>
+        <v>82.5</v>
+      </c>
+      <c r="AK79" t="inlineStr"/>
       <c r="AL79" t="inlineStr"/>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Maris Otter</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
@@ -10652,7 +10648,11 @@
       <c r="AQ79" t="inlineStr"/>
       <c r="AR79" t="inlineStr"/>
       <c r="AS79" t="inlineStr"/>
-      <c r="AT79" t="inlineStr"/>
+      <c r="AT79" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -10672,26 +10672,26 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>default-d9e04639a2c</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
+          <t>tqtVycoLMiKmJMplyu7GCIAsAeeETL</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
+          <t>{"_nanoseconds": 476000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1781339591852</v>
+        <v>1781339591476</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -10699,25 +10699,25 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q80" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>Base (Vienna)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X80" t="b">
         <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>2.85</v>
+        <v>6.7</v>
       </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>Swaen Vienna</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE80" t="b">
@@ -10730,13 +10730,13 @@
         </is>
       </c>
       <c r="AH80" t="n">
-        <v>11.07</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="AI80" t="n">
-        <v>1.03588</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ80" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL80" t="inlineStr"/>
       <c r="AM80" t="inlineStr">
@@ -10774,71 +10774,81 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 526000000, "_seconds": 1719746358}</t>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1775498604}</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>default-132c22b</t>
+          <t>default-d9e04639a2c</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>feD3na0a4sxySPUBRKwyBrSewo4G5I</t>
+          <t>zNojkfDZoro1z7t7fMQtUDJKvZGT6s</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 383000000, "_seconds": 1772634460}</t>
+          <t>{"_nanoseconds": 852000000, "_seconds": 1781339591}</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1772634460383</v>
+        <v>1781339591852</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2.20.2</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="M81" t="n">
-        <v>1.22</v>
+        <v>0.34</v>
       </c>
       <c r="Q81" t="n">
-        <v>1</v>
+        <v>5.1</v>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Base (Vienna)</t>
+        </is>
       </c>
       <c r="X81" t="b">
         <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>Sugar, Table (Sucrose)</t>
+          <t>Swaen Vienna</t>
         </is>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
       <c r="AF81" t="inlineStr"/>
-      <c r="AG81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
       <c r="AH81" t="n">
-        <v>6.84</v>
+        <v>11.07</v>
       </c>
       <c r="AI81" t="n">
-        <v>1.046</v>
+        <v>1.03588</v>
       </c>
       <c r="AJ81" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AL81" t="inlineStr"/>
-      <c r="AM81" t="inlineStr"/>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>The Swaen</t>
+        </is>
+      </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Grain</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr"/>
@@ -10866,101 +10876,71 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
+          <t>{"_nanoseconds": 526000000, "_seconds": 1719746358}</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-132c22b</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>yKptvZxfGwlhwsenw2CQpv3yu9A5Qm</t>
+          <t>feD3na0a4sxySPUBRKwyBrSewo4G5I</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 905000000, "_seconds": 1785061180}</t>
+          <t>{"_nanoseconds": 383000000, "_seconds": 1772634460}</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1785061180905</v>
+        <v>1772634460383</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>2.20.2</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="M82" t="inlineStr"/>
-      <c r="P82" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Q82" t="n">
         <v>1</v>
       </c>
-      <c r="Q82" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S82" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U82" t="n">
-        <v>80</v>
-      </c>
-      <c r="V82" t="n">
-        <v>80</v>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Base (Munich)</t>
-        </is>
-      </c>
       <c r="X82" t="b">
         <v>0</v>
       </c>
-      <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AC82" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Sugar, Table (Sucrose)</t>
         </is>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
       <c r="AF82" t="inlineStr"/>
-      <c r="AG82" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
+      <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="n">
-        <v>3.58</v>
+        <v>6.84</v>
       </c>
       <c r="AI82" t="n">
-        <v>1.035</v>
+        <v>1.046</v>
       </c>
       <c r="AJ82" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK82" t="n">
-        <v>11.7</v>
+        <v>100</v>
       </c>
       <c r="AL82" t="inlineStr"/>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>The Swaen</t>
-        </is>
-      </c>
+      <c r="AM82" t="inlineStr"/>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>Grain</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr"/>
@@ -10988,102 +10968,96 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 545000000, "_seconds": 1775499034}</t>
+          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>default-b5ffdd1</t>
+          <t>default-c454dca637a</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Vhg3sieJEyft7qzQj4l2FF66e2XbYO</t>
+          <t>yKptvZxfGwlhwsenw2CQpv3yu9A5Qm</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 329000000, "_seconds": 1781339592}</t>
+          <t>{"_nanoseconds": 905000000, "_seconds": 1785061180}</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1781339592329</v>
+        <v>1785061180905</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
           <t>3.0.1</t>
         </is>
       </c>
-      <c r="K83" t="n">
-        <v>0</v>
-      </c>
       <c r="L83" t="n">
-        <v>0.01</v>
+        <v>0.11</v>
       </c>
       <c r="M83" t="inlineStr"/>
       <c r="P83" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q83" t="n">
-        <v>558.375635</v>
+        <v>6.6</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>18.2</v>
+      </c>
+      <c r="U83" t="n">
+        <v>80</v>
+      </c>
+      <c r="V83" t="n">
+        <v>80</v>
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>Roasted</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X83" t="b">
         <v>0</v>
       </c>
-      <c r="Y83" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="AB83" t="n">
-        <v>5</v>
+        <v>2.19</v>
       </c>
       <c r="AC83" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>Carafa Special II</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr">
-        <is>
-          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
-        </is>
-      </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH83" t="n">
-        <v>0.33</v>
+        <v>3.58</v>
       </c>
       <c r="AI83" t="n">
-        <v>1.036</v>
+        <v>1.035</v>
       </c>
       <c r="AJ83" t="n">
-        <v>77.90000000000001</v>
+        <v>75.37</v>
       </c>
       <c r="AK83" t="n">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="AL83" t="inlineStr"/>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>Weyermann</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
@@ -11093,9 +11067,7 @@
       </c>
       <c r="AO83" t="inlineStr"/>
       <c r="AP83" t="inlineStr"/>
-      <c r="AQ83" t="n">
-        <v>412.8</v>
-      </c>
+      <c r="AQ83" t="inlineStr"/>
       <c r="AR83" t="inlineStr"/>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr"/>
@@ -11103,12 +11075,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
+          <t>6uXxDtvdy8UOY2sOfjUUUeSVldFbeu</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Smash Mosaic</t>
+          <t>Saison</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11118,76 +11090,102 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+          <t>{"_nanoseconds": 545000000, "_seconds": 1775499034}</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-b5ffdd1</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>BglUUy5uFFFvFjGd9EbIYIPvAJyyIE</t>
+          <t>Vhg3sieJEyft7qzQj4l2FF66e2XbYO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 508000000, "_seconds": 1785061181}</t>
+          <t>{"_nanoseconds": 329000000, "_seconds": 1781339592}</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1785061181508</v>
+        <v>1781339592329</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
           <t>3.0.1</t>
         </is>
       </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
       <c r="L84" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="P84" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>558.375635</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Roasted</t>
+        </is>
+      </c>
+      <c r="X84" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC84" t="n">
         <v>3</v>
       </c>
-      <c r="Q84" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>Base (Pilsner)</t>
-        </is>
-      </c>
-      <c r="X84" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z84" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AD84" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>Carafa Special II</t>
         </is>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
+        </is>
+      </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="AH84" t="n">
-        <v>100</v>
+        <v>0.33</v>
       </c>
       <c r="AI84" t="n">
-        <v>1.0368</v>
+        <v>1.036</v>
       </c>
       <c r="AJ84" t="n">
-        <v>80</v>
+        <v>77.90000000000001</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>10</v>
       </c>
       <c r="AL84" t="inlineStr"/>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Weyermann</t>
         </is>
       </c>
       <c r="AN84" t="inlineStr">
@@ -11197,7 +11195,9 @@
       </c>
       <c r="AO84" t="inlineStr"/>
       <c r="AP84" t="inlineStr"/>
-      <c r="AQ84" t="inlineStr"/>
+      <c r="AQ84" t="n">
+        <v>412.8</v>
+      </c>
       <c r="AR84" t="inlineStr"/>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr"/>
@@ -11205,12 +11205,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>dXad4F2tnZ5bYPr0H7o1LxG5LkDq1C</t>
+          <t>rJhcyGonoBkZSA8onOHB3KYOWjvOFo</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Smash shoddy</t>
+          <t>Smash Mosaic</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11307,12 +11307,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TtkyFZuS1krih6K7d2BW7nY3qFmYPZ</t>
+          <t>dXad4F2tnZ5bYPr0H7o1LxG5LkDq1C</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kalahari blond</t>
+          <t>Smash shoddy</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11332,16 +11332,16 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>GOG6rzO2xrYYSto1fMsaU5lUVzV9v7</t>
+          <t>BglUUy5uFFFvFjGd9EbIYIPvAJyyIE</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 7000000, "_seconds": 1786789728}</t>
+          <t>{"_nanoseconds": 508000000, "_seconds": 1785061181}</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1786789728007</v>
+        <v>1785061181508</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="Q86" t="n">
         <v>1.9</v>
@@ -11363,7 +11363,7 @@
         <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>11.4</v>
+        <v>4.4</v>
       </c>
       <c r="AD86" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         </is>
       </c>
       <c r="AH86" t="n">
-        <v>79.37</v>
+        <v>100</v>
       </c>
       <c r="AI86" t="n">
         <v>1.0368</v>
@@ -11424,26 +11424,26 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>default-c454dca637a</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>8RBzx8WZSkSmbLLiWSJhSrf0Ak2Trz</t>
+          <t>GOG6rzO2xrYYSto1fMsaU5lUVzV9v7</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 681000000, "_seconds": 1788086444}</t>
+          <t>{"_nanoseconds": 7000000, "_seconds": 1786789728}</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1788086444681</v>
+        <v>1786789728007</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -11451,42 +11451,25 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="M87" t="inlineStr"/>
-      <c r="P87" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="Q87" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S87" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="U87" t="n">
-        <v>80</v>
-      </c>
-      <c r="V87" t="n">
-        <v>80</v>
+        <v>1.9</v>
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>Base (Munich)</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X87" t="b">
         <v>0</v>
       </c>
-      <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC87" t="n">
-        <v>4.6</v>
+        <v>11.4</v>
       </c>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>Swaen Munich Light</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE87" t="b">
@@ -11499,16 +11482,13 @@
         </is>
       </c>
       <c r="AH87" t="n">
-        <v>14.29</v>
+        <v>79.37</v>
       </c>
       <c r="AI87" t="n">
-        <v>1.035</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ87" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="AK87" t="n">
-        <v>11.7</v>
+        <v>80</v>
       </c>
       <c r="AL87" t="inlineStr"/>
       <c r="AM87" t="inlineStr">
@@ -11544,83 +11524,98 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 835000000, "_seconds": 1775498551}</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>default-MSMYXD2BJLGqRAHlZVbqdHLIa0VzoF</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="n">
-        <v>0</v>
+          <t>default-c454dca637a</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>8RBzx8WZSkSmbLLiWSJhSrf0Ak2Trz</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 681000000, "_seconds": 1788086444}</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>1788086444681</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
       </c>
       <c r="L88" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="M88" t="inlineStr"/>
       <c r="P88" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.5380711</v>
+        <v>6.6</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>18.2</v>
+      </c>
+      <c r="U88" t="n">
+        <v>80</v>
+      </c>
+      <c r="V88" t="n">
+        <v>80</v>
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>Base (Wheat)</t>
+          <t>Base (Munich)</t>
         </is>
       </c>
       <c r="X88" t="b">
         <v>0</v>
       </c>
-      <c r="Y88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB88" t="n">
-        <v>25</v>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="n">
+        <v>2.04</v>
       </c>
       <c r="AC88" t="n">
-        <v>10</v>
+        <v>4.6</v>
       </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>Torrefied Wheat</t>
+          <t>Swaen Munich Light</t>
         </is>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr">
-        <is>
-          <t>Pre-cooked, non-malted cereals provide the brewer with the opportunity for product differentiation. Flaked products can be added directly to the mash without the need for milling.</t>
-        </is>
-      </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH88" t="n">
-        <v>6.35</v>
+        <v>14.29</v>
       </c>
       <c r="AI88" t="n">
-        <v>1.038</v>
+        <v>1.035</v>
       </c>
       <c r="AJ88" t="n">
-        <v>82</v>
+        <v>75.37</v>
       </c>
       <c r="AK88" t="n">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="AL88" t="inlineStr"/>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
@@ -11638,12 +11633,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3IHDxeB1SX3QaLERATIxYhFsnmvLZZ</t>
+          <t>TtkyFZuS1krih6K7d2BW7nY3qFmYPZ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Old English Summer Stout</t>
+          <t>Kalahari blond</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11651,53 +11646,35 @@
           <t>Fermentable</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 499000000, "_seconds": 1706434201}</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>default-e6ba5b8</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>OTZvOBRODuXjmguhpWZUQ4uz2r8zid</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>{"_nanoseconds": 714000000, "_seconds": 1721546982}</t>
-        </is>
-      </c>
-      <c r="I89" t="n">
-        <v>1721546982714</v>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>2.10.6</t>
-        </is>
-      </c>
+          <t>default-MSMYXD2BJLGqRAHlZVbqdHLIa0VzoF</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="n">
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="M89" t="inlineStr"/>
       <c r="P89" t="n">
         <v>1.5</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.2994924</v>
+        <v>2.5380711</v>
       </c>
       <c r="S89" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>Base (Maris Otter)</t>
+          <t>Base (Wheat)</t>
         </is>
       </c>
       <c r="X89" t="b">
@@ -11706,18 +11683,15 @@
       <c r="Y89" t="n">
         <v>0</v>
       </c>
-      <c r="Z89" t="n">
-        <v>-4.59</v>
-      </c>
       <c r="AB89" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="AC89" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="AD89" t="inlineStr">
         <is>
-          <t>Finest Maris Otter® Ale Malt</t>
+          <t>Torrefied Wheat</t>
         </is>
       </c>
       <c r="AE89" t="b">
@@ -11725,7 +11699,7 @@
       </c>
       <c r="AF89" t="inlineStr">
         <is>
-          <t>The consistently reliable Maris Otter® continues to provide the qualities expected by the brewer</t>
+          <t>Pre-cooked, non-malted cereals provide the brewer with the opportunity for product differentiation. Flaked products can be added directly to the mash without the need for milling.</t>
         </is>
       </c>
       <c r="AG89" t="inlineStr">
@@ -11734,16 +11708,16 @@
         </is>
       </c>
       <c r="AH89" t="n">
-        <v>75</v>
+        <v>6.35</v>
       </c>
       <c r="AI89" t="n">
         <v>1.038</v>
       </c>
       <c r="AJ89" t="n">
-        <v>81.5</v>
+        <v>82</v>
       </c>
       <c r="AK89" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL89" t="inlineStr"/>
       <c r="AM89" t="inlineStr">
@@ -11781,51 +11755,51 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 14000000, "_seconds": 1787844774}</t>
+          <t>{"_nanoseconds": 499000000, "_seconds": 1706434201}</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>default-MSMYXD2BJLGqRAHlZVbqdHLIa0VzoF</t>
+          <t>default-e6ba5b8</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>RfTzDOwr83mMgEx7DXAJqSmiTnkaet</t>
+          <t>OTZvOBRODuXjmguhpWZUQ4uz2r8zid</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 14000000, "_seconds": 1787844774}</t>
+          <t>{"_nanoseconds": 714000000, "_seconds": 1721546982}</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1787844774014</v>
+        <v>1721546982714</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>2.10.6</t>
         </is>
       </c>
       <c r="K90" t="n">
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="M90" t="inlineStr"/>
       <c r="P90" t="n">
         <v>1.5</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.5380711</v>
+        <v>3.2994924</v>
       </c>
       <c r="S90" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>Base (Wheat)</t>
+          <t>Base (Maris Otter)</t>
         </is>
       </c>
       <c r="X90" t="b">
@@ -11835,17 +11809,17 @@
         <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1</v>
+        <v>-4.59</v>
       </c>
       <c r="AB90" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="AC90" t="n">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>Torrefied Wheat</t>
+          <t>Finest Maris Otter® Ale Malt</t>
         </is>
       </c>
       <c r="AE90" t="b">
@@ -11853,7 +11827,7 @@
       </c>
       <c r="AF90" t="inlineStr">
         <is>
-          <t>Pre-cooked, non-malted cereals provide the brewer with the opportunity for product differentiation. Flaked products can be added directly to the mash without the need for milling.</t>
+          <t>The consistently reliable Maris Otter® continues to provide the qualities expected by the brewer</t>
         </is>
       </c>
       <c r="AG90" t="inlineStr">
@@ -11862,16 +11836,16 @@
         </is>
       </c>
       <c r="AH90" t="n">
-        <v>12.5</v>
+        <v>75</v>
       </c>
       <c r="AI90" t="n">
         <v>1.038</v>
       </c>
       <c r="AJ90" t="n">
-        <v>82</v>
+        <v>81.5</v>
       </c>
       <c r="AK90" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL90" t="inlineStr"/>
       <c r="AM90" t="inlineStr">
@@ -11909,52 +11883,71 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+          <t>{"_nanoseconds": 14000000, "_seconds": 1787844774}</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>default-25ba5c7007d</t>
+          <t>default-MSMYXD2BJLGqRAHlZVbqdHLIa0VzoF</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>1J9fe3tUex3oOKOPk0F51aZTCC6NvP</t>
+          <t>RfTzDOwr83mMgEx7DXAJqSmiTnkaet</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 983000000, "_seconds": 1785061179}</t>
+          <t>{"_nanoseconds": 14000000, "_seconds": 1787844774}</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1785061179983</v>
+        <v>1787844774014</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
           <t>3.0.1</t>
         </is>
       </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
       <c r="L91" t="n">
-        <v>0.12</v>
+        <v>0.4</v>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="P91" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q91" t="n">
-        <v>61</v>
+        <v>2.5380711</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>Crystal/Caramel</t>
+          <t>Base (Wheat)</t>
         </is>
       </c>
       <c r="X91" t="b">
         <v>0</v>
       </c>
+      <c r="Y91" t="n">
+        <v>0</v>
+      </c>
       <c r="Z91" t="n">
-        <v>1.31</v>
+        <v>1</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>10</v>
       </c>
       <c r="AD91" t="inlineStr">
         <is>
-          <t>GoldSwaen Classic</t>
+          <t>Torrefied Wheat</t>
         </is>
       </c>
       <c r="AE91" t="b">
@@ -11962,27 +11955,30 @@
       </c>
       <c r="AF91" t="inlineStr">
         <is>
-          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
+          <t>Pre-cooked, non-malted cereals provide the brewer with the opportunity for product differentiation. Flaked products can be added directly to the mash without the need for milling.</t>
         </is>
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AH91" t="n">
-        <v>3.75</v>
+        <v>12.5</v>
       </c>
       <c r="AI91" t="n">
-        <v>1.034</v>
+        <v>1.038</v>
       </c>
       <c r="AJ91" t="n">
-        <v>73.9130435</v>
+        <v>82</v>
+      </c>
+      <c r="AK91" t="n">
+        <v>10</v>
       </c>
       <c r="AL91" t="inlineStr"/>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>The Swaen</t>
+          <t>Crisp</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
@@ -12015,26 +12011,26 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 593000000, "_seconds": 1776345977}</t>
+          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>default-29dda1b5335</t>
+          <t>default-25ba5c7007d</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>R3yyMXfk1baparTfJ2ej9HajPEgito</t>
+          <t>1J9fe3tUex3oOKOPk0F51aZTCC6NvP</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 919000000, "_seconds": 1781339588}</t>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1785061179}</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1781339588919</v>
+        <v>1785061179983</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -12042,10 +12038,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="Q92" t="n">
-        <v>329.949239</v>
+        <v>61</v>
       </c>
       <c r="W92" t="inlineStr">
         <is>
@@ -12056,30 +12052,34 @@
         <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>0.65</v>
+        <v>1.31</v>
       </c>
       <c r="AD92" t="inlineStr">
         <is>
-          <t>BlackSwaen Coffee</t>
+          <t>GoldSwaen Classic</t>
         </is>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
+        </is>
+      </c>
       <c r="AG92" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
       <c r="AH92" t="n">
-        <v>3.13</v>
+        <v>3.75</v>
       </c>
       <c r="AI92" t="n">
-        <v>1.028</v>
+        <v>1.034</v>
       </c>
       <c r="AJ92" t="n">
-        <v>60.8695652</v>
+        <v>73.9130435</v>
       </c>
       <c r="AL92" t="inlineStr"/>
       <c r="AM92" t="inlineStr">
@@ -12094,9 +12094,7 @@
       </c>
       <c r="AO92" t="inlineStr"/>
       <c r="AP92" t="inlineStr"/>
-      <c r="AQ92" t="n">
-        <v>244.1</v>
-      </c>
+      <c r="AQ92" t="inlineStr"/>
       <c r="AR92" t="inlineStr"/>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr"/>
@@ -12119,26 +12117,26 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
+          <t>{"_nanoseconds": 593000000, "_seconds": 1776345977}</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>default-c3ff8bb88f9</t>
+          <t>default-29dda1b5335</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ou91CMOYwCNfTOIWjNXLjhWUBAxN7m</t>
+          <t>R3yyMXfk1baparTfJ2ej9HajPEgito</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 244000000, "_seconds": 1788086445}</t>
+          <t>{"_nanoseconds": 919000000, "_seconds": 1781339588}</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1788086445244</v>
+        <v>1781339588919</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -12149,22 +12147,22 @@
         <v>0.1</v>
       </c>
       <c r="Q93" t="n">
-        <v>1.9</v>
+        <v>329.949239</v>
       </c>
       <c r="W93" t="inlineStr">
         <is>
-          <t>Base (Pilsner)</t>
+          <t>Crystal/Caramel</t>
         </is>
       </c>
       <c r="X93" t="b">
         <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>10.7</v>
+        <v>0.65</v>
       </c>
       <c r="AD93" t="inlineStr">
         <is>
-          <t>Swaen Pilsner</t>
+          <t>BlackSwaen Coffee</t>
         </is>
       </c>
       <c r="AE93" t="b">
@@ -12180,10 +12178,10 @@
         <v>3.13</v>
       </c>
       <c r="AI93" t="n">
-        <v>1.0368</v>
+        <v>1.028</v>
       </c>
       <c r="AJ93" t="n">
-        <v>80</v>
+        <v>60.8695652</v>
       </c>
       <c r="AL93" t="inlineStr"/>
       <c r="AM93" t="inlineStr">
@@ -12198,7 +12196,9 @@
       </c>
       <c r="AO93" t="inlineStr"/>
       <c r="AP93" t="inlineStr"/>
-      <c r="AQ93" t="inlineStr"/>
+      <c r="AQ93" t="n">
+        <v>244.1</v>
+      </c>
       <c r="AR93" t="inlineStr"/>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr"/>
@@ -12221,102 +12221,76 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 212000000, "_seconds": 1775499019}</t>
+          <t>{"_nanoseconds": 563000000, "_seconds": 1775498626}</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>default-c5e48c4</t>
+          <t>default-c3ff8bb88f9</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>9mGQgdZMjKAOZQSjsXo7x5DVWTbPaC</t>
+          <t>Ou91CMOYwCNfTOIWjNXLjhWUBAxN7m</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 714000000, "_seconds": 1777108185}</t>
+          <t>{"_nanoseconds": 244000000, "_seconds": 1788086445}</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1777108185714</v>
+        <v>1788086445244</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>3.0.0</t>
-        </is>
-      </c>
-      <c r="K94" t="n">
-        <v>0</v>
+          <t>3.0.1</t>
+        </is>
       </c>
       <c r="L94" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="M94" t="inlineStr"/>
-      <c r="P94" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="Q94" t="n">
-        <v>529.4416244</v>
-      </c>
-      <c r="S94" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>Roasted</t>
+          <t>Base (Pilsner)</t>
         </is>
       </c>
       <c r="X94" t="b">
         <v>0</v>
       </c>
-      <c r="Y94" t="n">
-        <v>0</v>
-      </c>
       <c r="Z94" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AB94" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC94" t="n">
-        <v>2</v>
+        <v>10.7</v>
       </c>
       <c r="AD94" t="inlineStr">
         <is>
-          <t>Chocolate Malt</t>
+          <t>Swaen Pilsner</t>
         </is>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr">
-        <is>
-          <t>Gives dry, toasty flavours to rich, dark beers</t>
-        </is>
-      </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="AH94" t="n">
-        <v>2.5</v>
+        <v>3.13</v>
       </c>
       <c r="AI94" t="n">
-        <v>1.033</v>
+        <v>1.0368</v>
       </c>
       <c r="AJ94" t="n">
-        <v>72</v>
-      </c>
-      <c r="AK94" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="AL94" t="inlineStr"/>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>Crisp</t>
+          <t>The Swaen</t>
         </is>
       </c>
       <c r="AN94" t="inlineStr">
@@ -12331,8 +12305,136 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr"/>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>3IHDxeB1SX3QaLERATIxYhFsnmvLZZ</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Old English Summer Stout</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 212000000, "_seconds": 1775499019}</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>default-c5e48c4</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>9mGQgdZMjKAOZQSjsXo7x5DVWTbPaC</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 714000000, "_seconds": 1777108185}</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>1777108185714</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>3.0.0</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="P95" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>529.4416244</v>
+      </c>
+      <c r="S95" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Roasted</t>
+        </is>
+      </c>
+      <c r="X95" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>Chocolate Malt</t>
+        </is>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>Gives dry, toasty flavours to rich, dark beers</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="AH95" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI95" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="AJ95" t="n">
+        <v>72</v>
+      </c>
+      <c r="AK95" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL95" t="inlineStr"/>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>Crisp</t>
+        </is>
+      </c>
+      <c r="AN95" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr"/>
+      <c r="AP95" t="inlineStr"/>
+      <c r="AQ95" t="inlineStr"/>
+      <c r="AR95" t="inlineStr"/>
+      <c r="AS95" t="inlineStr"/>
+      <c r="AT95" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AT94"/>
+  <autoFilter ref="A1:AT95"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14703,7 +14805,7 @@
         <v>30</v>
       </c>
       <c r="Q23" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>

--- a/exports/Brewfather_Recipes_Summary.xlsx
+++ b/exports/Brewfather_Recipes_Summary.xlsx
@@ -14,11 +14,11 @@
     <sheet name="Misc" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recipes'!$A$1:$P$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$95</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hops'!$A$1:$AP$80</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Yeast'!$A$1:$AL$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Misc'!$A$1:$AB$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Recipes'!$A$1:$P$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fermentables'!$A$1:$AT$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hops'!$A$1:$AP$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Yeast'!$A$1:$AL$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Misc'!$A$1:$AB$152</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2158,8 +2158,68 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>xlBmZbXhzbuHWfN1GoclwNdsgM9yT6</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Summer stout </t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>English Porter</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>All Grain</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ernst Gouws</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>1.047430778</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>1.014</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>18.58</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P26"/>
+  <autoFilter ref="A1:P27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2170,7 +2230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT95"/>
+  <dimension ref="A1:AT101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -12433,8 +12493,662 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr"/>
     </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>xlBmZbXhzbuHWfN1GoclwNdsgM9yT6</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Summer stout </t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 499000000, "_seconds": 1706434201}</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>default-e6ba5b8</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>OTZvOBRODuXjmguhpWZUQ4uz2r8zid</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 714000000, "_seconds": 1721546982}</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>1721546982714</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2.10.6</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="P96" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>3.2994924</v>
+      </c>
+      <c r="S96" t="n">
+        <v>53</v>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Base (Maris Otter)</t>
+        </is>
+      </c>
+      <c r="X96" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>-4.59</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>Finest Maris Otter® Ale Malt</t>
+        </is>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>The consistently reliable Maris Otter® continues to provide the qualities expected by the brewer</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="AH96" t="n">
+        <v>84.18000000000001</v>
+      </c>
+      <c r="AI96" t="n">
+        <v>1.038</v>
+      </c>
+      <c r="AJ96" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="AK96" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL96" t="inlineStr"/>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>Crisp</t>
+        </is>
+      </c>
+      <c r="AN96" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr"/>
+      <c r="AP96" t="inlineStr"/>
+      <c r="AQ96" t="inlineStr"/>
+      <c r="AR96" t="inlineStr"/>
+      <c r="AS96" t="inlineStr"/>
+      <c r="AT96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>xlBmZbXhzbuHWfN1GoclwNdsgM9yT6</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Summer stout </t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>default-b5ffdd1</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="P97" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>558.375635</v>
+      </c>
+      <c r="S97" t="n">
+        <v>0</v>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Roasted</t>
+        </is>
+      </c>
+      <c r="X97" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>Carafa Special II</t>
+        </is>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>De-husked chocolate malt for a smoother flavor. Adds body, color, aroma. Dark beers, Alts, Bockbiers.</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="AH97" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AI97" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="AJ97" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="AK97" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL97" t="inlineStr"/>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>Weyermann</t>
+        </is>
+      </c>
+      <c r="AN97" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr"/>
+      <c r="AP97" t="inlineStr"/>
+      <c r="AQ97" t="n">
+        <v>412.8</v>
+      </c>
+      <c r="AR97" t="inlineStr"/>
+      <c r="AS97" t="inlineStr"/>
+      <c r="AT97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>xlBmZbXhzbuHWfN1GoclwNdsgM9yT6</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Summer stout </t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 306000000, "_seconds": 1776345994}</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>default-25ba5c7007d</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>1J9fe3tUex3oOKOPk0F51aZTCC6NvP</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 983000000, "_seconds": 1785061179}</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>1785061179983</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>61</v>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Crystal/Caramel</t>
+        </is>
+      </c>
+      <c r="X98" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>GoldSwaen Classic</t>
+        </is>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>5-10% for dark beers, 1-5% for light beer, Pale Ale 20%</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="AH98" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AI98" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="AJ98" t="n">
+        <v>73.9130435</v>
+      </c>
+      <c r="AL98" t="inlineStr"/>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>The Swaen</t>
+        </is>
+      </c>
+      <c r="AN98" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr"/>
+      <c r="AP98" t="inlineStr"/>
+      <c r="AQ98" t="inlineStr"/>
+      <c r="AR98" t="inlineStr"/>
+      <c r="AS98" t="inlineStr"/>
+      <c r="AT98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>xlBmZbXhzbuHWfN1GoclwNdsgM9yT6</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Summer stout </t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>default-d2c0778</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="L99" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr"/>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>Oats, Flaked</t>
+        </is>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AH99" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>1.0391</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL99" t="inlineStr"/>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>Briess</t>
+        </is>
+      </c>
+      <c r="AN99" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr"/>
+      <c r="AP99" t="inlineStr"/>
+      <c r="AQ99" t="inlineStr"/>
+      <c r="AR99" t="inlineStr"/>
+      <c r="AS99" t="inlineStr"/>
+      <c r="AT99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>xlBmZbXhzbuHWfN1GoclwNdsgM9yT6</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Summer stout </t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 212000000, "_seconds": 1775499019}</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>default-c5e48c4</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>9mGQgdZMjKAOZQSjsXo7x5DVWTbPaC</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 714000000, "_seconds": 1777108185}</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>1777108185714</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>3.0.0</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="P100" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>529.4416244</v>
+      </c>
+      <c r="S100" t="n">
+        <v>0</v>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Roasted</t>
+        </is>
+      </c>
+      <c r="X100" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>Chocolate Malt</t>
+        </is>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>Gives dry, toasty flavours to rich, dark beers</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="AH100" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>72</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL100" t="inlineStr"/>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Crisp</t>
+        </is>
+      </c>
+      <c r="AN100" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr"/>
+      <c r="AP100" t="inlineStr"/>
+      <c r="AQ100" t="inlineStr"/>
+      <c r="AR100" t="inlineStr"/>
+      <c r="AS100" t="inlineStr"/>
+      <c r="AT100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>xlBmZbXhzbuHWfN1GoclwNdsgM9yT6</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Summer stout </t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Fermentable</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 593000000, "_seconds": 1776345977}</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>default-29dda1b5335</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>R3yyMXfk1baparTfJ2ej9HajPEgito</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 919000000, "_seconds": 1781339588}</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>1781339588919</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>329.949239</v>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Crystal/Caramel</t>
+        </is>
+      </c>
+      <c r="X101" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>BlackSwaen Coffee</t>
+        </is>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="AH101" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>1.028</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>60.8695652</v>
+      </c>
+      <c r="AL101" t="inlineStr"/>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>The Swaen</t>
+        </is>
+      </c>
+      <c r="AN101" t="inlineStr">
+        <is>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr"/>
+      <c r="AP101" t="inlineStr"/>
+      <c r="AQ101" t="n">
+        <v>244.1</v>
+      </c>
+      <c r="AR101" t="inlineStr"/>
+      <c r="AS101" t="inlineStr"/>
+      <c r="AT101" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AT95"/>
+  <autoFilter ref="A1:AT101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12445,7 +13159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP80"/>
+  <dimension ref="A1:AP82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -20566,8 +21280,226 @@
       <c r="AO80" t="inlineStr"/>
       <c r="AP80" t="inlineStr"/>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>xlBmZbXhzbuHWfN1GoclwNdsgM9yT6</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Summer stout </t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Hop</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>default-J80zzFn0TQEAwwaQuzMQsRYzrIvBOC</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H81" t="n">
+        <v>15</v>
+      </c>
+      <c r="J81" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N81" t="b">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Hallertau Perle</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>A dual-purpose hop that offers great bittering properties as well as a well-rounded aroma profile. Aroma: Herbal - tea, pepper, floral, citrus, earthy, woody, grassy, caramel Alpha Acid: 4.0 - 9.0% Beta Acid: 2.5 - 4.5% Total Oil: 0.5 - 1.3 ml/100g</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr"/>
+      <c r="Z81" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>Pellet</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AF81" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 223000000, "_seconds": 1778682625}</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>G1hAXrUVQhnMlGnAla7zTuBYG3dJVx</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 715000000, "_seconds": 1789895043}</t>
+        </is>
+      </c>
+      <c r="AJ81" t="n">
+        <v>1789895043715</v>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>3.1.0</t>
+        </is>
+      </c>
+      <c r="AL81" t="n">
+        <v>138</v>
+      </c>
+      <c r="AM81" t="inlineStr"/>
+      <c r="AN81" t="inlineStr"/>
+      <c r="AO81" t="inlineStr"/>
+      <c r="AP81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>xlBmZbXhzbuHWfN1GoclwNdsgM9yT6</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Summer stout </t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Hop</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>default-J80zzFn0TQEAwwaQuzMQsRYzrIvBOC</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H82" t="n">
+        <v>15</v>
+      </c>
+      <c r="J82" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N82" t="b">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Hallertau Perle</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>A dual-purpose hop that offers great bittering properties as well as a well-rounded aroma profile. Aroma: Herbal - tea, pepper, floral, citrus, earthy, woody, grassy, caramel Alpha Acid: 4.0 - 9.0% Beta Acid: 2.5 - 4.5% Total Oil: 0.5 - 1.3 ml/100g</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr"/>
+      <c r="Z82" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>Pellet</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="AD82" t="inlineStr"/>
+      <c r="AE82" t="inlineStr"/>
+      <c r="AF82" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 223000000, "_seconds": 1778682625}</t>
+        </is>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>G1hAXrUVQhnMlGnAla7zTuBYG3dJVx</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 715000000, "_seconds": 1789895043}</t>
+        </is>
+      </c>
+      <c r="AJ82" t="n">
+        <v>1789895043715</v>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>3.1.0</t>
+        </is>
+      </c>
+      <c r="AL82" t="n">
+        <v>138</v>
+      </c>
+      <c r="AM82" t="inlineStr"/>
+      <c r="AN82" t="inlineStr"/>
+      <c r="AO82" t="inlineStr"/>
+      <c r="AP82" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AP80"/>
+  <autoFilter ref="A1:AP82"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20578,7 +21510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL26"/>
+  <dimension ref="A1:AL27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -23569,8 +24501,115 @@
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>xlBmZbXhzbuHWfN1GoclwNdsgM9yT6</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Summer stout </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Yeast</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>default-clIP1PsQiKPjtT5G8QaCqk0OjM2WlR</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>70</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Clean, aggressive, attenuative, ABV tolerant and highly flocculant. This yeast is the go-to house yeast for many microbreweries. This English style yeast provides the backbone for everything from IPA's to stouts to barleywines. Equivalent: Imperial House, White Labs WLP007 Dry English Ale, Wyeast 1098 British, Omega British Ale I</t>
+        </is>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Dry</t>
+        </is>
+      </c>
+      <c r="N27" t="b">
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>WHC Lab</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>12</v>
+      </c>
+      <c r="R27" t="n">
+        <v>80</v>
+      </c>
+      <c r="S27" t="n">
+        <v>21</v>
+      </c>
+      <c r="T27" t="n">
+        <v>73</v>
+      </c>
+      <c r="U27" t="n">
+        <v>16</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>British Pub Ale</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>pkg</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Stout, IPA, Pale Ale, Brown Ale, Red Ale, Imperial Stout</t>
+        </is>
+      </c>
+      <c r="AL27" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AL26"/>
+  <autoFilter ref="A1:AL27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23581,7 +24620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB146"/>
+  <dimension ref="A1:AB152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -35831,8 +36870,529 @@
       <c r="AA146" t="inlineStr"/>
       <c r="AB146" t="inlineStr"/>
     </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>xlBmZbXhzbuHWfN1GoclwNdsgM9yT6</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Summer stout </t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 20000000, "_seconds": 1706434207}</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>default-2302b0</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>dHzf3qHIzqCVtmbVlXqvCaYqHnAPxv</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 69000000, "_seconds": 1781339599}</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>1781339599069</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="K147" t="n">
+        <v>2</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="b">
+        <v>0</v>
+      </c>
+      <c r="N147" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Baking Soda (NaHCO3)</t>
+        </is>
+      </c>
+      <c r="Q147" t="b">
+        <v>0</v>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U147" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y147" t="inlineStr"/>
+      <c r="Z147" t="inlineStr"/>
+      <c r="AA147" t="inlineStr"/>
+      <c r="AB147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>xlBmZbXhzbuHWfN1GoclwNdsgM9yT6</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Summer stout </t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 152000000, "_seconds": 1699176797}</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>default-3b1827</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>xD9x1qmhYt1snySGFEG5hYH8K6gljD</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 647000000, "_seconds": 1789895044}</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>1789895044647</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>3.1.0</t>
+        </is>
+      </c>
+      <c r="K148" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M148" t="b">
+        <v>0</v>
+      </c>
+      <c r="N148" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Calcium Chloride (CaCl2)</t>
+        </is>
+      </c>
+      <c r="Q148" t="b">
+        <v>0</v>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U148" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y148" t="inlineStr"/>
+      <c r="Z148" t="inlineStr"/>
+      <c r="AA148" t="inlineStr"/>
+      <c r="AB148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>xlBmZbXhzbuHWfN1GoclwNdsgM9yT6</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Summer stout </t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 144000000, "_seconds": 1699176796}</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>default-1f88df</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>gPQRHI0XC908S70pJd3aPLDlxNrL00</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 309000000, "_seconds": 1789895044}</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>1789895044309</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>3.1.0</t>
+        </is>
+      </c>
+      <c r="K149" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="b">
+        <v>0</v>
+      </c>
+      <c r="N149" t="n">
+        <v>929.5</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Gypsum (CaSO4)</t>
+        </is>
+      </c>
+      <c r="Q149" t="b">
+        <v>0</v>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U149" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y149" t="inlineStr"/>
+      <c r="Z149" t="inlineStr"/>
+      <c r="AA149" t="inlineStr"/>
+      <c r="AB149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>xlBmZbXhzbuHWfN1GoclwNdsgM9yT6</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Summer stout </t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 828000000, "_seconds": 1706434207}</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>default-07adb1</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>1f3RTpuz73jj4GfdSrqo9SZDV92mBR</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 34000000, "_seconds": 1789895045}</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>1789895045034</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>3.1.0</t>
+        </is>
+      </c>
+      <c r="K150" t="n">
+        <v>2</v>
+      </c>
+      <c r="L150" t="n">
+        <v>80</v>
+      </c>
+      <c r="M150" t="b">
+        <v>0</v>
+      </c>
+      <c r="N150" t="n">
+        <v>334</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Lactic Acid</t>
+        </is>
+      </c>
+      <c r="Q150" t="b">
+        <v>0</v>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>Water Agent</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Mash</t>
+        </is>
+      </c>
+      <c r="U150" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y150" t="inlineStr"/>
+      <c r="Z150" t="inlineStr"/>
+      <c r="AA150" t="inlineStr"/>
+      <c r="AB150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>xlBmZbXhzbuHWfN1GoclwNdsgM9yT6</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Summer stout </t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 504000000, "_seconds": 1775809151}</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>default-5adf6e</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>XqJmJZ27RihaOgdZypjjCAeZ5Ybero</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 404000000, "_seconds": 1789895045}</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>1789895045404</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>3.1.0</t>
+        </is>
+      </c>
+      <c r="K151" t="n">
+        <v>1</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="b">
+        <v>0</v>
+      </c>
+      <c r="N151" t="n">
+        <v>4</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Irish Moss</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q151" t="b">
+        <v>0</v>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>Fining</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr"/>
+      <c r="Y151" t="inlineStr"/>
+      <c r="Z151" t="inlineStr"/>
+      <c r="AA151" t="inlineStr"/>
+      <c r="AB151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>xlBmZbXhzbuHWfN1GoclwNdsgM9yT6</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Summer stout </t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 67000000, "_seconds": 1775809134}</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>default-yn-wln1000</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>kdl08EEBMhKVgFHBmTNKK0S3PJxlNw</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>{"_nanoseconds": 532000000, "_seconds": 1789895046}</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>1789895046532</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>3.1.0</t>
+        </is>
+      </c>
+      <c r="K152" t="n">
+        <v>5</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="b">
+        <v>0</v>
+      </c>
+      <c r="N152" t="n">
+        <v>77.23999999999999</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Yeast Nutrient (WLN1000)</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q152" t="b">
+        <v>0</v>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr"/>
+      <c r="V152" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">White Labs Yeast Nutrient is used to increase the health of yeast, this improves fermentation and re-pitching performance. It contains diammonium phosphate (DAP), essential vitamins and co-factors, nitrogen, amino acids, proteins, peptides, and minerals. An effective boost for first and/or late-generation yeast slurry. If the grist is not 100% malt, then White Labs Yeast Nutrient can help make up for the lack of nutrients.
+We recommend using traditional finings agents for most fermentations. If you are still struggling with unwanted haze, filtration may be necessary. </t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr"/>
+      <c r="AA152" t="inlineStr"/>
+      <c r="AB152" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB146"/>
+  <autoFilter ref="A1:AB152"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/exports/Brewfather_Recipes_Summary.xlsx
+++ b/exports/Brewfather_Recipes_Summary.xlsx
@@ -28545,30 +28545,30 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>tRIJHPH0GJDvX68lIylAwbxCHqdx60</t>
+          <t>xD9x1qmhYt1snySGFEG5hYH8K6gljD</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 930000000, "_seconds": 1704369575}</t>
+          <t>{"_nanoseconds": 647000000, "_seconds": 1789895044}</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1704369575930</v>
+        <v>1789895044647</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2.10.4</t>
+          <t>3.1.0</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="M46" t="b">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>32.5</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -28596,9 +28596,6 @@
       <c r="U46" t="b">
         <v>1</v>
       </c>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr"/>
@@ -28632,20 +28629,20 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>lcvTqdMfO6NPRj6JBJoHMhZuaJN2Fj</t>
+          <t>gPQRHI0XC908S70pJd3aPLDlxNrL00</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 428000000, "_seconds": 1772634485}</t>
+          <t>{"_nanoseconds": 309000000, "_seconds": 1789895044}</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1772634485428</v>
+        <v>1789895044309</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2.20.2</t>
+          <t>3.1.0</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -28656,7 +28653,7 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>929.5</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -28717,24 +28714,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>eIuDGEasVf2TMzwhyNhxT2RGDDKeIc</t>
+          <t>1f3RTpuz73jj4GfdSrqo9SZDV92mBR</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>{"_nanoseconds": 497000000, "_seconds": 1772634487}</t>
+          <t>{"_nanoseconds": 34000000, "_seconds": 1789895045}</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1772634487497</v>
+        <v>1789895045034</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2.20.2</t>
+          <t>3.1.0</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="L48" t="n">
         <v>80</v>
@@ -28743,7 +28740,7 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
